--- a/src/gcover/data/GC_Sources_PA.xlsx
+++ b/src/gcover/data/GC_Sources_PA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\v0t0020a.adr.admin.ch\lg\01_PRODUKTION\GIS\TOPGIS\Produktableitung\R17_2026\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6192329A-3C09-4AED-8E0F-8A8B41471FF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CE66F6-C326-456E-AD2A-421E09061623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12615" yWindow="2115" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1122" uniqueCount="243">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="247">
   <si>
     <t>MSH_MAP_TITLE</t>
   </si>
@@ -192,9 +192,6 @@
     <t>Cossonay</t>
   </si>
   <si>
-    <t>Sissach</t>
-  </si>
-  <si>
     <t>Saas</t>
   </si>
   <si>
@@ -811,13 +808,28 @@
   </si>
   <si>
     <t>Mapsheet Val Bregaglia + Campodolcino fusionnés (feuille Campodolcino supprimée). Selon planning</t>
+  </si>
+  <si>
+    <t>Sissach-Rheinfelden</t>
+  </si>
+  <si>
+    <t>Release</t>
+  </si>
+  <si>
+    <t>Comment</t>
+  </si>
+  <si>
+    <t>R16</t>
+  </si>
+  <si>
+    <t>R17</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -842,8 +854,13 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -880,6 +897,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -893,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -940,14 +969,28 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1255,16 +1298,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="18" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E1" s="19" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F1" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="G1" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="G1" s="19" t="s">
-        <v>234</v>
+      <c r="H1" s="19" t="s">
+        <v>244</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>243</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="2"/>
@@ -1274,7 +1323,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
@@ -1283,16 +1332,16 @@
         <v>1086</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
@@ -1301,7 +1350,7 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B3" s="5">
         <v>2</v>
@@ -1310,16 +1359,16 @@
         <v>1162</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="2"/>
@@ -1328,7 +1377,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B4" s="5">
         <v>3</v>
@@ -1337,16 +1386,16 @@
         <v>1087</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="2"/>
@@ -1364,16 +1413,16 @@
         <v>1222</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="2"/>
@@ -1382,7 +1431,7 @@
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="5">
         <v>12</v>
@@ -1391,16 +1440,16 @@
         <v>1300</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K6" s="1"/>
       <c r="L6" s="2"/>
@@ -1409,7 +1458,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B7" s="5">
         <v>15</v>
@@ -1418,16 +1467,16 @@
         <v>1124</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="2"/>
@@ -1436,7 +1485,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B8" s="5">
         <v>17</v>
@@ -1445,16 +1494,16 @@
         <v>1221</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="2"/>
@@ -1463,7 +1512,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B9" s="5">
         <v>25</v>
@@ -1472,16 +1521,16 @@
         <v>1241</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="2"/>
@@ -1490,7 +1539,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B10" s="5">
         <v>26</v>
@@ -1499,16 +1548,16 @@
         <v>1186</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="2"/>
@@ -1526,16 +1575,16 @@
         <v>1223</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="2"/>
@@ -1553,16 +1602,16 @@
         <v>1206</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="2"/>
@@ -1571,7 +1620,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B13" s="5">
         <v>40</v>
@@ -1580,16 +1629,16 @@
         <v>1085</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="2"/>
@@ -1598,7 +1647,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B14" s="5">
         <v>42</v>
@@ -1607,16 +1656,16 @@
         <v>1202</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="2"/>
@@ -1625,7 +1674,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B15" s="5">
         <v>46</v>
@@ -1634,16 +1683,16 @@
         <v>1281</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="2"/>
@@ -1652,7 +1701,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B16" s="5">
         <v>48</v>
@@ -1661,16 +1710,16 @@
         <v>1301</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="2"/>
@@ -1679,7 +1728,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B17" s="5">
         <v>49</v>
@@ -1688,16 +1737,16 @@
         <v>1066</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="2"/>
@@ -1715,16 +1764,16 @@
         <v>1144</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="2"/>
@@ -1733,7 +1782,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B19" s="5">
         <v>55</v>
@@ -1742,16 +1791,16 @@
         <v>1065</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="2"/>
@@ -1760,7 +1809,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B20" s="5">
         <v>59</v>
@@ -1769,16 +1818,16 @@
         <v>1047</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="2"/>
@@ -1787,7 +1836,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B21" s="5">
         <v>60</v>
@@ -1796,16 +1845,16 @@
         <v>1145</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="2"/>
@@ -1814,7 +1863,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B22" s="5">
         <v>62</v>
@@ -1823,16 +1872,16 @@
         <v>1242</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="2"/>
@@ -1841,7 +1890,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B23" s="5">
         <v>63</v>
@@ -1850,16 +1899,16 @@
         <v>1165</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="2"/>
@@ -1868,7 +1917,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B24" s="5">
         <v>67</v>
@@ -1877,16 +1926,16 @@
         <v>1164</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="2"/>
@@ -1904,16 +1953,16 @@
         <v>1067</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="2"/>
@@ -1922,7 +1971,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B26" s="5">
         <v>85</v>
@@ -1931,16 +1980,16 @@
         <v>1243</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="2"/>
@@ -1949,7 +1998,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B27" s="5">
         <v>88</v>
@@ -1958,16 +2007,16 @@
         <v>1285</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="2"/>
@@ -1976,7 +2025,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B28" s="5">
         <v>94</v>
@@ -1985,16 +2034,16 @@
         <v>1203</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="2"/>
@@ -2003,7 +2052,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B29" s="5">
         <v>95</v>
@@ -2012,16 +2061,16 @@
         <v>1182</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="2"/>
@@ -2030,7 +2079,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B30" s="5">
         <v>96</v>
@@ -2039,16 +2088,16 @@
         <v>1106</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="2"/>
@@ -2057,7 +2106,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B31" s="5">
         <v>98</v>
@@ -2066,16 +2115,16 @@
         <v>1185</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="2"/>
@@ -2084,7 +2133,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B32" s="5">
         <v>99</v>
@@ -2093,16 +2142,16 @@
         <v>1204</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="2"/>
@@ -2111,7 +2160,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B33" s="5">
         <v>105</v>
@@ -2120,16 +2169,16 @@
         <v>1205</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="2"/>
@@ -2138,7 +2187,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B34" s="5">
         <v>114</v>
@@ -2147,16 +2196,16 @@
         <v>1183</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="2"/>
@@ -2165,7 +2214,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B35" s="5">
         <v>117</v>
@@ -2174,16 +2223,16 @@
         <v>1261</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="2"/>
@@ -2192,7 +2241,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B36" s="5">
         <v>123</v>
@@ -2201,16 +2250,16 @@
         <v>1184</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="2"/>
@@ -2219,7 +2268,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B37" s="5">
         <v>139</v>
@@ -2228,16 +2277,16 @@
         <v>1107</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="2"/>
@@ -2246,7 +2295,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="5">
         <v>143</v>
@@ -2255,16 +2304,16 @@
         <v>1226</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="2"/>
@@ -2273,7 +2322,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B39" s="5">
         <v>147</v>
@@ -2282,16 +2331,16 @@
         <v>1105</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="2"/>
@@ -2300,7 +2349,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B40" s="5">
         <v>155</v>
@@ -2309,16 +2358,16 @@
         <v>1125</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="2"/>
@@ -2327,7 +2376,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B41" s="8">
         <v>162</v>
@@ -2336,16 +2385,16 @@
         <v>1163</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E41" s="9" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
@@ -2365,16 +2414,16 @@
         <v>1143</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
@@ -2385,7 +2434,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B43" s="5">
         <v>180</v>
@@ -2394,16 +2443,16 @@
         <v>1195</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="2"/>
@@ -2412,7 +2461,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A44" s="8" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B44" s="8">
         <v>179</v>
@@ -2421,16 +2470,16 @@
         <v>1051</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
@@ -2441,7 +2490,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B45" s="5">
         <v>1329</v>
@@ -2450,19 +2499,19 @@
         <v>1329</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H45" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="2"/>
@@ -2471,7 +2520,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A46" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B46" s="12">
         <v>58</v>
@@ -2480,16 +2529,19 @@
         <v>1305</v>
       </c>
       <c r="D46" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E46" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G46" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I46" t="s">
+        <v>245</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="2"/>
@@ -2507,16 +2559,19 @@
         <v>1069</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G47" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I47" t="s">
+        <v>245</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="2"/>
@@ -2525,7 +2580,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B48" s="12">
         <v>115</v>
@@ -2534,16 +2589,19 @@
         <v>1225</v>
       </c>
       <c r="D48" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G48" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I48" t="s">
+        <v>245</v>
       </c>
       <c r="K48" s="4"/>
       <c r="L48" s="2"/>
@@ -2561,16 +2619,19 @@
         <v>1072</v>
       </c>
       <c r="D49" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G49" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I49" t="s">
+        <v>245</v>
       </c>
       <c r="K49" s="4"/>
       <c r="L49" s="2"/>
@@ -2588,16 +2649,19 @@
         <v>1114</v>
       </c>
       <c r="D50" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G50" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I50" t="s">
+        <v>245</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="2"/>
@@ -2606,7 +2670,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B51" s="12">
         <v>142</v>
@@ -2615,16 +2679,19 @@
         <v>1113</v>
       </c>
       <c r="D51" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G51" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I51" t="s">
+        <v>245</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="2"/>
@@ -2633,7 +2700,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A52" s="12" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B52" s="12">
         <v>151</v>
@@ -2642,16 +2709,19 @@
         <v>1071</v>
       </c>
       <c r="D52" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G52" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I52" t="s">
+        <v>245</v>
       </c>
       <c r="K52" s="4"/>
       <c r="L52" s="2"/>
@@ -2669,138 +2739,152 @@
         <v>1084</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G53" s="14" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="I53" t="s">
+        <v>245</v>
+      </c>
       <c r="K53" s="4"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B54" s="3">
-        <v>169</v>
-      </c>
-      <c r="C54" s="3">
-        <v>1327</v>
-      </c>
-      <c r="D54" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="E54" s="10" t="s">
+      <c r="A54" s="26" t="s">
+        <v>135</v>
+      </c>
+      <c r="B54" s="26">
+        <v>1189</v>
+      </c>
+      <c r="C54" s="26">
+        <v>1189</v>
+      </c>
+      <c r="D54" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E54" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G54" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="K54" s="4"/>
+      <c r="F54" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G54" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H54" t="s">
+        <v>240</v>
+      </c>
+      <c r="I54" t="s">
+        <v>246</v>
+      </c>
+      <c r="K54" s="1"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="4"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="B55" s="3">
-        <v>1136</v>
-      </c>
-      <c r="C55" s="3">
-        <v>1136</v>
-      </c>
-      <c r="D55" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="E55" s="10" t="s">
+      <c r="A55" s="26" t="s">
+        <v>127</v>
+      </c>
+      <c r="B55" s="26">
+        <v>14</v>
+      </c>
+      <c r="C55" s="26">
+        <v>1198</v>
+      </c>
+      <c r="D55" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G55" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="I55" s="3"/>
-      <c r="K55" s="4"/>
+      <c r="F55" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G55" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H55" t="s">
+        <v>240</v>
+      </c>
+      <c r="I55" t="s">
+        <v>246</v>
+      </c>
+      <c r="K55" s="1"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
-      <c r="N55" s="4"/>
+      <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" t="s">
-        <v>136</v>
-      </c>
-      <c r="B56">
-        <v>1189</v>
-      </c>
-      <c r="C56">
-        <v>1189</v>
-      </c>
-      <c r="D56" s="20" t="s">
-        <v>224</v>
-      </c>
-      <c r="E56" s="11" t="s">
+      <c r="A56" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="B56" s="26">
+        <v>1171</v>
+      </c>
+      <c r="C56" s="26">
+        <v>1171</v>
+      </c>
+      <c r="D56" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="E56" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G56" s="2" t="s">
-        <v>231</v>
+      <c r="F56" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G56" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="H56" t="s">
-        <v>241</v>
+        <v>240</v>
+      </c>
+      <c r="I56" t="s">
+        <v>246</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
-      <c r="N56" s="4"/>
+      <c r="N56" s="1"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" t="s">
-        <v>194</v>
-      </c>
-      <c r="B57">
-        <v>1249</v>
-      </c>
-      <c r="C57">
-        <v>1249</v>
-      </c>
-      <c r="D57" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E57" s="11" t="s">
+      <c r="A57" s="26" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="26">
+        <v>1176</v>
+      </c>
+      <c r="C57" s="26">
+        <v>1176</v>
+      </c>
+      <c r="D57" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="E57" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G57" s="2" t="s">
-        <v>231</v>
+      <c r="F57" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G57" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="H57" t="s">
-        <v>236</v>
+        <v>240</v>
+      </c>
+      <c r="I57" t="s">
+        <v>246</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="2"/>
@@ -2808,29 +2892,32 @@
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" t="s">
-        <v>61</v>
-      </c>
-      <c r="B58">
-        <v>1250</v>
-      </c>
-      <c r="C58">
-        <v>1250</v>
-      </c>
-      <c r="D58" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E58" s="11" t="s">
+      <c r="A58" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B58" s="26">
+        <v>1190</v>
+      </c>
+      <c r="C58" s="26">
+        <v>1190</v>
+      </c>
+      <c r="D58" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E58" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>231</v>
+      <c r="F58" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G58" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="H58" t="s">
-        <v>237</v>
+        <v>240</v>
+      </c>
+      <c r="I58" t="s">
+        <v>246</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="2"/>
@@ -2838,86 +2925,98 @@
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" t="s">
-        <v>143</v>
-      </c>
-      <c r="B59">
-        <v>1270</v>
-      </c>
-      <c r="C59">
-        <v>1270</v>
-      </c>
-      <c r="D59" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="E59" s="11" t="s">
+      <c r="A59" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="26">
+        <v>1191</v>
+      </c>
+      <c r="C59" s="26">
+        <v>1191</v>
+      </c>
+      <c r="D59" s="20" t="s">
+        <v>223</v>
+      </c>
+      <c r="E59" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G59" s="2" t="s">
-        <v>231</v>
+      <c r="F59" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G59" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="H59" t="s">
-        <v>237</v>
+        <v>240</v>
+      </c>
+      <c r="I59" t="s">
+        <v>246</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
-      <c r="N59" s="4"/>
+      <c r="N59" s="1"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" t="s">
-        <v>69</v>
-      </c>
-      <c r="B60">
-        <v>1293</v>
-      </c>
-      <c r="C60">
-        <v>1293</v>
-      </c>
-      <c r="D60" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="E60" s="11" t="s">
+      <c r="A60" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="B60" s="26">
+        <v>1273</v>
+      </c>
+      <c r="C60" s="26">
+        <v>1273</v>
+      </c>
+      <c r="D60" s="23" t="s">
+        <v>223</v>
+      </c>
+      <c r="E60" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="G60" s="2" t="s">
-        <v>231</v>
+      <c r="F60" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G60" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="H60" t="s">
-        <v>238</v>
+        <v>240</v>
+      </c>
+      <c r="I60" t="s">
+        <v>246</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
-      <c r="N60" s="1"/>
+      <c r="N60" s="4"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" t="s">
-        <v>86</v>
-      </c>
-      <c r="B61">
-        <v>4</v>
-      </c>
-      <c r="C61">
-        <v>1094</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E61" s="1" t="s">
+      <c r="A61" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="B61" s="26">
+        <v>1276</v>
+      </c>
+      <c r="C61" s="26">
+        <v>1276</v>
+      </c>
+      <c r="D61" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E61" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G61" s="2" t="s">
-        <v>231</v>
+      <c r="F61" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G61" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H61" t="s">
+        <v>241</v>
+      </c>
+      <c r="I61" t="s">
+        <v>246</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="2"/>
@@ -2925,26 +3024,32 @@
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" t="s">
-        <v>48</v>
-      </c>
-      <c r="B62">
-        <v>6</v>
-      </c>
-      <c r="C62">
-        <v>1228</v>
-      </c>
-      <c r="D62" s="1" t="s">
+      <c r="A62" s="26" t="s">
+        <v>213</v>
+      </c>
+      <c r="B62" s="26">
+        <v>1254</v>
+      </c>
+      <c r="C62" s="26">
+        <v>1254</v>
+      </c>
+      <c r="D62" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G62" s="2" t="s">
-        <v>231</v>
+      <c r="F62" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G62" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H62" t="s">
+        <v>240</v>
+      </c>
+      <c r="I62" t="s">
+        <v>246</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="2"/>
@@ -2952,26 +3057,32 @@
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" t="s">
-        <v>82</v>
-      </c>
-      <c r="B63">
-        <v>7</v>
-      </c>
-      <c r="C63">
-        <v>1112</v>
-      </c>
-      <c r="D63" s="1" t="s">
+      <c r="A63" s="26" t="s">
+        <v>77</v>
+      </c>
+      <c r="B63" s="26">
+        <v>1294</v>
+      </c>
+      <c r="C63" s="26">
+        <v>1294</v>
+      </c>
+      <c r="D63" s="21" t="s">
         <v>223</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G63" s="2" t="s">
-        <v>231</v>
+      <c r="F63" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="G63" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H63" t="s">
+        <v>240</v>
+      </c>
+      <c r="I63" t="s">
+        <v>246</v>
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="2"/>
@@ -2979,26 +3090,32 @@
       <c r="N63" s="1"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" t="s">
-        <v>94</v>
-      </c>
-      <c r="B64">
-        <v>8</v>
-      </c>
-      <c r="C64">
-        <v>1304</v>
-      </c>
-      <c r="D64" s="1" t="s">
+      <c r="A64" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="B64" s="26">
+        <v>127</v>
+      </c>
+      <c r="C64" s="26">
+        <v>1172</v>
+      </c>
+      <c r="D64" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G64" s="2" t="s">
-        <v>231</v>
+      <c r="F64" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G64" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H64" t="s">
+        <v>240</v>
+      </c>
+      <c r="I64" t="s">
+        <v>246</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="2"/>
@@ -3006,26 +3123,32 @@
       <c r="N64" s="1"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" t="s">
-        <v>52</v>
-      </c>
-      <c r="B65">
-        <v>9</v>
-      </c>
-      <c r="C65">
-        <v>1217</v>
-      </c>
-      <c r="D65" s="1" t="s">
+      <c r="A65" s="26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" s="26">
+        <v>129</v>
+      </c>
+      <c r="C65" s="26">
+        <v>1132</v>
+      </c>
+      <c r="D65" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>231</v>
+      <c r="F65" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G65" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H65" t="s">
+        <v>240</v>
+      </c>
+      <c r="I65" t="s">
+        <v>246</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="2"/>
@@ -3033,26 +3156,32 @@
       <c r="N65" s="1"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" t="s">
-        <v>83</v>
-      </c>
-      <c r="B66">
-        <v>11</v>
-      </c>
-      <c r="C66">
-        <v>1314</v>
-      </c>
-      <c r="D66" s="1" t="s">
+      <c r="A66" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="B66" s="26">
+        <v>146</v>
+      </c>
+      <c r="C66" s="26">
+        <v>1211</v>
+      </c>
+      <c r="D66" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>231</v>
+      <c r="F66" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G66" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H66" t="s">
+        <v>240</v>
+      </c>
+      <c r="I66" t="s">
+        <v>246</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="2"/>
@@ -3060,26 +3189,32 @@
       <c r="N66" s="1"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" t="s">
-        <v>32</v>
-      </c>
-      <c r="B67">
-        <v>13</v>
-      </c>
-      <c r="C67">
-        <v>1229</v>
-      </c>
-      <c r="D67" s="1" t="s">
+      <c r="A67" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="26">
+        <v>154</v>
+      </c>
+      <c r="C67" s="26">
+        <v>1215</v>
+      </c>
+      <c r="D67" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>231</v>
+      <c r="F67" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G67" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H67" t="s">
+        <v>240</v>
+      </c>
+      <c r="I67" t="s">
+        <v>246</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="2"/>
@@ -3087,137 +3222,164 @@
       <c r="N67" s="1"/>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" t="s">
-        <v>128</v>
-      </c>
-      <c r="B68">
-        <v>14</v>
-      </c>
-      <c r="C68">
-        <v>1198</v>
-      </c>
-      <c r="D68" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="E68" s="1" t="s">
+      <c r="A68" s="27" t="s">
+        <v>43</v>
+      </c>
+      <c r="B68" s="27">
+        <v>158</v>
+      </c>
+      <c r="C68" s="27">
+        <v>1088</v>
+      </c>
+      <c r="D68" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="E68" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G68" s="2" t="s">
-        <v>231</v>
+      <c r="F68" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G68" s="28" t="s">
+        <v>230</v>
       </c>
       <c r="H68" t="s">
-        <v>241</v>
-      </c>
-      <c r="K68" s="1"/>
+        <v>240</v>
+      </c>
+      <c r="I68" t="s">
+        <v>246</v>
+      </c>
+      <c r="K68" s="4"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
-      <c r="N68" s="1"/>
+      <c r="N68" s="4"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" t="s">
-        <v>63</v>
-      </c>
-      <c r="B69">
-        <v>16</v>
-      </c>
-      <c r="C69">
-        <v>1053</v>
-      </c>
-      <c r="D69" s="1" t="s">
+      <c r="A69" s="27" t="s">
+        <v>17</v>
+      </c>
+      <c r="B69" s="27">
+        <v>160</v>
+      </c>
+      <c r="C69" s="27">
+        <v>1212</v>
+      </c>
+      <c r="D69" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G69" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K69" s="1"/>
+      <c r="F69" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G69" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H69" t="s">
+        <v>240</v>
+      </c>
+      <c r="I69" t="s">
+        <v>246</v>
+      </c>
+      <c r="K69" s="4"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
-      <c r="N69" s="1"/>
+      <c r="N69" s="4"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" t="s">
-        <v>184</v>
-      </c>
-      <c r="B70">
-        <v>18</v>
-      </c>
-      <c r="C70">
-        <v>1130</v>
-      </c>
-      <c r="D70" s="1" t="s">
+      <c r="A70" s="27" t="s">
+        <v>242</v>
+      </c>
+      <c r="B70" s="27">
+        <v>161</v>
+      </c>
+      <c r="C70" s="27">
+        <v>1068</v>
+      </c>
+      <c r="D70" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K70" s="1"/>
+      <c r="F70" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G70" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H70" t="s">
+        <v>240</v>
+      </c>
+      <c r="I70" t="s">
+        <v>246</v>
+      </c>
+      <c r="K70" s="4"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
-      <c r="N70" s="1"/>
+      <c r="N70" s="4"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" t="s">
-        <v>93</v>
-      </c>
-      <c r="B71">
-        <v>20</v>
-      </c>
-      <c r="C71">
-        <v>1218</v>
-      </c>
-      <c r="D71" s="1" t="s">
+      <c r="A71" s="27" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" s="27">
+        <v>173</v>
+      </c>
+      <c r="C71" s="27">
+        <v>1174</v>
+      </c>
+      <c r="D71" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G71" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K71" s="1"/>
+      <c r="F71" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G71" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H71" t="s">
+        <v>240</v>
+      </c>
+      <c r="I71" t="s">
+        <v>246</v>
+      </c>
+      <c r="K71" s="4"/>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
-      <c r="N71" s="1"/>
+      <c r="N71" s="4"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72" t="s">
-        <v>76</v>
-      </c>
-      <c r="B72">
-        <v>21</v>
-      </c>
-      <c r="C72">
-        <v>1187</v>
-      </c>
-      <c r="D72" s="1" t="s">
+      <c r="A72" s="26" t="s">
+        <v>217</v>
+      </c>
+      <c r="B72" s="26">
+        <v>178</v>
+      </c>
+      <c r="C72" s="26">
+        <v>1175</v>
+      </c>
+      <c r="D72" s="24" t="s">
         <v>223</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="22" t="s">
         <v>226</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G72" s="2" t="s">
-        <v>231</v>
+      <c r="F72" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G72" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H72" t="s">
+        <v>240</v>
+      </c>
+      <c r="I72" t="s">
+        <v>246</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="2"/>
@@ -3225,26 +3387,32 @@
       <c r="N72" s="1"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73" t="s">
-        <v>166</v>
-      </c>
-      <c r="B73">
-        <v>22</v>
-      </c>
-      <c r="C73">
-        <v>1147</v>
-      </c>
-      <c r="D73" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E73" s="1" t="s">
+      <c r="A73" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="B73" s="26">
+        <v>133</v>
+      </c>
+      <c r="C73" s="26">
+        <v>1231</v>
+      </c>
+      <c r="D73" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="E73" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G73" s="2" t="s">
-        <v>231</v>
+      <c r="F73" s="28" t="s">
+        <v>229</v>
+      </c>
+      <c r="G73" s="28" t="s">
+        <v>230</v>
+      </c>
+      <c r="H73" t="s">
+        <v>240</v>
+      </c>
+      <c r="I73" t="s">
+        <v>246</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="2"/>
@@ -3252,80 +3420,89 @@
       <c r="N73" s="1"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74" t="s">
-        <v>222</v>
-      </c>
-      <c r="B74">
-        <v>23</v>
-      </c>
-      <c r="C74">
-        <v>1095</v>
-      </c>
-      <c r="D74" s="1" t="s">
+      <c r="A74" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B74" s="3">
+        <v>169</v>
+      </c>
+      <c r="C74" s="3">
+        <v>1327</v>
+      </c>
+      <c r="D74" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E74" s="1" t="s">
-        <v>226</v>
+      <c r="E74" s="10" t="s">
+        <v>225</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K74" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
+      <c r="K74" s="4"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
-      <c r="N74" s="1"/>
+      <c r="N74" s="4"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75" t="s">
-        <v>152</v>
-      </c>
-      <c r="B75">
-        <v>24</v>
-      </c>
-      <c r="C75">
-        <v>1324</v>
-      </c>
-      <c r="D75" s="1" t="s">
+      <c r="A75" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B75" s="3">
+        <v>1136</v>
+      </c>
+      <c r="C75" s="3">
+        <v>1136</v>
+      </c>
+      <c r="D75" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E75" s="1" t="s">
-        <v>226</v>
+      <c r="E75" s="10" t="s">
+        <v>225</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K75" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H75" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I75" s="3"/>
+      <c r="K75" s="4"/>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
-      <c r="N75" s="1"/>
+      <c r="N75" s="4"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>29</v>
+        <v>193</v>
       </c>
       <c r="B76">
-        <v>28</v>
+        <v>1249</v>
       </c>
       <c r="C76">
-        <v>1150</v>
-      </c>
-      <c r="D76" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D76" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E76" s="1" t="s">
-        <v>226</v>
+      <c r="E76" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+      <c r="H76" t="s">
+        <v>235</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="2"/>
@@ -3334,25 +3511,28 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="B77">
-        <v>29</v>
+        <v>1250</v>
       </c>
       <c r="C77">
-        <v>1348</v>
-      </c>
-      <c r="D77" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D77" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E77" s="1" t="s">
-        <v>226</v>
+      <c r="E77" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="F77" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+      <c r="H77" t="s">
+        <v>236</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="2"/>
@@ -3361,52 +3541,58 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>38</v>
+        <v>142</v>
       </c>
       <c r="B78">
-        <v>30</v>
+        <v>1270</v>
       </c>
       <c r="C78">
-        <v>1349</v>
-      </c>
-      <c r="D78" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D78" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="E78" s="1" t="s">
-        <v>226</v>
+      <c r="E78" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+      <c r="H78" t="s">
+        <v>236</v>
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
-      <c r="N78" s="1"/>
+      <c r="N78" s="4"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="B79">
-        <v>32</v>
+        <v>1293</v>
       </c>
       <c r="C79">
-        <v>1267</v>
-      </c>
-      <c r="D79" s="1" t="s">
+        <v>1293</v>
+      </c>
+      <c r="D79" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E79" s="1" t="s">
-        <v>226</v>
+      <c r="E79" s="11" t="s">
+        <v>225</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
+      </c>
+      <c r="H79" t="s">
+        <v>237</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="2"/>
@@ -3415,25 +3601,25 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>59</v>
+        <v>85</v>
       </c>
       <c r="B80">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C80">
-        <v>1365</v>
+        <v>1094</v>
       </c>
       <c r="D80" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="2"/>
@@ -3442,25 +3628,25 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>192</v>
+        <v>47</v>
       </c>
       <c r="B81">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="C81">
-        <v>1271</v>
+        <v>1228</v>
       </c>
       <c r="D81" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K81" s="1"/>
       <c r="L81" s="2"/>
@@ -3469,25 +3655,25 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="B82">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="C82">
-        <v>1286</v>
+        <v>1112</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K82" s="1"/>
       <c r="L82" s="2"/>
@@ -3496,25 +3682,25 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>118</v>
+        <v>93</v>
       </c>
       <c r="B83">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="C83">
-        <v>1284</v>
+        <v>1304</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K83" s="1"/>
       <c r="L83" s="2"/>
@@ -3523,25 +3709,25 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>34</v>
+        <v>51</v>
       </c>
       <c r="B84">
-        <v>38</v>
+        <v>9</v>
       </c>
       <c r="C84">
-        <v>1032</v>
+        <v>1217</v>
       </c>
       <c r="D84" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="2"/>
@@ -3550,25 +3736,25 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>215</v>
+        <v>82</v>
       </c>
       <c r="B85">
-        <v>39</v>
+        <v>11</v>
       </c>
       <c r="C85">
-        <v>1333</v>
+        <v>1314</v>
       </c>
       <c r="D85" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="2"/>
@@ -3577,25 +3763,25 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>190</v>
+        <v>32</v>
       </c>
       <c r="B86">
-        <v>41</v>
+        <v>13</v>
       </c>
       <c r="C86">
-        <v>1266</v>
+        <v>1229</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K86" s="1"/>
       <c r="L86" s="2"/>
@@ -3604,25 +3790,25 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="B87">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="C87">
-        <v>1328</v>
+        <v>1053</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="2"/>
@@ -3631,25 +3817,25 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B88">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C88">
-        <v>1199</v>
+        <v>1130</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K88" s="1"/>
       <c r="L88" s="2"/>
@@ -3658,25 +3844,25 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>188</v>
+        <v>92</v>
       </c>
       <c r="B89">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="C89">
-        <v>1075</v>
+        <v>1218</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K89" s="1"/>
       <c r="L89" s="2"/>
@@ -3685,25 +3871,25 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="B90">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C90">
-        <v>1264</v>
+        <v>1187</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K90" s="1"/>
       <c r="L90" s="2"/>
@@ -3712,25 +3898,25 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>18</v>
+        <v>165</v>
       </c>
       <c r="B91">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C91">
-        <v>1090</v>
+        <v>1147</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K91" s="1"/>
       <c r="L91" s="2"/>
@@ -3739,25 +3925,25 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>77</v>
+        <v>221</v>
       </c>
       <c r="B92">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="C92">
-        <v>1052</v>
+        <v>1095</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K92" s="1"/>
       <c r="L92" s="2"/>
@@ -3766,25 +3952,25 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>168</v>
+        <v>151</v>
       </c>
       <c r="B93">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="C93">
-        <v>1133</v>
+        <v>1324</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K93" s="1"/>
       <c r="L93" s="2"/>
@@ -3793,25 +3979,25 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="B94">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="C94">
-        <v>1054</v>
+        <v>1150</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K94" s="1"/>
       <c r="L94" s="2"/>
@@ -3820,25 +4006,25 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>220</v>
+        <v>46</v>
       </c>
       <c r="B95">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="C95">
-        <v>1235</v>
+        <v>1348</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K95" s="1"/>
       <c r="L95" s="2"/>
@@ -3847,25 +4033,25 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>182</v>
+        <v>37</v>
       </c>
       <c r="B96">
-        <v>57</v>
+        <v>30</v>
       </c>
       <c r="C96">
-        <v>1093</v>
+        <v>1349</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K96" s="1"/>
       <c r="L96" s="2"/>
@@ -3874,25 +4060,25 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>27</v>
+        <v>122</v>
       </c>
       <c r="B97">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="C97">
-        <v>1309</v>
+        <v>1267</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K97" s="1"/>
       <c r="L97" s="2"/>
@@ -3901,25 +4087,25 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A98" t="s">
-        <v>115</v>
+        <v>58</v>
       </c>
       <c r="B98">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="C98">
-        <v>1265</v>
+        <v>1365</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K98" s="1"/>
       <c r="L98" s="2"/>
@@ -3928,25 +4114,25 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>49</v>
+        <v>191</v>
       </c>
       <c r="B99">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="C99">
-        <v>1074</v>
+        <v>1271</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K99" s="1"/>
       <c r="L99" s="2"/>
@@ -3955,25 +4141,25 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
       <c r="B100">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="C100">
-        <v>1313</v>
+        <v>1286</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K100" s="1"/>
       <c r="L100" s="2"/>
@@ -3982,25 +4168,25 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="B101">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="C101">
-        <v>1251</v>
+        <v>1284</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K101" s="1"/>
       <c r="L101" s="2"/>
@@ -4009,25 +4195,25 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="B102">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="C102">
-        <v>1353</v>
+        <v>1032</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K102" s="1"/>
       <c r="L102" s="2"/>
@@ -4036,25 +4222,25 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>175</v>
+        <v>214</v>
       </c>
       <c r="B103">
-        <v>70</v>
+        <v>39</v>
       </c>
       <c r="C103">
-        <v>1296</v>
+        <v>1333</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K103" s="1"/>
       <c r="L103" s="2"/>
@@ -4063,25 +4249,25 @@
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A104" t="s">
-        <v>167</v>
+        <v>189</v>
       </c>
       <c r="B104">
-        <v>71</v>
+        <v>41</v>
       </c>
       <c r="C104">
-        <v>1308</v>
+        <v>1266</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K104" s="1"/>
       <c r="L104" s="2"/>
@@ -4090,25 +4276,25 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>212</v>
+        <v>40</v>
       </c>
       <c r="B105">
-        <v>72</v>
+        <v>43</v>
       </c>
       <c r="C105">
-        <v>1127</v>
+        <v>1328</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K105" s="1"/>
       <c r="L105" s="2"/>
@@ -4117,25 +4303,25 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>216</v>
+        <v>169</v>
       </c>
       <c r="B106">
-        <v>73</v>
+        <v>44</v>
       </c>
       <c r="C106">
-        <v>1272</v>
+        <v>1199</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K106" s="1"/>
       <c r="L106" s="2"/>
@@ -4144,25 +4330,25 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B107">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="C107">
-        <v>1031</v>
+        <v>1075</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K107" s="1"/>
       <c r="L107" s="2"/>
@@ -4171,25 +4357,25 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A108" t="s">
-        <v>46</v>
+        <v>121</v>
       </c>
       <c r="B108">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="C108">
-        <v>1188</v>
+        <v>1264</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K108" s="1"/>
       <c r="L108" s="2"/>
@@ -4198,25 +4384,25 @@
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A109" t="s">
-        <v>56</v>
+        <v>18</v>
       </c>
       <c r="B109">
-        <v>76</v>
+        <v>50</v>
       </c>
       <c r="C109">
-        <v>1146</v>
+        <v>1090</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K109" s="1"/>
       <c r="L109" s="2"/>
@@ -4225,25 +4411,25 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A110" t="s">
-        <v>103</v>
+        <v>76</v>
       </c>
       <c r="B110">
-        <v>77</v>
+        <v>52</v>
       </c>
       <c r="C110">
-        <v>1325</v>
+        <v>1052</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K110" s="1"/>
       <c r="L110" s="2"/>
@@ -4252,25 +4438,25 @@
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A111" t="s">
-        <v>80</v>
+        <v>167</v>
       </c>
       <c r="B111">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="C111">
-        <v>1115</v>
+        <v>1133</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E111" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K111" s="1"/>
       <c r="L111" s="2"/>
@@ -4279,25 +4465,25 @@
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A112" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="B112">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="C112">
-        <v>1128</v>
+        <v>1054</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E112" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K112" s="1"/>
       <c r="L112" s="2"/>
@@ -4306,25 +4492,25 @@
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A113" t="s">
-        <v>164</v>
+        <v>219</v>
       </c>
       <c r="B113">
-        <v>81</v>
+        <v>56</v>
       </c>
       <c r="C113">
-        <v>1237</v>
+        <v>1235</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E113" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K113" s="1"/>
       <c r="L113" s="2"/>
@@ -4333,25 +4519,25 @@
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A114" t="s">
-        <v>134</v>
+        <v>181</v>
       </c>
       <c r="B114">
-        <v>82</v>
+        <v>57</v>
       </c>
       <c r="C114">
-        <v>1268</v>
+        <v>1093</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K114" s="1"/>
       <c r="L114" s="2"/>
@@ -4360,25 +4546,25 @@
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A115" t="s">
-        <v>160</v>
+        <v>27</v>
       </c>
       <c r="B115">
-        <v>83</v>
+        <v>61</v>
       </c>
       <c r="C115">
-        <v>1192</v>
+        <v>1309</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K115" s="1"/>
       <c r="L115" s="2"/>
@@ -4387,25 +4573,25 @@
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A116" t="s">
-        <v>85</v>
+        <v>114</v>
       </c>
       <c r="B116">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="C116">
-        <v>1129</v>
+        <v>1265</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K116" s="1"/>
       <c r="L116" s="2"/>
@@ -4414,25 +4600,25 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A117" t="s">
-        <v>185</v>
+        <v>48</v>
       </c>
       <c r="B117">
-        <v>86</v>
+        <v>65</v>
       </c>
       <c r="C117">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K117" s="1"/>
       <c r="L117" s="2"/>
@@ -4441,25 +4627,25 @@
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A118" t="s">
-        <v>104</v>
+        <v>49</v>
       </c>
       <c r="B118">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="C118">
-        <v>1247</v>
+        <v>1313</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E118" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K118" s="1"/>
       <c r="L118" s="2"/>
@@ -4468,25 +4654,25 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A119" t="s">
-        <v>133</v>
+        <v>63</v>
       </c>
       <c r="B119">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="C119">
-        <v>1131</v>
+        <v>1251</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K119" s="1"/>
       <c r="L119" s="2"/>
@@ -4495,25 +4681,25 @@
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A120" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B120">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="C120">
-        <v>1091</v>
+        <v>1353</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K120" s="1"/>
       <c r="L120" s="2"/>
@@ -4522,25 +4708,25 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>120</v>
+        <v>174</v>
       </c>
       <c r="B121">
-        <v>91</v>
+        <v>70</v>
       </c>
       <c r="C121">
-        <v>1345</v>
+        <v>1296</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K121" s="1"/>
       <c r="L121" s="2"/>
@@ -4549,25 +4735,25 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>70</v>
+        <v>166</v>
       </c>
       <c r="B122">
-        <v>92</v>
+        <v>71</v>
       </c>
       <c r="C122">
-        <v>1244</v>
+        <v>1308</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K122" s="1"/>
       <c r="L122" s="2"/>
@@ -4576,25 +4762,25 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>58</v>
+        <v>211</v>
       </c>
       <c r="B123">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="C123">
-        <v>1289</v>
+        <v>1127</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K123" s="1"/>
       <c r="L123" s="2"/>
@@ -4603,25 +4789,25 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="B124">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="C124">
-        <v>1011</v>
+        <v>1272</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F124" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K124" s="1"/>
       <c r="L124" s="2"/>
@@ -4630,25 +4816,25 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="B125">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="C125">
-        <v>1166</v>
+        <v>1031</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K125" s="1"/>
       <c r="L125" s="2"/>
@@ -4657,25 +4843,25 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="B126">
-        <v>101</v>
+        <v>75</v>
       </c>
       <c r="C126">
-        <v>1346</v>
+        <v>1188</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K126" s="1"/>
       <c r="L126" s="2"/>
@@ -4684,25 +4870,25 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>131</v>
+        <v>55</v>
       </c>
       <c r="B127">
-        <v>102</v>
+        <v>76</v>
       </c>
       <c r="C127">
-        <v>1050</v>
+        <v>1146</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K127" s="1"/>
       <c r="L127" s="2"/>
@@ -4711,25 +4897,25 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>205</v>
+        <v>102</v>
       </c>
       <c r="B128">
-        <v>103</v>
+        <v>77</v>
       </c>
       <c r="C128">
-        <v>1224</v>
+        <v>1325</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K128" s="1"/>
       <c r="L128" s="2"/>
@@ -4738,25 +4924,25 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="B129">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="C129">
-        <v>1167</v>
+        <v>1115</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K129" s="1"/>
       <c r="L129" s="2"/>
@@ -4765,25 +4951,25 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>200</v>
+        <v>97</v>
       </c>
       <c r="B130">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="C130">
-        <v>1134</v>
+        <v>1128</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K130" s="1"/>
       <c r="L130" s="2"/>
@@ -4792,25 +4978,25 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>99</v>
+        <v>163</v>
       </c>
       <c r="B131">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="C131">
-        <v>1347</v>
+        <v>1237</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K131" s="1"/>
       <c r="L131" s="2"/>
@@ -4819,25 +5005,25 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>187</v>
+        <v>133</v>
       </c>
       <c r="B132">
-        <v>108</v>
+        <v>82</v>
       </c>
       <c r="C132">
-        <v>1076</v>
+        <v>1268</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K132" s="1"/>
       <c r="L132" s="2"/>
@@ -4846,25 +5032,25 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="B133">
-        <v>109</v>
+        <v>83</v>
       </c>
       <c r="C133">
-        <v>1126</v>
+        <v>1192</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E133" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K133" s="1"/>
       <c r="L133" s="2"/>
@@ -4873,25 +5059,25 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="B134">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="C134">
-        <v>1287</v>
+        <v>1129</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K134" s="1"/>
       <c r="L134" s="2"/>
@@ -4900,25 +5086,25 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>74</v>
+        <v>184</v>
       </c>
       <c r="B135">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C135">
-        <v>1033</v>
+        <v>1073</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K135" s="1"/>
       <c r="L135" s="2"/>
@@ -4927,25 +5113,25 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>198</v>
+        <v>103</v>
       </c>
       <c r="B136">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="C136">
-        <v>1108</v>
+        <v>1247</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K136" s="1"/>
       <c r="L136" s="2"/>
@@ -4954,25 +5140,25 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="B137">
-        <v>116</v>
+        <v>89</v>
       </c>
       <c r="C137">
-        <v>1151</v>
+        <v>1131</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F137" s="2" t="s">
         <v>230</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K137" s="1"/>
       <c r="L137" s="2"/>
@@ -4981,25 +5167,25 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="B138">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="C138">
-        <v>1257</v>
+        <v>1091</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K138" s="1"/>
       <c r="L138" s="2"/>
@@ -5008,25 +5194,25 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>217</v>
+        <v>119</v>
       </c>
       <c r="B139">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="C139">
-        <v>1277</v>
+        <v>1345</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K139" s="1"/>
       <c r="L139" s="2"/>
@@ -5035,25 +5221,25 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>132</v>
+        <v>69</v>
       </c>
       <c r="B140">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="C140">
-        <v>1070</v>
+        <v>1244</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K140" s="1"/>
       <c r="L140" s="2"/>
@@ -5062,25 +5248,25 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>138</v>
+        <v>57</v>
       </c>
       <c r="B141">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="C141">
-        <v>1234</v>
+        <v>1289</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K141" s="1"/>
       <c r="L141" s="2"/>
@@ -5089,25 +5275,25 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>203</v>
+        <v>171</v>
       </c>
       <c r="B142">
-        <v>122</v>
+        <v>97</v>
       </c>
       <c r="C142">
-        <v>1307</v>
+        <v>1011</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K142" s="1"/>
       <c r="L142" s="2"/>
@@ -5116,25 +5302,25 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="B143">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="C143">
-        <v>1256</v>
+        <v>1166</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E143" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K143" s="1"/>
       <c r="L143" s="2"/>
@@ -5143,25 +5329,25 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>124</v>
+        <v>52</v>
       </c>
       <c r="B144">
-        <v>125</v>
+        <v>101</v>
       </c>
       <c r="C144">
-        <v>1055</v>
+        <v>1346</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K144" s="1"/>
       <c r="L144" s="2"/>
@@ -5170,25 +5356,25 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>208</v>
+        <v>130</v>
       </c>
       <c r="B145">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="C145">
-        <v>1232</v>
+        <v>1050</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K145" s="1"/>
       <c r="L145" s="2"/>
@@ -5197,25 +5383,25 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="B146">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="C146">
-        <v>1172</v>
+        <v>1224</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E146" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K146" s="1"/>
       <c r="L146" s="2"/>
@@ -5224,25 +5410,25 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="B147">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="C147">
-        <v>1092</v>
+        <v>1167</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E147" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K147" s="1"/>
       <c r="L147" s="2"/>
@@ -5251,25 +5437,25 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>176</v>
+        <v>199</v>
       </c>
       <c r="B148">
-        <v>129</v>
+        <v>106</v>
       </c>
       <c r="C148">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E148" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K148" s="1"/>
       <c r="L148" s="2"/>
@@ -5278,25 +5464,25 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>191</v>
+        <v>98</v>
       </c>
       <c r="B149">
-        <v>130</v>
+        <v>107</v>
       </c>
       <c r="C149">
-        <v>1306</v>
+        <v>1347</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K149" s="1"/>
       <c r="L149" s="2"/>
@@ -5305,25 +5491,25 @@
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A150" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B150">
-        <v>131</v>
+        <v>108</v>
       </c>
       <c r="C150">
-        <v>1269</v>
+        <v>1076</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K150" s="1"/>
       <c r="L150" s="2"/>
@@ -5332,25 +5518,25 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>33</v>
+        <v>83</v>
       </c>
       <c r="B151">
-        <v>132</v>
+        <v>109</v>
       </c>
       <c r="C151">
-        <v>1214</v>
+        <v>1126</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E151" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K151" s="1"/>
       <c r="L151" s="2"/>
@@ -5359,25 +5545,25 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="B152">
-        <v>133</v>
+        <v>111</v>
       </c>
       <c r="C152">
-        <v>1231</v>
+        <v>1287</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E152" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K152" s="1"/>
       <c r="L152" s="2"/>
@@ -5386,25 +5572,25 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="B153">
-        <v>134</v>
+        <v>112</v>
       </c>
       <c r="C153">
-        <v>1111</v>
+        <v>1033</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E153" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K153" s="1"/>
       <c r="L153" s="2"/>
@@ -5413,25 +5599,25 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>127</v>
+        <v>197</v>
       </c>
       <c r="B154">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="C154">
-        <v>1089</v>
+        <v>1108</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K154" s="1"/>
       <c r="L154" s="2"/>
@@ -5440,25 +5626,25 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="B155">
-        <v>136</v>
+        <v>116</v>
       </c>
       <c r="C155">
-        <v>1233</v>
+        <v>1151</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E155" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K155" s="1"/>
       <c r="L155" s="2"/>
@@ -5467,25 +5653,25 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>135</v>
+        <v>61</v>
       </c>
       <c r="B156">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="C156">
-        <v>1170</v>
+        <v>1257</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E156" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K156" s="1"/>
       <c r="L156" s="2"/>
@@ -5494,25 +5680,25 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="B157">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="C157">
-        <v>1252</v>
+        <v>1277</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K157" s="1"/>
       <c r="L157" s="2"/>
@@ -5521,25 +5707,25 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>96</v>
+        <v>131</v>
       </c>
       <c r="B158">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="C158">
-        <v>1245</v>
+        <v>1070</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E158" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K158" s="1"/>
       <c r="L158" s="2"/>
@@ -5548,25 +5734,25 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>105</v>
+        <v>137</v>
       </c>
       <c r="B159">
-        <v>145</v>
+        <v>121</v>
       </c>
       <c r="C159">
-        <v>1291</v>
+        <v>1234</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K159" s="1"/>
       <c r="L159" s="2"/>
@@ -5575,25 +5761,25 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>117</v>
+        <v>202</v>
       </c>
       <c r="B160">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="C160">
-        <v>1211</v>
+        <v>1307</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K160" s="1"/>
       <c r="L160" s="2"/>
@@ -5602,25 +5788,25 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="B161">
-        <v>148</v>
+        <v>124</v>
       </c>
       <c r="C161">
-        <v>1169</v>
+        <v>1256</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K161" s="1"/>
       <c r="L161" s="2"/>
@@ -5629,25 +5815,25 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>79</v>
+        <v>123</v>
       </c>
       <c r="B162">
-        <v>149</v>
+        <v>125</v>
       </c>
       <c r="C162">
-        <v>1135</v>
+        <v>1055</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K162" s="1"/>
       <c r="L162" s="2"/>
@@ -5656,25 +5842,25 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>125</v>
+        <v>207</v>
       </c>
       <c r="B163">
-        <v>150</v>
+        <v>126</v>
       </c>
       <c r="C163">
-        <v>1109</v>
+        <v>1232</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K163" s="1"/>
       <c r="L163" s="2"/>
@@ -5683,25 +5869,25 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B164">
-        <v>152</v>
+        <v>128</v>
       </c>
       <c r="C164">
-        <v>1373</v>
+        <v>1092</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K164" s="1"/>
       <c r="L164" s="2"/>
@@ -5710,25 +5896,25 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>139</v>
+        <v>190</v>
       </c>
       <c r="B165">
-        <v>153</v>
+        <v>130</v>
       </c>
       <c r="C165">
-        <v>1288</v>
+        <v>1306</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E165" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K165" s="1"/>
       <c r="L165" s="2"/>
@@ -5737,25 +5923,25 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="B166">
-        <v>154</v>
+        <v>131</v>
       </c>
       <c r="C166">
-        <v>1215</v>
+        <v>1269</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K166" s="1"/>
       <c r="L166" s="2"/>
@@ -5763,403 +5949,377 @@
       <c r="N166" s="1"/>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A167" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B167" s="3">
-        <v>156</v>
-      </c>
-      <c r="C167" s="3">
-        <v>1197</v>
-      </c>
-      <c r="D167" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E167" s="4" t="s">
-        <v>226</v>
+      <c r="A167" t="s">
+        <v>33</v>
+      </c>
+      <c r="B167">
+        <v>132</v>
+      </c>
+      <c r="C167">
+        <v>1214</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E167" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H167" s="3"/>
-      <c r="I167" s="3"/>
-      <c r="K167" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K167" s="1"/>
       <c r="L167" s="2"/>
       <c r="M167" s="2"/>
-      <c r="N167" s="4"/>
+      <c r="N167" s="1"/>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A168" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B168" s="3">
-        <v>157</v>
-      </c>
-      <c r="C168" s="3">
-        <v>1155</v>
-      </c>
-      <c r="D168" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E168" s="4" t="s">
-        <v>226</v>
+      <c r="A168" t="s">
+        <v>209</v>
+      </c>
+      <c r="B168">
+        <v>134</v>
+      </c>
+      <c r="C168">
+        <v>1111</v>
+      </c>
+      <c r="D168" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E168" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H168" s="3"/>
-      <c r="I168" s="3"/>
-      <c r="K168" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K168" s="1"/>
       <c r="L168" s="2"/>
       <c r="M168" s="2"/>
-      <c r="N168" s="4"/>
+      <c r="N168" s="1"/>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A169" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B169" s="3">
-        <v>158</v>
-      </c>
-      <c r="C169" s="3">
-        <v>1088</v>
-      </c>
-      <c r="D169" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E169" s="4" t="s">
-        <v>226</v>
+      <c r="A169" t="s">
+        <v>126</v>
+      </c>
+      <c r="B169">
+        <v>135</v>
+      </c>
+      <c r="C169">
+        <v>1089</v>
+      </c>
+      <c r="D169" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E169" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H169" s="3"/>
-      <c r="I169" s="3"/>
-      <c r="K169" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K169" s="1"/>
       <c r="L169" s="2"/>
       <c r="M169" s="2"/>
-      <c r="N169" s="4"/>
+      <c r="N169" s="1"/>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A170" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B170" s="3">
-        <v>159</v>
-      </c>
-      <c r="C170" s="3">
-        <v>1312</v>
-      </c>
-      <c r="D170" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E170" s="4" t="s">
-        <v>226</v>
+      <c r="A170" t="s">
+        <v>109</v>
+      </c>
+      <c r="B170">
+        <v>136</v>
+      </c>
+      <c r="C170">
+        <v>1233</v>
+      </c>
+      <c r="D170" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E170" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H170" s="3"/>
-      <c r="I170" s="3"/>
-      <c r="K170" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K170" s="1"/>
       <c r="L170" s="2"/>
       <c r="M170" s="2"/>
-      <c r="N170" s="4"/>
+      <c r="N170" s="1"/>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A171" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B171" s="3">
-        <v>160</v>
-      </c>
-      <c r="C171" s="3">
-        <v>1212</v>
-      </c>
-      <c r="D171" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E171" s="4" t="s">
-        <v>226</v>
+      <c r="A171" t="s">
+        <v>134</v>
+      </c>
+      <c r="B171">
+        <v>137</v>
+      </c>
+      <c r="C171">
+        <v>1170</v>
+      </c>
+      <c r="D171" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E171" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H171" s="3"/>
-      <c r="I171" s="3"/>
-      <c r="K171" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K171" s="1"/>
       <c r="L171" s="2"/>
       <c r="M171" s="2"/>
-      <c r="N171" s="4"/>
+      <c r="N171" s="1"/>
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A172" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B172" s="3">
-        <v>161</v>
-      </c>
-      <c r="C172" s="3">
-        <v>1068</v>
-      </c>
-      <c r="D172" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E172" s="4" t="s">
-        <v>226</v>
+      <c r="A172" t="s">
+        <v>26</v>
+      </c>
+      <c r="B172">
+        <v>138</v>
+      </c>
+      <c r="C172">
+        <v>1252</v>
+      </c>
+      <c r="D172" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E172" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H172" s="3"/>
-      <c r="I172" s="3"/>
-      <c r="K172" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K172" s="1"/>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
-      <c r="N172" s="4"/>
+      <c r="N172" s="1"/>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B173" s="3">
-        <v>163</v>
-      </c>
-      <c r="C173" s="3">
-        <v>1148</v>
-      </c>
-      <c r="D173" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E173" s="4" t="s">
-        <v>226</v>
+      <c r="A173" t="s">
+        <v>95</v>
+      </c>
+      <c r="B173">
+        <v>144</v>
+      </c>
+      <c r="C173">
+        <v>1245</v>
+      </c>
+      <c r="D173" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E173" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H173" s="3"/>
-      <c r="I173" s="3"/>
-      <c r="K173" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K173" s="1"/>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
-      <c r="N173" s="4"/>
+      <c r="N173" s="1"/>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B174" s="3">
-        <v>164</v>
-      </c>
-      <c r="C174" s="3">
-        <v>1149</v>
-      </c>
-      <c r="D174" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E174" s="4" t="s">
-        <v>226</v>
+      <c r="A174" t="s">
+        <v>104</v>
+      </c>
+      <c r="B174">
+        <v>145</v>
+      </c>
+      <c r="C174">
+        <v>1291</v>
+      </c>
+      <c r="D174" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E174" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H174" s="3"/>
-      <c r="I174" s="3"/>
-      <c r="K174" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K174" s="1"/>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
-      <c r="N174" s="4"/>
+      <c r="N174" s="1"/>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B175" s="3">
-        <v>165</v>
-      </c>
-      <c r="C175" s="3">
-        <v>1168</v>
-      </c>
-      <c r="D175" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E175" s="4" t="s">
-        <v>226</v>
+      <c r="A175" t="s">
+        <v>71</v>
+      </c>
+      <c r="B175">
+        <v>148</v>
+      </c>
+      <c r="C175">
+        <v>1169</v>
+      </c>
+      <c r="D175" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E175" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H175" s="3"/>
-      <c r="I175" s="3"/>
-      <c r="K175" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K175" s="1"/>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
-      <c r="N175" s="4"/>
+      <c r="N175" s="1"/>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B176" s="3">
-        <v>166</v>
-      </c>
-      <c r="C176" s="3">
-        <v>1173</v>
-      </c>
-      <c r="D176" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E176" s="4" t="s">
-        <v>226</v>
+      <c r="A176" t="s">
+        <v>78</v>
+      </c>
+      <c r="B176">
+        <v>149</v>
+      </c>
+      <c r="C176">
+        <v>1135</v>
+      </c>
+      <c r="D176" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H176" s="3"/>
-      <c r="I176" s="3"/>
-      <c r="K176" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K176" s="1"/>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
-      <c r="N176" s="4"/>
+      <c r="N176" s="1"/>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A177" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B177" s="3">
-        <v>167</v>
-      </c>
-      <c r="C177" s="3">
-        <v>1210</v>
-      </c>
-      <c r="D177" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E177" s="4" t="s">
-        <v>226</v>
+      <c r="A177" t="s">
+        <v>124</v>
+      </c>
+      <c r="B177">
+        <v>150</v>
+      </c>
+      <c r="C177">
+        <v>1109</v>
+      </c>
+      <c r="D177" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E177" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H177" s="3"/>
-      <c r="I177" s="3"/>
-      <c r="K177" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K177" s="1"/>
       <c r="L177" s="2"/>
       <c r="M177" s="2"/>
-      <c r="N177" s="4"/>
+      <c r="N177" s="1"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B178" s="3">
-        <v>168</v>
-      </c>
-      <c r="C178" s="3">
-        <v>1110</v>
-      </c>
-      <c r="D178" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E178" s="4" t="s">
-        <v>226</v>
+      <c r="A178" t="s">
+        <v>3</v>
+      </c>
+      <c r="B178">
+        <v>152</v>
+      </c>
+      <c r="C178">
+        <v>1373</v>
+      </c>
+      <c r="D178" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E178" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H178" s="3"/>
-      <c r="I178" s="3"/>
-      <c r="K178" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K178" s="1"/>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
-      <c r="N178" s="4"/>
+      <c r="N178" s="1"/>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A179" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="B179" s="3">
-        <v>170</v>
-      </c>
-      <c r="C179" s="3">
-        <v>1209</v>
-      </c>
-      <c r="D179" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E179" s="4" t="s">
-        <v>226</v>
+      <c r="A179" t="s">
+        <v>138</v>
+      </c>
+      <c r="B179">
+        <v>153</v>
+      </c>
+      <c r="C179">
+        <v>1288</v>
+      </c>
+      <c r="D179" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E179" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H179" s="3"/>
-      <c r="I179" s="3"/>
-      <c r="K179" s="4"/>
+        <v>230</v>
+      </c>
+      <c r="K179" s="1"/>
       <c r="L179" s="2"/>
       <c r="M179" s="2"/>
-      <c r="N179" s="4"/>
+      <c r="N179" s="1"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A180" s="3" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B180" s="3">
-        <v>171</v>
+        <v>156</v>
       </c>
       <c r="C180" s="3">
-        <v>1208</v>
+        <v>1197</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H180" s="3"/>
       <c r="I180" s="3"/>
@@ -6170,25 +6330,25 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="B181" s="3">
-        <v>173</v>
+        <v>157</v>
       </c>
       <c r="C181" s="3">
-        <v>1174</v>
+        <v>1155</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H181" s="3"/>
       <c r="I181" s="3"/>
@@ -6198,275 +6358,287 @@
       <c r="N181" s="4"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A182" t="s">
-        <v>221</v>
-      </c>
-      <c r="B182">
-        <v>174</v>
-      </c>
-      <c r="C182">
-        <v>1230</v>
-      </c>
-      <c r="D182" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E182" s="1" t="s">
-        <v>226</v>
+      <c r="A182" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B182" s="3">
+        <v>159</v>
+      </c>
+      <c r="C182" s="3">
+        <v>1312</v>
+      </c>
+      <c r="D182" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E182" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K182" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H182" s="3"/>
+      <c r="I182" s="3"/>
+      <c r="K182" s="4"/>
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
-      <c r="N182" s="1"/>
+      <c r="N182" s="4"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A183" t="s">
-        <v>157</v>
-      </c>
-      <c r="B183">
-        <v>175</v>
-      </c>
-      <c r="C183">
-        <v>1152</v>
-      </c>
-      <c r="D183" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E183" s="1" t="s">
-        <v>226</v>
+      <c r="A183" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B183" s="3">
+        <v>163</v>
+      </c>
+      <c r="C183" s="3">
+        <v>1148</v>
+      </c>
+      <c r="D183" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E183" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K183" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H183" s="3"/>
+      <c r="I183" s="3"/>
+      <c r="K183" s="4"/>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
-      <c r="N183" s="1"/>
+      <c r="N183" s="4"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A184" t="s">
-        <v>91</v>
-      </c>
-      <c r="B184">
-        <v>177</v>
-      </c>
-      <c r="C184">
-        <v>1207</v>
-      </c>
-      <c r="D184" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E184" s="1" t="s">
-        <v>226</v>
+      <c r="A184" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B184" s="3">
+        <v>164</v>
+      </c>
+      <c r="C184" s="3">
+        <v>1149</v>
+      </c>
+      <c r="D184" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E184" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K184" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H184" s="3"/>
+      <c r="I184" s="3"/>
+      <c r="K184" s="4"/>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
-      <c r="N184" s="1"/>
+      <c r="N184" s="4"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A185" t="s">
-        <v>218</v>
-      </c>
-      <c r="B185">
-        <v>178</v>
-      </c>
-      <c r="C185">
-        <v>1175</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E185" s="1" t="s">
-        <v>226</v>
+      <c r="A185" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B185" s="3">
+        <v>165</v>
+      </c>
+      <c r="C185" s="3">
+        <v>1168</v>
+      </c>
+      <c r="D185" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E185" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K185" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H185" s="3"/>
+      <c r="I185" s="3"/>
+      <c r="K185" s="4"/>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
-      <c r="N185" s="1"/>
+      <c r="N185" s="4"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A186" t="s">
-        <v>73</v>
-      </c>
-      <c r="B186">
-        <v>1153</v>
-      </c>
-      <c r="C186">
-        <v>1153</v>
-      </c>
-      <c r="D186" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E186" s="1" t="s">
-        <v>226</v>
+      <c r="A186" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B186" s="3">
+        <v>166</v>
+      </c>
+      <c r="C186" s="3">
+        <v>1173</v>
+      </c>
+      <c r="D186" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E186" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K186" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H186" s="3"/>
+      <c r="I186" s="3"/>
+      <c r="K186" s="4"/>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
-      <c r="N186" s="1"/>
+      <c r="N186" s="4"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A187" t="s">
-        <v>174</v>
-      </c>
-      <c r="B187">
-        <v>1154</v>
-      </c>
-      <c r="C187">
-        <v>1154</v>
-      </c>
-      <c r="D187" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E187" s="1" t="s">
-        <v>226</v>
+      <c r="A187" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B187" s="3">
+        <v>167</v>
+      </c>
+      <c r="C187" s="3">
+        <v>1210</v>
+      </c>
+      <c r="D187" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E187" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K187" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H187" s="3"/>
+      <c r="I187" s="3"/>
+      <c r="K187" s="4"/>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
-      <c r="N187" s="1"/>
+      <c r="N187" s="4"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A188" t="s">
-        <v>147</v>
-      </c>
-      <c r="B188">
-        <v>1156</v>
-      </c>
-      <c r="C188">
-        <v>1156</v>
-      </c>
-      <c r="D188" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="E188" s="1" t="s">
-        <v>226</v>
+      <c r="A188" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B188" s="3">
+        <v>168</v>
+      </c>
+      <c r="C188" s="3">
+        <v>1110</v>
+      </c>
+      <c r="D188" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E188" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="K188" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H188" s="3"/>
+      <c r="I188" s="3"/>
+      <c r="K188" s="4"/>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
-      <c r="N188" s="1"/>
+      <c r="N188" s="4"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A189" t="s">
-        <v>163</v>
-      </c>
-      <c r="B189">
-        <v>1171</v>
-      </c>
-      <c r="C189">
-        <v>1171</v>
-      </c>
-      <c r="D189" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="E189" s="1" t="s">
-        <v>226</v>
+      <c r="A189" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B189" s="3">
+        <v>170</v>
+      </c>
+      <c r="C189" s="3">
+        <v>1209</v>
+      </c>
+      <c r="D189" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E189" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H189" t="s">
-        <v>241</v>
-      </c>
-      <c r="K189" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H189" s="3"/>
+      <c r="I189" s="3"/>
+      <c r="K189" s="4"/>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
-      <c r="N189" s="1"/>
+      <c r="N189" s="4"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A190" t="s">
-        <v>90</v>
-      </c>
-      <c r="B190">
-        <v>1176</v>
-      </c>
-      <c r="C190">
-        <v>1176</v>
-      </c>
-      <c r="D190" s="22" t="s">
-        <v>224</v>
-      </c>
-      <c r="E190" s="1" t="s">
-        <v>226</v>
+      <c r="A190" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B190" s="3">
+        <v>171</v>
+      </c>
+      <c r="C190" s="3">
+        <v>1208</v>
+      </c>
+      <c r="D190" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E190" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H190" t="s">
-        <v>241</v>
-      </c>
-      <c r="K190" s="1"/>
+        <v>230</v>
+      </c>
+      <c r="H190" s="3"/>
+      <c r="I190" s="3"/>
+      <c r="K190" s="4"/>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
-      <c r="N190" s="1"/>
+      <c r="N190" s="4"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>40</v>
+        <v>220</v>
       </c>
       <c r="B191">
-        <v>1177</v>
+        <v>174</v>
       </c>
       <c r="C191">
-        <v>1177</v>
+        <v>1230</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K191" s="1"/>
       <c r="L191" s="2"/>
@@ -6475,25 +6647,25 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>207</v>
+        <v>156</v>
       </c>
       <c r="B192">
-        <v>1179</v>
+        <v>175</v>
       </c>
       <c r="C192">
-        <v>1179</v>
+        <v>1152</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E192" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K192" s="1"/>
       <c r="L192" s="2"/>
@@ -6502,28 +6674,25 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>171</v>
+        <v>90</v>
       </c>
       <c r="B193">
-        <v>1190</v>
+        <v>177</v>
       </c>
       <c r="C193">
-        <v>1190</v>
-      </c>
-      <c r="D193" s="22" t="s">
-        <v>224</v>
+        <v>1207</v>
+      </c>
+      <c r="D193" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="E193" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H193" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="K193" s="1"/>
       <c r="L193" s="2"/>
@@ -6532,28 +6701,25 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="B194">
-        <v>1191</v>
+        <v>1153</v>
       </c>
       <c r="C194">
-        <v>1191</v>
-      </c>
-      <c r="D194" s="22" t="s">
-        <v>224</v>
+        <v>1153</v>
+      </c>
+      <c r="D194" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="E194" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H194" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="K194" s="1"/>
       <c r="L194" s="2"/>
@@ -6562,25 +6728,25 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>213</v>
+        <v>173</v>
       </c>
       <c r="B195">
-        <v>1193</v>
+        <v>1154</v>
       </c>
       <c r="C195">
-        <v>1193</v>
+        <v>1154</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K195" s="1"/>
       <c r="L195" s="2"/>
@@ -6589,25 +6755,25 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>179</v>
+        <v>146</v>
       </c>
       <c r="B196">
-        <v>1194</v>
+        <v>1156</v>
       </c>
       <c r="C196">
-        <v>1194</v>
+        <v>1156</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E196" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K196" s="1"/>
       <c r="L196" s="2"/>
@@ -6616,25 +6782,25 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
-        <v>109</v>
+        <v>39</v>
       </c>
       <c r="B197">
-        <v>1196</v>
+        <v>1177</v>
       </c>
       <c r="C197">
-        <v>1196</v>
+        <v>1177</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K197" s="1"/>
       <c r="L197" s="2"/>
@@ -6643,25 +6809,25 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>16</v>
+        <v>206</v>
       </c>
       <c r="B198">
-        <v>1213</v>
+        <v>1179</v>
       </c>
       <c r="C198">
-        <v>1213</v>
+        <v>1179</v>
       </c>
       <c r="D198" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E198" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K198" s="1"/>
       <c r="L198" s="2"/>
@@ -6670,25 +6836,25 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>181</v>
+        <v>212</v>
       </c>
       <c r="B199">
-        <v>1216</v>
+        <v>1193</v>
       </c>
       <c r="C199">
-        <v>1216</v>
+        <v>1193</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E199" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K199" s="1"/>
       <c r="L199" s="2"/>
@@ -6697,25 +6863,25 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>206</v>
+        <v>178</v>
       </c>
       <c r="B200">
-        <v>1219</v>
+        <v>1194</v>
       </c>
       <c r="C200">
-        <v>1219</v>
+        <v>1194</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E200" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K200" s="1"/>
       <c r="L200" s="2"/>
@@ -6724,25 +6890,25 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>178</v>
+        <v>108</v>
       </c>
       <c r="B201">
-        <v>1227</v>
+        <v>1196</v>
       </c>
       <c r="C201">
-        <v>1227</v>
+        <v>1196</v>
       </c>
       <c r="D201" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E201" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K201" s="1"/>
       <c r="L201" s="2"/>
@@ -6751,25 +6917,25 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>162</v>
+        <v>16</v>
       </c>
       <c r="B202">
-        <v>1236</v>
+        <v>1213</v>
       </c>
       <c r="C202">
-        <v>1236</v>
+        <v>1213</v>
       </c>
       <c r="D202" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E202" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K202" s="1"/>
       <c r="L202" s="2"/>
@@ -6778,25 +6944,25 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>154</v>
+        <v>180</v>
       </c>
       <c r="B203">
-        <v>1238</v>
+        <v>1216</v>
       </c>
       <c r="C203">
-        <v>1238</v>
+        <v>1216</v>
       </c>
       <c r="D203" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E203" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K203" s="1"/>
       <c r="L203" s="2"/>
@@ -6805,25 +6971,25 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>183</v>
+        <v>205</v>
       </c>
       <c r="B204">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="C204">
-        <v>1239</v>
+        <v>1219</v>
       </c>
       <c r="D204" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E204" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K204" s="1"/>
       <c r="L204" s="2"/>
@@ -6832,25 +6998,25 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>57</v>
+        <v>177</v>
       </c>
       <c r="B205">
-        <v>1248</v>
+        <v>1227</v>
       </c>
       <c r="C205">
-        <v>1248</v>
+        <v>1227</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E205" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K205" s="1"/>
       <c r="L205" s="2"/>
@@ -6859,25 +7025,25 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B206">
-        <v>1253</v>
+        <v>1236</v>
       </c>
       <c r="C206">
-        <v>1253</v>
+        <v>1236</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E206" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K206" s="1"/>
       <c r="L206" s="2"/>
@@ -6886,25 +7052,25 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>214</v>
+        <v>153</v>
       </c>
       <c r="B207">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="C207">
-        <v>1254</v>
+        <v>1238</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E207" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K207" s="1"/>
       <c r="L207" s="2"/>
@@ -6913,25 +7079,25 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>30</v>
+        <v>182</v>
       </c>
       <c r="B208">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="C208">
-        <v>1255</v>
+        <v>1239</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E208" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K208" s="1"/>
       <c r="L208" s="2"/>
@@ -6940,25 +7106,25 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="B209">
-        <v>1258</v>
+        <v>1248</v>
       </c>
       <c r="C209">
-        <v>1258</v>
+        <v>1248</v>
       </c>
       <c r="D209" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E209" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K209" s="1"/>
       <c r="L209" s="2"/>
@@ -6967,55 +7133,52 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>211</v>
+        <v>172</v>
       </c>
       <c r="B210">
-        <v>1273</v>
+        <v>1253</v>
       </c>
       <c r="C210">
-        <v>1273</v>
-      </c>
-      <c r="D210" s="20" t="s">
-        <v>224</v>
+        <v>1253</v>
+      </c>
+      <c r="D210" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="E210" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H210" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="K210" s="1"/>
       <c r="L210" s="2"/>
       <c r="M210" s="2"/>
-      <c r="N210" s="4"/>
+      <c r="N210" s="1"/>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="B211">
-        <v>1274</v>
+        <v>1255</v>
       </c>
       <c r="C211">
-        <v>1274</v>
+        <v>1255</v>
       </c>
       <c r="D211" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E211" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K211" s="1"/>
       <c r="L211" s="2"/>
@@ -7024,28 +7187,25 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>60</v>
+        <v>106</v>
       </c>
       <c r="B212">
-        <v>1276</v>
+        <v>1258</v>
       </c>
       <c r="C212">
-        <v>1276</v>
-      </c>
-      <c r="D212" s="21" t="s">
-        <v>223</v>
+        <v>1258</v>
+      </c>
+      <c r="D212" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="E212" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="H212" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="K212" s="1"/>
       <c r="L212" s="2"/>
@@ -7054,25 +7214,25 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>28</v>
+        <v>128</v>
       </c>
       <c r="B213">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="C213">
-        <v>1278</v>
+        <v>1274</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E213" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K213" s="1"/>
       <c r="L213" s="2"/>
@@ -7081,25 +7241,25 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A214" t="s">
-        <v>71</v>
+        <v>28</v>
       </c>
       <c r="B214">
-        <v>1290</v>
+        <v>1278</v>
       </c>
       <c r="C214">
-        <v>1290</v>
+        <v>1278</v>
       </c>
       <c r="D214" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E214" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K214" s="1"/>
       <c r="L214" s="2"/>
@@ -7108,25 +7268,25 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>137</v>
+        <v>70</v>
       </c>
       <c r="B215">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="C215">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E215" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K215" s="1"/>
       <c r="L215" s="2"/>
@@ -7135,25 +7295,25 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>78</v>
+        <v>136</v>
       </c>
       <c r="B216">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="C216">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="D216" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E216" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K216" s="1"/>
       <c r="L216" s="2"/>
@@ -7162,7 +7322,7 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B217">
         <v>1298</v>
@@ -7171,16 +7331,16 @@
         <v>1298</v>
       </c>
       <c r="D217" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E217" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K217" s="1"/>
       <c r="L217" s="2"/>
@@ -7189,7 +7349,7 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B218">
         <v>1311</v>
@@ -7198,16 +7358,16 @@
         <v>1311</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E218" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K218" s="1"/>
       <c r="L218" s="2"/>
@@ -7216,7 +7376,7 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B219">
         <v>1326</v>
@@ -7225,16 +7385,16 @@
         <v>1326</v>
       </c>
       <c r="D219" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E219" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K219" s="1"/>
       <c r="L219" s="2"/>
@@ -7243,7 +7403,7 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B220">
         <v>1332</v>
@@ -7252,16 +7412,16 @@
         <v>1332</v>
       </c>
       <c r="D220" s="1" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E220" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="K220" s="1"/>
       <c r="L220" s="2"/>
@@ -7270,7 +7430,7 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B221">
         <v>1246</v>
@@ -7279,19 +7439,19 @@
         <v>1246</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="E221" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H221" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="K221" s="1"/>
       <c r="L221" s="2"/>
@@ -7300,9 +7460,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P223">
-    <sortCondition descending="1" ref="E2:E223"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N221">
+    <sortCondition descending="1" ref="E2:E221"/>
   </sortState>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/src/gcover/data/GC_Sources_PA.xlsx
+++ b/src/gcover/data/GC_Sources_PA.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\v0t0020a.adr.admin.ch\lg\01_PRODUKTION\GIS\TOPGIS\Produktableitung\R17_2026\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70CE66F6-C326-456E-AD2A-421E09061623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549AA853-4802-4A2E-86CF-6419B054669F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1164" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="250">
   <si>
     <t>MSH_MAP_TITLE</t>
   </si>
@@ -823,6 +823,15 @@
   </si>
   <si>
     <t>R17</t>
+  </si>
+  <si>
+    <t>Correction DAS suite à Rückmeldung client</t>
+  </si>
+  <si>
+    <t>R15</t>
+  </si>
+  <si>
+    <t>sans points</t>
   </si>
 </sst>
 </file>
@@ -860,7 +869,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -876,12 +885,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -909,6 +912,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -922,7 +937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -951,47 +966,57 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1288,31 +1313,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="D1" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="14" t="s">
         <v>227</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="G1" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="H1" s="14" t="s">
         <v>244</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="I1" s="14" t="s">
         <v>243</v>
       </c>
       <c r="J1" s="1"/>
@@ -1323,25 +1348,31 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>120</v>
+        <v>36</v>
       </c>
       <c r="B2" s="5">
-        <v>1</v>
+        <v>1329</v>
       </c>
       <c r="C2" s="5">
-        <v>1086</v>
+        <v>1329</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>226</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
+      </c>
+      <c r="H2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I2" t="s">
+        <v>248</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
@@ -1350,13 +1381,13 @@
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>150</v>
+        <v>194</v>
       </c>
       <c r="B3" s="5">
-        <v>2</v>
+        <v>180</v>
       </c>
       <c r="C3" s="5">
-        <v>1162</v>
+        <v>1195</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>223</v>
@@ -1368,7 +1399,10 @@
         <v>229</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
+      </c>
+      <c r="I3" t="s">
+        <v>248</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="2"/>
@@ -1376,17 +1410,17 @@
       <c r="N3" s="1"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="B4" s="5">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5">
-        <v>1087</v>
+      <c r="A4" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="B4" s="8">
+        <v>179</v>
+      </c>
+      <c r="C4" s="8">
+        <v>1051</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="E4" s="6" t="s">
         <v>226</v>
@@ -1395,7 +1429,11 @@
         <v>229</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" t="s">
+        <v>248</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="2"/>
@@ -1403,16 +1441,16 @@
       <c r="N4" s="1"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="5">
-        <v>5</v>
-      </c>
-      <c r="C5" s="5">
-        <v>1222</v>
-      </c>
-      <c r="D5" s="6" t="s">
+      <c r="A5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="8">
+        <v>172</v>
+      </c>
+      <c r="C5" s="8">
+        <v>1143</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>223</v>
       </c>
       <c r="E5" s="6" t="s">
@@ -1423,26 +1461,30 @@
       </c>
       <c r="G5" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" t="s">
+        <v>248</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="1"/>
+      <c r="N5" s="4"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="5">
-        <v>12</v>
-      </c>
-      <c r="C6" s="5">
-        <v>1300</v>
-      </c>
-      <c r="D6" s="6" t="s">
+      <c r="A6" s="8" t="s">
+        <v>154</v>
+      </c>
+      <c r="B6" s="8">
+        <v>162</v>
+      </c>
+      <c r="C6" s="8">
+        <v>1163</v>
+      </c>
+      <c r="D6" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="9" t="s">
         <v>226</v>
       </c>
       <c r="F6" s="7" t="s">
@@ -1451,20 +1493,24 @@
       <c r="G6" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="H6" s="3"/>
+      <c r="I6" t="s">
+        <v>248</v>
+      </c>
+      <c r="K6" s="4"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="1"/>
+      <c r="N6" s="4"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="B7" s="5">
-        <v>15</v>
+        <v>155</v>
       </c>
       <c r="C7" s="5">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>223</v>
@@ -1477,6 +1523,9 @@
       </c>
       <c r="G7" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I7" t="s">
+        <v>248</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="2"/>
@@ -1485,13 +1534,13 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
-        <v>200</v>
+        <v>96</v>
       </c>
       <c r="B8" s="5">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="C8" s="5">
-        <v>1221</v>
+        <v>1105</v>
       </c>
       <c r="D8" s="6" t="s">
         <v>223</v>
@@ -1504,6 +1553,9 @@
       </c>
       <c r="G8" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I8" t="s">
+        <v>248</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="2"/>
@@ -1512,13 +1564,13 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="B9" s="5">
-        <v>25</v>
+        <v>143</v>
       </c>
       <c r="C9" s="5">
-        <v>1241</v>
+        <v>1226</v>
       </c>
       <c r="D9" s="6" t="s">
         <v>223</v>
@@ -1531,6 +1583,9 @@
       </c>
       <c r="G9" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I9" t="s">
+        <v>248</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="2"/>
@@ -1539,13 +1594,13 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>160</v>
+        <v>201</v>
       </c>
       <c r="B10" s="5">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="C10" s="5">
-        <v>1186</v>
+        <v>1107</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>223</v>
@@ -1558,6 +1613,9 @@
       </c>
       <c r="G10" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I10" t="s">
+        <v>248</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="2"/>
@@ -1566,13 +1624,13 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
-        <v>7</v>
+        <v>111</v>
       </c>
       <c r="B11" s="5">
-        <v>27</v>
+        <v>123</v>
       </c>
       <c r="C11" s="5">
-        <v>1223</v>
+        <v>1184</v>
       </c>
       <c r="D11" s="6" t="s">
         <v>223</v>
@@ -1585,6 +1643,9 @@
       </c>
       <c r="G11" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I11" t="s">
+        <v>248</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="2"/>
@@ -1593,13 +1654,13 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
-        <v>4</v>
+        <v>110</v>
       </c>
       <c r="B12" s="5">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="C12" s="5">
-        <v>1206</v>
+        <v>1261</v>
       </c>
       <c r="D12" s="6" t="s">
         <v>223</v>
@@ -1608,10 +1669,13 @@
         <v>226</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G12" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I12" t="s">
+        <v>248</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="2"/>
@@ -1620,13 +1684,13 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
-        <v>38</v>
+        <v>149</v>
       </c>
       <c r="B13" s="5">
-        <v>40</v>
+        <v>114</v>
       </c>
       <c r="C13" s="5">
-        <v>1085</v>
+        <v>1183</v>
       </c>
       <c r="D13" s="6" t="s">
         <v>223</v>
@@ -1635,10 +1699,13 @@
         <v>226</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G13" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I13" t="s">
+        <v>248</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="2"/>
@@ -1647,13 +1714,13 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="B14" s="5">
         <v>105</v>
       </c>
-      <c r="B14" s="5">
-        <v>42</v>
-      </c>
       <c r="C14" s="5">
-        <v>1202</v>
+        <v>1205</v>
       </c>
       <c r="D14" s="6" t="s">
         <v>223</v>
@@ -1666,6 +1733,9 @@
       </c>
       <c r="G14" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I14" t="s">
+        <v>248</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="2"/>
@@ -1674,13 +1744,13 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
-        <v>198</v>
+        <v>115</v>
       </c>
       <c r="B15" s="5">
-        <v>46</v>
+        <v>99</v>
       </c>
       <c r="C15" s="5">
-        <v>1281</v>
+        <v>1204</v>
       </c>
       <c r="D15" s="6" t="s">
         <v>223</v>
@@ -1693,6 +1763,9 @@
       </c>
       <c r="G15" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I15" t="s">
+        <v>248</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="2"/>
@@ -1701,13 +1774,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
-        <v>145</v>
+        <v>99</v>
       </c>
       <c r="B16" s="5">
-        <v>48</v>
+        <v>98</v>
       </c>
       <c r="C16" s="5">
-        <v>1301</v>
+        <v>1185</v>
       </c>
       <c r="D16" s="6" t="s">
         <v>223</v>
@@ -1720,6 +1793,9 @@
       </c>
       <c r="G16" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I16" t="s">
+        <v>248</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="2"/>
@@ -1728,13 +1804,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="B17" s="5">
-        <v>49</v>
+        <v>96</v>
       </c>
       <c r="C17" s="5">
-        <v>1066</v>
+        <v>1106</v>
       </c>
       <c r="D17" s="6" t="s">
         <v>223</v>
@@ -1747,6 +1823,9 @@
       </c>
       <c r="G17" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I17" t="s">
+        <v>248</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="2"/>
@@ -1755,13 +1834,13 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>24</v>
+        <v>148</v>
       </c>
       <c r="B18" s="5">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="C18" s="5">
-        <v>1144</v>
+        <v>1182</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>223</v>
@@ -1774,6 +1853,9 @@
       </c>
       <c r="G18" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I18" t="s">
+        <v>248</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="2"/>
@@ -1782,13 +1864,13 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
-        <v>91</v>
+        <v>176</v>
       </c>
       <c r="B19" s="5">
-        <v>55</v>
+        <v>94</v>
       </c>
       <c r="C19" s="5">
-        <v>1065</v>
+        <v>1203</v>
       </c>
       <c r="D19" s="6" t="s">
         <v>223</v>
@@ -1801,6 +1883,9 @@
       </c>
       <c r="G19" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I19" t="s">
+        <v>248</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="2"/>
@@ -1809,13 +1894,13 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
-        <v>144</v>
+        <v>107</v>
       </c>
       <c r="B20" s="5">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C20" s="5">
-        <v>1047</v>
+        <v>1285</v>
       </c>
       <c r="D20" s="6" t="s">
         <v>223</v>
@@ -1828,6 +1913,9 @@
       </c>
       <c r="G20" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I20" t="s">
+        <v>248</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="2"/>
@@ -1836,13 +1924,13 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
-        <v>192</v>
+        <v>157</v>
       </c>
       <c r="B21" s="5">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="C21" s="5">
-        <v>1145</v>
+        <v>1243</v>
       </c>
       <c r="D21" s="6" t="s">
         <v>223</v>
@@ -1855,6 +1943,9 @@
       </c>
       <c r="G21" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I21" t="s">
+        <v>248</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="2"/>
@@ -1863,13 +1954,13 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
-        <v>140</v>
+        <v>25</v>
       </c>
       <c r="B22" s="5">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C22" s="5">
-        <v>1242</v>
+        <v>1067</v>
       </c>
       <c r="D22" s="6" t="s">
         <v>223</v>
@@ -1882,6 +1973,9 @@
       </c>
       <c r="G22" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I22" t="s">
+        <v>248</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="2"/>
@@ -1890,13 +1984,13 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="B23" s="5">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="C23" s="5">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>223</v>
@@ -1909,6 +2003,9 @@
       </c>
       <c r="G23" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I23" t="s">
+        <v>248</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="2"/>
@@ -1917,13 +2014,13 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="B24" s="5">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C24" s="5">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>223</v>
@@ -1936,6 +2033,9 @@
       </c>
       <c r="G24" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I24" t="s">
+        <v>248</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="2"/>
@@ -1944,13 +2044,13 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
-        <v>25</v>
+        <v>140</v>
       </c>
       <c r="B25" s="5">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="C25" s="5">
-        <v>1067</v>
+        <v>1242</v>
       </c>
       <c r="D25" s="6" t="s">
         <v>223</v>
@@ -1963,6 +2063,9 @@
       </c>
       <c r="G25" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I25" t="s">
+        <v>248</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="2"/>
@@ -1971,13 +2074,13 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="B26" s="5">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="C26" s="5">
-        <v>1243</v>
+        <v>1145</v>
       </c>
       <c r="D26" s="6" t="s">
         <v>223</v>
@@ -1990,6 +2093,9 @@
       </c>
       <c r="G26" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I26" t="s">
+        <v>248</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="2"/>
@@ -1998,13 +2104,13 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
-        <v>107</v>
+        <v>144</v>
       </c>
       <c r="B27" s="5">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C27" s="5">
-        <v>1285</v>
+        <v>1047</v>
       </c>
       <c r="D27" s="6" t="s">
         <v>223</v>
@@ -2017,6 +2123,9 @@
       </c>
       <c r="G27" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I27" t="s">
+        <v>248</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="2"/>
@@ -2025,13 +2134,13 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
-        <v>176</v>
+        <v>91</v>
       </c>
       <c r="B28" s="5">
-        <v>94</v>
+        <v>55</v>
       </c>
       <c r="C28" s="5">
-        <v>1203</v>
+        <v>1065</v>
       </c>
       <c r="D28" s="6" t="s">
         <v>223</v>
@@ -2044,6 +2153,9 @@
       </c>
       <c r="G28" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I28" t="s">
+        <v>248</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="2"/>
@@ -2052,13 +2164,13 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
-        <v>148</v>
+        <v>24</v>
       </c>
       <c r="B29" s="5">
-        <v>95</v>
+        <v>51</v>
       </c>
       <c r="C29" s="5">
-        <v>1182</v>
+        <v>1144</v>
       </c>
       <c r="D29" s="6" t="s">
         <v>223</v>
@@ -2071,6 +2183,9 @@
       </c>
       <c r="G29" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I29" t="s">
+        <v>248</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="2"/>
@@ -2079,13 +2194,13 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="B30" s="5">
-        <v>96</v>
+        <v>49</v>
       </c>
       <c r="C30" s="5">
-        <v>1106</v>
+        <v>1066</v>
       </c>
       <c r="D30" s="6" t="s">
         <v>223</v>
@@ -2098,6 +2213,9 @@
       </c>
       <c r="G30" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I30" t="s">
+        <v>248</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="2"/>
@@ -2106,13 +2224,13 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
-        <v>99</v>
+        <v>145</v>
       </c>
       <c r="B31" s="5">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="C31" s="5">
-        <v>1185</v>
+        <v>1301</v>
       </c>
       <c r="D31" s="6" t="s">
         <v>223</v>
@@ -2125,6 +2243,9 @@
       </c>
       <c r="G31" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I31" t="s">
+        <v>248</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="2"/>
@@ -2133,13 +2254,13 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>115</v>
+        <v>198</v>
       </c>
       <c r="B32" s="5">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="C32" s="5">
-        <v>1204</v>
+        <v>1281</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>223</v>
@@ -2152,6 +2273,9 @@
       </c>
       <c r="G32" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I32" t="s">
+        <v>248</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="2"/>
@@ -2160,13 +2284,13 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
-        <v>185</v>
+        <v>105</v>
       </c>
       <c r="B33" s="5">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="C33" s="5">
-        <v>1205</v>
+        <v>1202</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>223</v>
@@ -2179,6 +2303,9 @@
       </c>
       <c r="G33" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I33" t="s">
+        <v>248</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="2"/>
@@ -2187,13 +2314,13 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
-        <v>149</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5">
-        <v>114</v>
+        <v>40</v>
       </c>
       <c r="C34" s="5">
-        <v>1183</v>
+        <v>1085</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>223</v>
@@ -2202,10 +2329,13 @@
         <v>226</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G34" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I34" t="s">
+        <v>248</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="2"/>
@@ -2214,13 +2344,13 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="B35" s="5">
-        <v>117</v>
+        <v>36</v>
       </c>
       <c r="C35" s="5">
-        <v>1261</v>
+        <v>1206</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>223</v>
@@ -2229,10 +2359,13 @@
         <v>226</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G35" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I35" t="s">
+        <v>248</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="2"/>
@@ -2241,13 +2374,13 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
-        <v>111</v>
+        <v>7</v>
       </c>
       <c r="B36" s="5">
-        <v>123</v>
+        <v>27</v>
       </c>
       <c r="C36" s="5">
-        <v>1184</v>
+        <v>1223</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>223</v>
@@ -2260,6 +2393,9 @@
       </c>
       <c r="G36" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I36" t="s">
+        <v>248</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="2"/>
@@ -2268,13 +2404,13 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>201</v>
+        <v>160</v>
       </c>
       <c r="B37" s="5">
-        <v>139</v>
+        <v>26</v>
       </c>
       <c r="C37" s="5">
-        <v>1107</v>
+        <v>1186</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>223</v>
@@ -2287,6 +2423,9 @@
       </c>
       <c r="G37" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I37" t="s">
+        <v>248</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="2"/>
@@ -2295,13 +2434,13 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="B38" s="5">
-        <v>143</v>
+        <v>25</v>
       </c>
       <c r="C38" s="5">
-        <v>1226</v>
+        <v>1241</v>
       </c>
       <c r="D38" s="6" t="s">
         <v>223</v>
@@ -2314,6 +2453,9 @@
       </c>
       <c r="G38" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I38" t="s">
+        <v>248</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="2"/>
@@ -2322,13 +2464,13 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
-        <v>96</v>
+        <v>200</v>
       </c>
       <c r="B39" s="5">
-        <v>147</v>
+        <v>17</v>
       </c>
       <c r="C39" s="5">
-        <v>1105</v>
+        <v>1221</v>
       </c>
       <c r="D39" s="6" t="s">
         <v>223</v>
@@ -2341,6 +2483,9 @@
       </c>
       <c r="G39" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I39" t="s">
+        <v>248</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="2"/>
@@ -2349,13 +2494,13 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="B40" s="5">
-        <v>155</v>
+        <v>15</v>
       </c>
       <c r="C40" s="5">
-        <v>1125</v>
+        <v>1124</v>
       </c>
       <c r="D40" s="6" t="s">
         <v>223</v>
@@ -2368,6 +2513,9 @@
       </c>
       <c r="G40" s="7" t="s">
         <v>229</v>
+      </c>
+      <c r="I40" t="s">
+        <v>248</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="2"/>
@@ -2375,19 +2523,19 @@
       <c r="N40" s="1"/>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A41" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="8">
-        <v>162</v>
-      </c>
-      <c r="C41" s="8">
-        <v>1163</v>
-      </c>
-      <c r="D41" s="9" t="s">
+      <c r="A41" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B41" s="5">
+        <v>12</v>
+      </c>
+      <c r="C41" s="5">
+        <v>1300</v>
+      </c>
+      <c r="D41" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E41" s="9" t="s">
+      <c r="E41" s="6" t="s">
         <v>226</v>
       </c>
       <c r="F41" s="7" t="s">
@@ -2396,24 +2544,25 @@
       <c r="G41" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-      <c r="K41" s="4"/>
+      <c r="I41" t="s">
+        <v>248</v>
+      </c>
+      <c r="K41" s="1"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
-      <c r="N41" s="4"/>
+      <c r="N41" s="1"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A42" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="B42" s="8">
-        <v>172</v>
-      </c>
-      <c r="C42" s="8">
-        <v>1143</v>
-      </c>
-      <c r="D42" s="9" t="s">
+      <c r="A42" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="B42" s="5">
+        <v>5</v>
+      </c>
+      <c r="C42" s="5">
+        <v>1222</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>223</v>
       </c>
       <c r="E42" s="6" t="s">
@@ -2425,22 +2574,23 @@
       <c r="G42" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
+      <c r="I42" t="s">
+        <v>248</v>
+      </c>
       <c r="K42" s="1"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
-      <c r="N42" s="4"/>
+      <c r="N42" s="1"/>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>194</v>
+        <v>164</v>
       </c>
       <c r="B43" s="5">
-        <v>180</v>
+        <v>3</v>
       </c>
       <c r="C43" s="5">
-        <v>1195</v>
+        <v>1087</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>223</v>
@@ -2452,7 +2602,10 @@
         <v>229</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
+      </c>
+      <c r="I43" t="s">
+        <v>248</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="2"/>
@@ -2460,17 +2613,17 @@
       <c r="N43" s="1"/>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A44" s="8" t="s">
-        <v>129</v>
-      </c>
-      <c r="B44" s="8">
-        <v>179</v>
-      </c>
-      <c r="C44" s="8">
-        <v>1051</v>
+      <c r="A44" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B44" s="5">
+        <v>2</v>
+      </c>
+      <c r="C44" s="5">
+        <v>1162</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="E44" s="6" t="s">
         <v>226</v>
@@ -2479,10 +2632,11 @@
         <v>229</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
+        <v>229</v>
+      </c>
+      <c r="I44" t="s">
+        <v>248</v>
+      </c>
       <c r="K44" s="1"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
@@ -2490,28 +2644,28 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="B45" s="5">
-        <v>1329</v>
+        <v>1</v>
       </c>
       <c r="C45" s="5">
-        <v>1329</v>
+        <v>1086</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="E45" s="6" t="s">
         <v>226</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>230</v>
-      </c>
-      <c r="H45" t="s">
-        <v>238</v>
+        <v>229</v>
+      </c>
+      <c r="I45" t="s">
+        <v>248</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="2"/>
@@ -2519,27 +2673,28 @@
       <c r="N45" s="1"/>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A46" s="12" t="s">
-        <v>179</v>
-      </c>
-      <c r="B46" s="12">
-        <v>58</v>
-      </c>
-      <c r="C46" s="12">
-        <v>1305</v>
-      </c>
-      <c r="D46" s="13" t="s">
+      <c r="A46" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B46" s="8">
+        <v>1084</v>
+      </c>
+      <c r="C46" s="8">
+        <v>1084</v>
+      </c>
+      <c r="D46" s="9" t="s">
         <v>223</v>
       </c>
-      <c r="E46" s="13" t="s">
+      <c r="E46" s="9" t="s">
         <v>226</v>
       </c>
-      <c r="F46" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G46" s="14" t="s">
-        <v>229</v>
-      </c>
+      <c r="F46" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="H46" s="3"/>
       <c r="I46" t="s">
         <v>245</v>
       </c>
@@ -2549,208 +2704,207 @@
       <c r="N46" s="1"/>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A47" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B47" s="12">
-        <v>110</v>
-      </c>
-      <c r="C47" s="12">
-        <v>1069</v>
-      </c>
-      <c r="D47" s="13" t="s">
+      <c r="A47" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="B47" s="5">
+        <v>151</v>
+      </c>
+      <c r="C47" s="5">
+        <v>1071</v>
+      </c>
+      <c r="D47" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E47" s="13" t="s">
+      <c r="E47" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F47" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G47" s="14" t="s">
+      <c r="F47" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G47" s="7" t="s">
         <v>229</v>
       </c>
       <c r="I47" t="s">
         <v>245</v>
       </c>
-      <c r="K47" s="1"/>
+      <c r="K47" s="4"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="1"/>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A48" s="12" t="s">
-        <v>141</v>
-      </c>
-      <c r="B48" s="12">
-        <v>115</v>
-      </c>
-      <c r="C48" s="12">
-        <v>1225</v>
-      </c>
-      <c r="D48" s="13" t="s">
+      <c r="A48" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="B48" s="5">
+        <v>142</v>
+      </c>
+      <c r="C48" s="5">
+        <v>1113</v>
+      </c>
+      <c r="D48" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E48" s="13" t="s">
+      <c r="E48" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F48" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G48" s="14" t="s">
+      <c r="F48" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G48" s="7" t="s">
         <v>229</v>
       </c>
       <c r="I48" t="s">
         <v>245</v>
       </c>
-      <c r="K48" s="4"/>
+      <c r="K48" s="1"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="1"/>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A49" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B49" s="12">
-        <v>140</v>
-      </c>
-      <c r="C49" s="12">
-        <v>1072</v>
-      </c>
-      <c r="D49" s="13" t="s">
+      <c r="A49" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="B49" s="5">
+        <v>141</v>
+      </c>
+      <c r="C49" s="5">
+        <v>1114</v>
+      </c>
+      <c r="D49" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E49" s="13" t="s">
+      <c r="E49" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F49" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G49" s="14" t="s">
+      <c r="F49" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G49" s="7" t="s">
         <v>229</v>
       </c>
       <c r="I49" t="s">
         <v>245</v>
       </c>
-      <c r="K49" s="4"/>
+      <c r="K49" s="1"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="1"/>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A50" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B50" s="12">
-        <v>141</v>
-      </c>
-      <c r="C50" s="12">
-        <v>1114</v>
-      </c>
-      <c r="D50" s="13" t="s">
+      <c r="A50" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" s="5">
+        <v>140</v>
+      </c>
+      <c r="C50" s="5">
+        <v>1072</v>
+      </c>
+      <c r="D50" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E50" s="13" t="s">
+      <c r="E50" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F50" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G50" s="14" t="s">
+      <c r="F50" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G50" s="7" t="s">
         <v>229</v>
       </c>
       <c r="I50" t="s">
         <v>245</v>
       </c>
-      <c r="K50" s="1"/>
+      <c r="K50" s="4"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="1"/>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A51" s="12" t="s">
-        <v>208</v>
-      </c>
-      <c r="B51" s="12">
-        <v>142</v>
-      </c>
-      <c r="C51" s="12">
-        <v>1113</v>
-      </c>
-      <c r="D51" s="13" t="s">
+      <c r="A51" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="B51" s="5">
+        <v>115</v>
+      </c>
+      <c r="C51" s="5">
+        <v>1225</v>
+      </c>
+      <c r="D51" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E51" s="13" t="s">
+      <c r="E51" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F51" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G51" s="14" t="s">
+      <c r="F51" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G51" s="7" t="s">
         <v>229</v>
       </c>
       <c r="I51" t="s">
         <v>245</v>
       </c>
-      <c r="K51" s="1"/>
+      <c r="K51" s="4"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="1"/>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A52" s="12" t="s">
-        <v>125</v>
-      </c>
-      <c r="B52" s="12">
-        <v>151</v>
-      </c>
-      <c r="C52" s="12">
-        <v>1071</v>
-      </c>
-      <c r="D52" s="13" t="s">
+      <c r="A52" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B52" s="5">
+        <v>110</v>
+      </c>
+      <c r="C52" s="5">
+        <v>1069</v>
+      </c>
+      <c r="D52" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E52" s="13" t="s">
+      <c r="E52" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F52" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="G52" s="14" t="s">
+      <c r="F52" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G52" s="7" t="s">
         <v>229</v>
       </c>
       <c r="I52" t="s">
         <v>245</v>
       </c>
-      <c r="K52" s="4"/>
+      <c r="K52" s="1"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="1"/>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A53" s="15" t="s">
-        <v>22</v>
-      </c>
-      <c r="B53" s="15">
-        <v>1084</v>
-      </c>
-      <c r="C53" s="15">
-        <v>1084</v>
-      </c>
-      <c r="D53" s="16" t="s">
+      <c r="A53" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="B53" s="5">
+        <v>58</v>
+      </c>
+      <c r="C53" s="5">
+        <v>1305</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="6" t="s">
         <v>226</v>
       </c>
-      <c r="F53" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="G53" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="H53" s="3"/>
+      <c r="F53" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="G53" s="7" t="s">
+        <v>229</v>
+      </c>
       <c r="I53" t="s">
         <v>245</v>
       </c>
@@ -2760,25 +2914,25 @@
       <c r="N53" s="1"/>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="B54" s="26">
-        <v>1189</v>
-      </c>
-      <c r="C54" s="26">
-        <v>1189</v>
-      </c>
-      <c r="D54" s="23" t="s">
+      <c r="A54" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="B54" s="20">
+        <v>1294</v>
+      </c>
+      <c r="C54" s="20">
+        <v>1294</v>
+      </c>
+      <c r="D54" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E54" s="21" t="s">
+      <c r="E54" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="F54" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G54" s="28" t="s">
+      <c r="F54" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G54" s="22" t="s">
         <v>230</v>
       </c>
       <c r="H54" t="s">
@@ -2786,36 +2940,39 @@
       </c>
       <c r="I54" t="s">
         <v>246</v>
+      </c>
+      <c r="J54" t="s">
+        <v>249</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
-      <c r="N54" s="4"/>
+      <c r="N54" s="1"/>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="26" t="s">
-        <v>127</v>
-      </c>
-      <c r="B55" s="26">
-        <v>14</v>
-      </c>
-      <c r="C55" s="26">
-        <v>1198</v>
-      </c>
-      <c r="D55" s="20" t="s">
-        <v>223</v>
-      </c>
-      <c r="E55" s="21" t="s">
+      <c r="A55" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55" s="27">
+        <v>1276</v>
+      </c>
+      <c r="C55" s="27">
+        <v>1276</v>
+      </c>
+      <c r="D55" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="E55" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="F55" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G55" s="28" t="s">
+      <c r="F55" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="G55" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H55" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="I55" t="s">
         <v>246</v>
@@ -2826,25 +2983,25 @@
       <c r="N55" s="1"/>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="26" t="s">
-        <v>162</v>
-      </c>
-      <c r="B56" s="26">
-        <v>1171</v>
-      </c>
-      <c r="C56" s="26">
-        <v>1171</v>
-      </c>
-      <c r="D56" s="24" t="s">
+      <c r="A56" s="27" t="s">
+        <v>210</v>
+      </c>
+      <c r="B56" s="27">
+        <v>1273</v>
+      </c>
+      <c r="C56" s="27">
+        <v>1273</v>
+      </c>
+      <c r="D56" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="E56" s="21" t="s">
+      <c r="E56" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="F56" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G56" s="28" t="s">
+      <c r="F56" s="30" t="s">
+        <v>230</v>
+      </c>
+      <c r="G56" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H56" t="s">
@@ -2856,28 +3013,28 @@
       <c r="K56" s="1"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
-      <c r="N56" s="1"/>
+      <c r="N56" s="4"/>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="26" t="s">
-        <v>89</v>
-      </c>
-      <c r="B57" s="26">
-        <v>1176</v>
-      </c>
-      <c r="C57" s="26">
-        <v>1176</v>
-      </c>
-      <c r="D57" s="24" t="s">
+      <c r="A57" s="20" t="s">
+        <v>213</v>
+      </c>
+      <c r="B57" s="20">
+        <v>1254</v>
+      </c>
+      <c r="C57" s="20">
+        <v>1254</v>
+      </c>
+      <c r="D57" s="16" t="s">
         <v>223</v>
       </c>
-      <c r="E57" s="21" t="s">
+      <c r="E57" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G57" s="28" t="s">
+      <c r="F57" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G57" s="22" t="s">
         <v>230</v>
       </c>
       <c r="H57" t="s">
@@ -2885,6 +3042,9 @@
       </c>
       <c r="I57" t="s">
         <v>246</v>
+      </c>
+      <c r="J57" t="s">
+        <v>249</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="2"/>
@@ -2892,25 +3052,25 @@
       <c r="N57" s="1"/>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="B58" s="26">
-        <v>1190</v>
-      </c>
-      <c r="C58" s="26">
-        <v>1190</v>
-      </c>
-      <c r="D58" s="20" t="s">
+      <c r="A58" s="20" t="s">
+        <v>10</v>
+      </c>
+      <c r="B58" s="20">
+        <v>1191</v>
+      </c>
+      <c r="C58" s="20">
+        <v>1191</v>
+      </c>
+      <c r="D58" s="15" t="s">
         <v>223</v>
       </c>
-      <c r="E58" s="21" t="s">
+      <c r="E58" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="F58" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G58" s="28" t="s">
+      <c r="F58" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G58" s="22" t="s">
         <v>230</v>
       </c>
       <c r="H58" t="s">
@@ -2918,6 +3078,9 @@
       </c>
       <c r="I58" t="s">
         <v>246</v>
+      </c>
+      <c r="J58" t="s">
+        <v>249</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="2"/>
@@ -2925,25 +3088,25 @@
       <c r="N58" s="1"/>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B59" s="26">
-        <v>1191</v>
-      </c>
-      <c r="C59" s="26">
-        <v>1191</v>
-      </c>
-      <c r="D59" s="20" t="s">
+      <c r="A59" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="B59" s="20">
+        <v>1189</v>
+      </c>
+      <c r="C59" s="20">
+        <v>1189</v>
+      </c>
+      <c r="D59" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="E59" s="21" t="s">
+      <c r="E59" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G59" s="28" t="s">
+      <c r="F59" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G59" s="22" t="s">
         <v>230</v>
       </c>
       <c r="H59" t="s">
@@ -2955,28 +3118,28 @@
       <c r="K59" s="1"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
-      <c r="N59" s="1"/>
+      <c r="N59" s="4"/>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="26" t="s">
-        <v>210</v>
-      </c>
-      <c r="B60" s="26">
-        <v>1273</v>
-      </c>
-      <c r="C60" s="26">
-        <v>1273</v>
-      </c>
-      <c r="D60" s="23" t="s">
+      <c r="A60" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="B60" s="20">
+        <v>1176</v>
+      </c>
+      <c r="C60" s="20">
+        <v>1176</v>
+      </c>
+      <c r="D60" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="E60" s="21" t="s">
+      <c r="E60" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="F60" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G60" s="28" t="s">
+      <c r="F60" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G60" s="22" t="s">
         <v>230</v>
       </c>
       <c r="H60" t="s">
@@ -2988,35 +3151,38 @@
       <c r="K60" s="1"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
-      <c r="N60" s="4"/>
+      <c r="N60" s="1"/>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="26">
-        <v>1276</v>
-      </c>
-      <c r="C61" s="26">
-        <v>1276</v>
-      </c>
-      <c r="D61" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="E61" s="21" t="s">
+      <c r="A61" s="20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B61" s="20">
+        <v>1171</v>
+      </c>
+      <c r="C61" s="20">
+        <v>1171</v>
+      </c>
+      <c r="D61" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="E61" s="16" t="s">
         <v>226</v>
       </c>
-      <c r="F61" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G61" s="28" t="s">
+      <c r="F61" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="G61" s="22" t="s">
         <v>230</v>
       </c>
       <c r="H61" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="I61" t="s">
         <v>246</v>
+      </c>
+      <c r="J61" t="s">
+        <v>249</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="2"/>
@@ -3024,25 +3190,25 @@
       <c r="N61" s="1"/>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" s="26" t="s">
-        <v>213</v>
-      </c>
-      <c r="B62" s="26">
-        <v>1254</v>
-      </c>
-      <c r="C62" s="26">
-        <v>1254</v>
-      </c>
-      <c r="D62" s="21" t="s">
+      <c r="A62" s="27" t="s">
+        <v>217</v>
+      </c>
+      <c r="B62" s="27">
+        <v>178</v>
+      </c>
+      <c r="C62" s="27">
+        <v>1175</v>
+      </c>
+      <c r="D62" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E62" s="21" t="s">
+      <c r="E62" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="F62" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G62" s="28" t="s">
+      <c r="F62" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G62" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H62" t="s">
@@ -3057,25 +3223,25 @@
       <c r="N62" s="1"/>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="26" t="s">
-        <v>77</v>
-      </c>
-      <c r="B63" s="26">
-        <v>1294</v>
-      </c>
-      <c r="C63" s="26">
-        <v>1294</v>
-      </c>
-      <c r="D63" s="21" t="s">
+      <c r="A63" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="B63" s="32">
+        <v>173</v>
+      </c>
+      <c r="C63" s="32">
+        <v>1174</v>
+      </c>
+      <c r="D63" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E63" s="21" t="s">
+      <c r="E63" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="F63" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="G63" s="28" t="s">
+      <c r="F63" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G63" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H63" t="s">
@@ -3084,31 +3250,31 @@
       <c r="I63" t="s">
         <v>246</v>
       </c>
-      <c r="K63" s="1"/>
+      <c r="K63" s="4"/>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
-      <c r="N63" s="1"/>
+      <c r="N63" s="4"/>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="26" t="s">
-        <v>66</v>
-      </c>
-      <c r="B64" s="26">
-        <v>127</v>
-      </c>
-      <c r="C64" s="26">
-        <v>1172</v>
-      </c>
-      <c r="D64" s="24" t="s">
+      <c r="A64" s="32" t="s">
+        <v>242</v>
+      </c>
+      <c r="B64" s="32">
+        <v>161</v>
+      </c>
+      <c r="C64" s="32">
+        <v>1068</v>
+      </c>
+      <c r="D64" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="F64" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G64" s="28" t="s">
+      <c r="F64" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G64" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H64" t="s">
@@ -3117,31 +3283,31 @@
       <c r="I64" t="s">
         <v>246</v>
       </c>
-      <c r="K64" s="1"/>
+      <c r="K64" s="4"/>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
-      <c r="N64" s="1"/>
+      <c r="N64" s="4"/>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="26" t="s">
-        <v>175</v>
-      </c>
-      <c r="B65" s="26">
-        <v>129</v>
-      </c>
-      <c r="C65" s="26">
-        <v>1132</v>
-      </c>
-      <c r="D65" s="24" t="s">
+      <c r="A65" s="32" t="s">
+        <v>17</v>
+      </c>
+      <c r="B65" s="32">
+        <v>160</v>
+      </c>
+      <c r="C65" s="32">
+        <v>1212</v>
+      </c>
+      <c r="D65" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="F65" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G65" s="28" t="s">
+      <c r="F65" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G65" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H65" t="s">
@@ -3150,31 +3316,31 @@
       <c r="I65" t="s">
         <v>246</v>
       </c>
-      <c r="K65" s="1"/>
+      <c r="K65" s="4"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
-      <c r="N65" s="1"/>
+      <c r="N65" s="4"/>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="26" t="s">
-        <v>116</v>
-      </c>
-      <c r="B66" s="26">
-        <v>146</v>
-      </c>
-      <c r="C66" s="26">
-        <v>1211</v>
-      </c>
-      <c r="D66" s="24" t="s">
+      <c r="A66" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="B66" s="21">
+        <v>158</v>
+      </c>
+      <c r="C66" s="21">
+        <v>1088</v>
+      </c>
+      <c r="D66" s="19" t="s">
         <v>223</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F66" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G66" s="28" t="s">
+      <c r="F66" s="22" t="s">
+        <v>229</v>
+      </c>
+      <c r="G66" s="22" t="s">
         <v>230</v>
       </c>
       <c r="H66" t="s">
@@ -3183,31 +3349,31 @@
       <c r="I66" t="s">
         <v>246</v>
       </c>
-      <c r="K66" s="1"/>
+      <c r="K66" s="4"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
-      <c r="N66" s="1"/>
+      <c r="N66" s="4"/>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="26" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" s="26">
-        <v>154</v>
-      </c>
-      <c r="C67" s="26">
-        <v>1215</v>
-      </c>
-      <c r="D67" s="24" t="s">
+      <c r="A67" s="27" t="s">
+        <v>116</v>
+      </c>
+      <c r="B67" s="27">
+        <v>146</v>
+      </c>
+      <c r="C67" s="27">
+        <v>1211</v>
+      </c>
+      <c r="D67" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="F67" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G67" s="28" t="s">
+      <c r="F67" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G67" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H67" t="s">
@@ -3223,24 +3389,24 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A68" s="27" t="s">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="B68" s="27">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="C68" s="27">
-        <v>1088</v>
-      </c>
-      <c r="D68" s="24" t="s">
+        <v>1231</v>
+      </c>
+      <c r="D68" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="28" t="s">
         <v>226</v>
       </c>
-      <c r="F68" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G68" s="28" t="s">
+      <c r="F68" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G68" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H68" t="s">
@@ -3249,31 +3415,31 @@
       <c r="I68" t="s">
         <v>246</v>
       </c>
-      <c r="K68" s="4"/>
+      <c r="K68" s="1"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
-      <c r="N68" s="4"/>
+      <c r="N68" s="1"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A69" s="27" t="s">
-        <v>17</v>
+        <v>175</v>
       </c>
       <c r="B69" s="27">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="C69" s="27">
-        <v>1212</v>
-      </c>
-      <c r="D69" s="24" t="s">
+        <v>1132</v>
+      </c>
+      <c r="D69" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E69" s="22" t="s">
+      <c r="E69" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="F69" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G69" s="28" t="s">
+      <c r="F69" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G69" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H69" t="s">
@@ -3282,31 +3448,31 @@
       <c r="I69" t="s">
         <v>246</v>
       </c>
-      <c r="K69" s="4"/>
+      <c r="K69" s="1"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
-      <c r="N69" s="4"/>
+      <c r="N69" s="1"/>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A70" s="27" t="s">
-        <v>242</v>
+        <v>66</v>
       </c>
       <c r="B70" s="27">
-        <v>161</v>
+        <v>127</v>
       </c>
       <c r="C70" s="27">
-        <v>1068</v>
-      </c>
-      <c r="D70" s="24" t="s">
+        <v>1172</v>
+      </c>
+      <c r="D70" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="E70" s="22" t="s">
+      <c r="E70" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="F70" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G70" s="28" t="s">
+      <c r="F70" s="30" t="s">
+        <v>229</v>
+      </c>
+      <c r="G70" s="30" t="s">
         <v>230</v>
       </c>
       <c r="H70" t="s">
@@ -3315,71 +3481,59 @@
       <c r="I70" t="s">
         <v>246</v>
       </c>
-      <c r="K70" s="4"/>
+      <c r="K70" s="1"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
-      <c r="N70" s="4"/>
+      <c r="N70" s="1"/>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A71" s="27" t="s">
-        <v>9</v>
-      </c>
-      <c r="B71" s="27">
-        <v>173</v>
-      </c>
-      <c r="C71" s="27">
-        <v>1174</v>
-      </c>
-      <c r="D71" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="E71" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="F71" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G71" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="H71" t="s">
-        <v>240</v>
-      </c>
-      <c r="I71" t="s">
-        <v>246</v>
-      </c>
-      <c r="K71" s="4"/>
+      <c r="A71" t="s">
+        <v>50</v>
+      </c>
+      <c r="B71">
+        <v>1332</v>
+      </c>
+      <c r="C71">
+        <v>1332</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="K71" s="1"/>
       <c r="L71" s="2"/>
       <c r="M71" s="2"/>
-      <c r="N71" s="4"/>
+      <c r="N71" s="1"/>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A72" s="26" t="s">
-        <v>217</v>
-      </c>
-      <c r="B72" s="26">
-        <v>178</v>
-      </c>
-      <c r="C72" s="26">
-        <v>1175</v>
-      </c>
-      <c r="D72" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="E72" s="22" t="s">
-        <v>226</v>
-      </c>
-      <c r="F72" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G72" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="H72" t="s">
-        <v>240</v>
-      </c>
-      <c r="I72" t="s">
-        <v>246</v>
+      <c r="A72" t="s">
+        <v>53</v>
+      </c>
+      <c r="B72">
+        <v>1326</v>
+      </c>
+      <c r="C72">
+        <v>1326</v>
+      </c>
+      <c r="D72" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="K72" s="1"/>
       <c r="L72" s="2"/>
@@ -3387,32 +3541,26 @@
       <c r="N72" s="1"/>
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A73" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="B73" s="26">
-        <v>133</v>
-      </c>
-      <c r="C73" s="26">
-        <v>1231</v>
-      </c>
-      <c r="D73" s="24" t="s">
-        <v>222</v>
-      </c>
-      <c r="E73" s="21" t="s">
-        <v>226</v>
-      </c>
-      <c r="F73" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="G73" s="28" t="s">
-        <v>230</v>
-      </c>
-      <c r="H73" t="s">
-        <v>240</v>
-      </c>
-      <c r="I73" t="s">
-        <v>246</v>
+      <c r="A73" t="s">
+        <v>101</v>
+      </c>
+      <c r="B73">
+        <v>1311</v>
+      </c>
+      <c r="C73">
+        <v>1311</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>230</v>
       </c>
       <c r="K73" s="1"/>
       <c r="L73" s="2"/>
@@ -3420,48 +3568,46 @@
       <c r="N73" s="1"/>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A74" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B74" s="3">
-        <v>169</v>
-      </c>
-      <c r="C74" s="3">
-        <v>1327</v>
-      </c>
-      <c r="D74" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="E74" s="10" t="s">
+      <c r="A74" t="s">
+        <v>196</v>
+      </c>
+      <c r="B74">
+        <v>1298</v>
+      </c>
+      <c r="C74">
+        <v>1298</v>
+      </c>
+      <c r="D74" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E74" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-      <c r="K74" s="4"/>
+      <c r="K74" s="1"/>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
-      <c r="N74" s="4"/>
+      <c r="N74" s="1"/>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A75" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="B75" s="3">
-        <v>1136</v>
-      </c>
-      <c r="C75" s="3">
-        <v>1136</v>
-      </c>
-      <c r="D75" s="10" t="s">
+      <c r="A75" t="s">
+        <v>68</v>
+      </c>
+      <c r="B75">
+        <v>1293</v>
+      </c>
+      <c r="C75">
+        <v>1293</v>
+      </c>
+      <c r="D75" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="11" t="s">
         <v>225</v>
       </c>
       <c r="F75" s="2" t="s">
@@ -3470,29 +3616,28 @@
       <c r="G75" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H75" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="I75" s="3"/>
-      <c r="K75" s="4"/>
+      <c r="H75" t="s">
+        <v>237</v>
+      </c>
+      <c r="K75" s="1"/>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
-      <c r="N75" s="4"/>
+      <c r="N75" s="1"/>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>193</v>
+        <v>136</v>
       </c>
       <c r="B76">
-        <v>1249</v>
+        <v>1292</v>
       </c>
       <c r="C76">
-        <v>1249</v>
-      </c>
-      <c r="D76" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E76" s="11" t="s">
+        <v>1292</v>
+      </c>
+      <c r="D76" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E76" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F76" s="2" t="s">
@@ -3500,9 +3645,6 @@
       </c>
       <c r="G76" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="H76" t="s">
-        <v>235</v>
       </c>
       <c r="K76" s="1"/>
       <c r="L76" s="2"/>
@@ -3511,18 +3653,18 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="B77">
-        <v>1250</v>
+        <v>1290</v>
       </c>
       <c r="C77">
-        <v>1250</v>
-      </c>
-      <c r="D77" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E77" s="11" t="s">
+        <v>1290</v>
+      </c>
+      <c r="D77" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E77" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F77" s="2" t="s">
@@ -3530,9 +3672,6 @@
       </c>
       <c r="G77" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="H77" t="s">
-        <v>236</v>
       </c>
       <c r="K77" s="1"/>
       <c r="L77" s="2"/>
@@ -3541,18 +3680,18 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>142</v>
+        <v>28</v>
       </c>
       <c r="B78">
-        <v>1270</v>
+        <v>1278</v>
       </c>
       <c r="C78">
-        <v>1270</v>
-      </c>
-      <c r="D78" s="10" t="s">
-        <v>223</v>
-      </c>
-      <c r="E78" s="11" t="s">
+        <v>1278</v>
+      </c>
+      <c r="D78" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E78" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F78" s="2" t="s">
@@ -3560,29 +3699,26 @@
       </c>
       <c r="G78" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="H78" t="s">
-        <v>236</v>
       </c>
       <c r="K78" s="1"/>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
-      <c r="N78" s="4"/>
+      <c r="N78" s="1"/>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
-        <v>68</v>
+        <v>128</v>
       </c>
       <c r="B79">
-        <v>1293</v>
+        <v>1274</v>
       </c>
       <c r="C79">
-        <v>1293</v>
-      </c>
-      <c r="D79" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="E79" s="11" t="s">
+        <v>1274</v>
+      </c>
+      <c r="D79" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E79" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F79" s="2" t="s">
@@ -3590,9 +3726,6 @@
       </c>
       <c r="G79" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="H79" t="s">
-        <v>237</v>
       </c>
       <c r="K79" s="1"/>
       <c r="L79" s="2"/>
@@ -3601,40 +3734,43 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
-        <v>85</v>
+        <v>142</v>
       </c>
       <c r="B80">
-        <v>4</v>
+        <v>1270</v>
       </c>
       <c r="C80">
-        <v>1094</v>
-      </c>
-      <c r="D80" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E80" s="1" t="s">
+        <v>1270</v>
+      </c>
+      <c r="D80" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E80" s="11" t="s">
         <v>225</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>230</v>
+      </c>
+      <c r="H80" t="s">
+        <v>236</v>
       </c>
       <c r="K80" s="1"/>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
-      <c r="N80" s="1"/>
+      <c r="N80" s="4"/>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="B81">
-        <v>6</v>
+        <v>1258</v>
       </c>
       <c r="C81">
-        <v>1228</v>
+        <v>1258</v>
       </c>
       <c r="D81" s="1" t="s">
         <v>222</v>
@@ -3643,7 +3779,7 @@
         <v>225</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>230</v>
@@ -3655,13 +3791,13 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
-        <v>81</v>
+        <v>30</v>
       </c>
       <c r="B82">
-        <v>7</v>
+        <v>1255</v>
       </c>
       <c r="C82">
-        <v>1112</v>
+        <v>1255</v>
       </c>
       <c r="D82" s="1" t="s">
         <v>222</v>
@@ -3670,7 +3806,7 @@
         <v>225</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>230</v>
@@ -3682,13 +3818,13 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>93</v>
+        <v>172</v>
       </c>
       <c r="B83">
-        <v>8</v>
+        <v>1253</v>
       </c>
       <c r="C83">
-        <v>1304</v>
+        <v>1253</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>222</v>
@@ -3697,7 +3833,7 @@
         <v>225</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>230</v>
@@ -3709,25 +3845,28 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="B84">
-        <v>9</v>
+        <v>1250</v>
       </c>
       <c r="C84">
-        <v>1217</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E84" s="1" t="s">
+        <v>1250</v>
+      </c>
+      <c r="D84" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E84" s="11" t="s">
         <v>225</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>230</v>
+      </c>
+      <c r="H84" t="s">
+        <v>236</v>
       </c>
       <c r="K84" s="1"/>
       <c r="L84" s="2"/>
@@ -3736,25 +3875,28 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>82</v>
+        <v>193</v>
       </c>
       <c r="B85">
-        <v>11</v>
+        <v>1249</v>
       </c>
       <c r="C85">
-        <v>1314</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E85" s="1" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D85" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="E85" s="11" t="s">
         <v>225</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>230</v>
+      </c>
+      <c r="H85" t="s">
+        <v>235</v>
       </c>
       <c r="K85" s="1"/>
       <c r="L85" s="2"/>
@@ -3763,13 +3905,13 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="B86">
-        <v>13</v>
+        <v>1248</v>
       </c>
       <c r="C86">
-        <v>1229</v>
+        <v>1248</v>
       </c>
       <c r="D86" s="1" t="s">
         <v>222</v>
@@ -3778,7 +3920,7 @@
         <v>225</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>230</v>
@@ -3790,25 +3932,28 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
-        <v>62</v>
+        <v>218</v>
       </c>
       <c r="B87">
-        <v>16</v>
+        <v>1246</v>
       </c>
       <c r="C87">
-        <v>1053</v>
+        <v>1246</v>
       </c>
       <c r="D87" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>230</v>
+      </c>
+      <c r="H87" t="s">
+        <v>239</v>
       </c>
       <c r="K87" s="1"/>
       <c r="L87" s="2"/>
@@ -3817,13 +3962,13 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B88">
-        <v>18</v>
+        <v>1239</v>
       </c>
       <c r="C88">
-        <v>1130</v>
+        <v>1239</v>
       </c>
       <c r="D88" s="1" t="s">
         <v>222</v>
@@ -3832,7 +3977,7 @@
         <v>225</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>230</v>
@@ -3844,13 +3989,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>153</v>
       </c>
       <c r="B89">
-        <v>20</v>
+        <v>1238</v>
       </c>
       <c r="C89">
-        <v>1218</v>
+        <v>1238</v>
       </c>
       <c r="D89" s="1" t="s">
         <v>222</v>
@@ -3859,7 +4004,7 @@
         <v>225</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>230</v>
@@ -3871,13 +4016,13 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A90" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="B90">
-        <v>21</v>
+        <v>1236</v>
       </c>
       <c r="C90">
-        <v>1187</v>
+        <v>1236</v>
       </c>
       <c r="D90" s="1" t="s">
         <v>222</v>
@@ -3886,7 +4031,7 @@
         <v>225</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>230</v>
@@ -3898,13 +4043,13 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A91" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B91">
-        <v>22</v>
+        <v>1227</v>
       </c>
       <c r="C91">
-        <v>1147</v>
+        <v>1227</v>
       </c>
       <c r="D91" s="1" t="s">
         <v>222</v>
@@ -3913,7 +4058,7 @@
         <v>225</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>230</v>
@@ -3925,13 +4070,13 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A92" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B92">
-        <v>23</v>
+        <v>1219</v>
       </c>
       <c r="C92">
-        <v>1095</v>
+        <v>1219</v>
       </c>
       <c r="D92" s="1" t="s">
         <v>222</v>
@@ -3940,7 +4085,7 @@
         <v>225</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>230</v>
@@ -3952,13 +4097,13 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A93" t="s">
-        <v>151</v>
+        <v>180</v>
       </c>
       <c r="B93">
-        <v>24</v>
+        <v>1216</v>
       </c>
       <c r="C93">
-        <v>1324</v>
+        <v>1216</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>222</v>
@@ -3967,7 +4112,7 @@
         <v>225</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>230</v>
@@ -3979,13 +4124,13 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="B94">
-        <v>28</v>
+        <v>1213</v>
       </c>
       <c r="C94">
-        <v>1150</v>
+        <v>1213</v>
       </c>
       <c r="D94" s="1" t="s">
         <v>222</v>
@@ -3994,7 +4139,7 @@
         <v>225</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>230</v>
@@ -4006,13 +4151,13 @@
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A95" t="s">
-        <v>46</v>
+        <v>108</v>
       </c>
       <c r="B95">
-        <v>29</v>
+        <v>1196</v>
       </c>
       <c r="C95">
-        <v>1348</v>
+        <v>1196</v>
       </c>
       <c r="D95" s="1" t="s">
         <v>222</v>
@@ -4021,7 +4166,7 @@
         <v>225</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>230</v>
@@ -4033,13 +4178,13 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A96" t="s">
-        <v>37</v>
+        <v>178</v>
       </c>
       <c r="B96">
-        <v>30</v>
+        <v>1194</v>
       </c>
       <c r="C96">
-        <v>1349</v>
+        <v>1194</v>
       </c>
       <c r="D96" s="1" t="s">
         <v>222</v>
@@ -4048,7 +4193,7 @@
         <v>225</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>230</v>
@@ -4060,13 +4205,13 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A97" t="s">
-        <v>122</v>
+        <v>212</v>
       </c>
       <c r="B97">
-        <v>32</v>
+        <v>1193</v>
       </c>
       <c r="C97">
-        <v>1267</v>
+        <v>1193</v>
       </c>
       <c r="D97" s="1" t="s">
         <v>222</v>
@@ -4075,7 +4220,7 @@
         <v>225</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>230</v>
@@ -4086,25 +4231,25 @@
       <c r="N97" s="1"/>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A98" t="s">
-        <v>58</v>
-      </c>
-      <c r="B98">
-        <v>33</v>
-      </c>
-      <c r="C98">
-        <v>1365</v>
-      </c>
-      <c r="D98" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E98" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F98" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="G98" s="2" t="s">
+      <c r="A98" s="24" t="s">
+        <v>170</v>
+      </c>
+      <c r="B98" s="24">
+        <v>1190</v>
+      </c>
+      <c r="C98" s="24">
+        <v>1190</v>
+      </c>
+      <c r="D98" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E98" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="G98" s="26" t="s">
         <v>230</v>
       </c>
       <c r="K98" s="1"/>
@@ -4114,13 +4259,13 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A99" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
       <c r="B99">
-        <v>34</v>
+        <v>1179</v>
       </c>
       <c r="C99">
-        <v>1271</v>
+        <v>1179</v>
       </c>
       <c r="D99" s="1" t="s">
         <v>222</v>
@@ -4129,7 +4274,7 @@
         <v>225</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G99" s="2" t="s">
         <v>230</v>
@@ -4141,13 +4286,13 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A100" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="B100">
-        <v>35</v>
+        <v>1177</v>
       </c>
       <c r="C100">
-        <v>1286</v>
+        <v>1177</v>
       </c>
       <c r="D100" s="1" t="s">
         <v>222</v>
@@ -4156,7 +4301,7 @@
         <v>225</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G100" s="2" t="s">
         <v>230</v>
@@ -4168,13 +4313,13 @@
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A101" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="B101">
-        <v>37</v>
+        <v>1156</v>
       </c>
       <c r="C101">
-        <v>1284</v>
+        <v>1156</v>
       </c>
       <c r="D101" s="1" t="s">
         <v>222</v>
@@ -4183,7 +4328,7 @@
         <v>225</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G101" s="2" t="s">
         <v>230</v>
@@ -4195,13 +4340,13 @@
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A102" t="s">
-        <v>34</v>
+        <v>173</v>
       </c>
       <c r="B102">
-        <v>38</v>
+        <v>1154</v>
       </c>
       <c r="C102">
-        <v>1032</v>
+        <v>1154</v>
       </c>
       <c r="D102" s="1" t="s">
         <v>222</v>
@@ -4210,7 +4355,7 @@
         <v>225</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>230</v>
@@ -4222,13 +4367,13 @@
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A103" t="s">
-        <v>214</v>
+        <v>72</v>
       </c>
       <c r="B103">
-        <v>39</v>
+        <v>1153</v>
       </c>
       <c r="C103">
-        <v>1333</v>
+        <v>1153</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>222</v>
@@ -4237,7 +4382,7 @@
         <v>225</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G103" s="2" t="s">
         <v>230</v>
@@ -4248,41 +4393,45 @@
       <c r="N103" s="1"/>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A104" t="s">
-        <v>189</v>
-      </c>
-      <c r="B104">
-        <v>41</v>
-      </c>
-      <c r="C104">
-        <v>1266</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E104" s="1" t="s">
+      <c r="A104" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B104" s="3">
+        <v>1136</v>
+      </c>
+      <c r="C104" s="3">
+        <v>1136</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E104" s="10" t="s">
         <v>225</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G104" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K104" s="1"/>
+      <c r="H104" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="I104" s="3"/>
+      <c r="K104" s="4"/>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
-      <c r="N104" s="1"/>
+      <c r="N104" s="4"/>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A105" t="s">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="B105">
-        <v>43</v>
+        <v>177</v>
       </c>
       <c r="C105">
-        <v>1328</v>
+        <v>1207</v>
       </c>
       <c r="D105" s="1" t="s">
         <v>222</v>
@@ -4303,13 +4452,13 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A106" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="B106">
-        <v>44</v>
+        <v>175</v>
       </c>
       <c r="C106">
-        <v>1199</v>
+        <v>1152</v>
       </c>
       <c r="D106" s="1" t="s">
         <v>222</v>
@@ -4330,13 +4479,13 @@
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A107" t="s">
-        <v>187</v>
+        <v>220</v>
       </c>
       <c r="B107">
-        <v>45</v>
+        <v>174</v>
       </c>
       <c r="C107">
-        <v>1075</v>
+        <v>1230</v>
       </c>
       <c r="D107" s="1" t="s">
         <v>222</v>
@@ -4356,19 +4505,19 @@
       <c r="N107" s="1"/>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A108" t="s">
-        <v>121</v>
-      </c>
-      <c r="B108">
-        <v>47</v>
-      </c>
-      <c r="C108">
-        <v>1264</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E108" s="1" t="s">
+      <c r="A108" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B108" s="3">
+        <v>171</v>
+      </c>
+      <c r="C108" s="3">
+        <v>1208</v>
+      </c>
+      <c r="D108" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E108" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F108" s="2" t="s">
@@ -4377,25 +4526,27 @@
       <c r="G108" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K108" s="1"/>
+      <c r="H108" s="3"/>
+      <c r="I108" s="3"/>
+      <c r="K108" s="4"/>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
-      <c r="N108" s="1"/>
+      <c r="N108" s="4"/>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A109" t="s">
-        <v>18</v>
-      </c>
-      <c r="B109">
-        <v>50</v>
-      </c>
-      <c r="C109">
-        <v>1090</v>
-      </c>
-      <c r="D109" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E109" s="1" t="s">
+      <c r="A109" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B109" s="3">
+        <v>170</v>
+      </c>
+      <c r="C109" s="3">
+        <v>1209</v>
+      </c>
+      <c r="D109" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E109" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F109" s="2" t="s">
@@ -4404,25 +4555,27 @@
       <c r="G109" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K109" s="1"/>
+      <c r="H109" s="3"/>
+      <c r="I109" s="3"/>
+      <c r="K109" s="4"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
-      <c r="N109" s="1"/>
+      <c r="N109" s="4"/>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A110" t="s">
-        <v>76</v>
-      </c>
-      <c r="B110">
-        <v>52</v>
-      </c>
-      <c r="C110">
-        <v>1052</v>
-      </c>
-      <c r="D110" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E110" s="1" t="s">
+      <c r="A110" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B110" s="3">
+        <v>169</v>
+      </c>
+      <c r="C110" s="3">
+        <v>1327</v>
+      </c>
+      <c r="D110" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="E110" s="10" t="s">
         <v>225</v>
       </c>
       <c r="F110" s="2" t="s">
@@ -4431,25 +4584,27 @@
       <c r="G110" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K110" s="1"/>
+      <c r="H110" s="3"/>
+      <c r="I110" s="3"/>
+      <c r="K110" s="4"/>
       <c r="L110" s="2"/>
       <c r="M110" s="2"/>
-      <c r="N110" s="1"/>
+      <c r="N110" s="4"/>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A111" t="s">
-        <v>167</v>
-      </c>
-      <c r="B111">
-        <v>53</v>
-      </c>
-      <c r="C111">
-        <v>1133</v>
-      </c>
-      <c r="D111" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E111" s="1" t="s">
+      <c r="A111" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" s="3">
+        <v>168</v>
+      </c>
+      <c r="C111" s="3">
+        <v>1110</v>
+      </c>
+      <c r="D111" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E111" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F111" s="2" t="s">
@@ -4458,25 +4613,27 @@
       <c r="G111" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K111" s="1"/>
+      <c r="H111" s="3"/>
+      <c r="I111" s="3"/>
+      <c r="K111" s="4"/>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
-      <c r="N111" s="1"/>
+      <c r="N111" s="4"/>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A112" t="s">
-        <v>94</v>
-      </c>
-      <c r="B112">
-        <v>54</v>
-      </c>
-      <c r="C112">
-        <v>1054</v>
-      </c>
-      <c r="D112" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E112" s="1" t="s">
+      <c r="A112" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B112" s="3">
+        <v>167</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1210</v>
+      </c>
+      <c r="D112" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E112" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F112" s="2" t="s">
@@ -4485,25 +4642,27 @@
       <c r="G112" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K112" s="1"/>
+      <c r="H112" s="3"/>
+      <c r="I112" s="3"/>
+      <c r="K112" s="4"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
-      <c r="N112" s="1"/>
+      <c r="N112" s="4"/>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A113" t="s">
-        <v>219</v>
-      </c>
-      <c r="B113">
-        <v>56</v>
-      </c>
-      <c r="C113">
-        <v>1235</v>
-      </c>
-      <c r="D113" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E113" s="1" t="s">
+      <c r="A113" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B113" s="3">
+        <v>166</v>
+      </c>
+      <c r="C113" s="3">
+        <v>1173</v>
+      </c>
+      <c r="D113" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E113" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F113" s="2" t="s">
@@ -4512,25 +4671,27 @@
       <c r="G113" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K113" s="1"/>
+      <c r="H113" s="3"/>
+      <c r="I113" s="3"/>
+      <c r="K113" s="4"/>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
-      <c r="N113" s="1"/>
+      <c r="N113" s="4"/>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A114" t="s">
-        <v>181</v>
-      </c>
-      <c r="B114">
-        <v>57</v>
-      </c>
-      <c r="C114">
-        <v>1093</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E114" s="1" t="s">
+      <c r="A114" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B114" s="3">
+        <v>165</v>
+      </c>
+      <c r="C114" s="3">
+        <v>1168</v>
+      </c>
+      <c r="D114" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E114" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F114" s="2" t="s">
@@ -4539,25 +4700,27 @@
       <c r="G114" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K114" s="1"/>
+      <c r="H114" s="3"/>
+      <c r="I114" s="3"/>
+      <c r="K114" s="4"/>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
-      <c r="N114" s="1"/>
+      <c r="N114" s="4"/>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A115" t="s">
-        <v>27</v>
-      </c>
-      <c r="B115">
-        <v>61</v>
-      </c>
-      <c r="C115">
-        <v>1309</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E115" s="1" t="s">
+      <c r="A115" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B115" s="3">
+        <v>164</v>
+      </c>
+      <c r="C115" s="3">
+        <v>1149</v>
+      </c>
+      <c r="D115" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E115" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F115" s="2" t="s">
@@ -4566,25 +4729,27 @@
       <c r="G115" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K115" s="1"/>
+      <c r="H115" s="3"/>
+      <c r="I115" s="3"/>
+      <c r="K115" s="4"/>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
-      <c r="N115" s="1"/>
+      <c r="N115" s="4"/>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A116" t="s">
-        <v>114</v>
-      </c>
-      <c r="B116">
-        <v>64</v>
-      </c>
-      <c r="C116">
-        <v>1265</v>
-      </c>
-      <c r="D116" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E116" s="1" t="s">
+      <c r="A116" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B116" s="3">
+        <v>163</v>
+      </c>
+      <c r="C116" s="3">
+        <v>1148</v>
+      </c>
+      <c r="D116" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E116" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F116" s="2" t="s">
@@ -4593,25 +4758,27 @@
       <c r="G116" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K116" s="1"/>
+      <c r="H116" s="3"/>
+      <c r="I116" s="3"/>
+      <c r="K116" s="4"/>
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
-      <c r="N116" s="1"/>
+      <c r="N116" s="4"/>
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A117" t="s">
-        <v>48</v>
-      </c>
-      <c r="B117">
-        <v>65</v>
-      </c>
-      <c r="C117">
-        <v>1074</v>
-      </c>
-      <c r="D117" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E117" s="1" t="s">
+      <c r="A117" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B117" s="3">
+        <v>159</v>
+      </c>
+      <c r="C117" s="3">
+        <v>1312</v>
+      </c>
+      <c r="D117" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E117" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F117" s="2" t="s">
@@ -4620,25 +4787,27 @@
       <c r="G117" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K117" s="1"/>
+      <c r="H117" s="3"/>
+      <c r="I117" s="3"/>
+      <c r="K117" s="4"/>
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
-      <c r="N117" s="1"/>
+      <c r="N117" s="4"/>
     </row>
     <row r="118" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A118" t="s">
-        <v>49</v>
-      </c>
-      <c r="B118">
-        <v>66</v>
-      </c>
-      <c r="C118">
-        <v>1313</v>
-      </c>
-      <c r="D118" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E118" s="1" t="s">
+      <c r="A118" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B118" s="3">
+        <v>157</v>
+      </c>
+      <c r="C118" s="3">
+        <v>1155</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E118" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F118" s="2" t="s">
@@ -4647,25 +4816,27 @@
       <c r="G118" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K118" s="1"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="K118" s="4"/>
       <c r="L118" s="2"/>
       <c r="M118" s="2"/>
-      <c r="N118" s="1"/>
+      <c r="N118" s="4"/>
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A119" t="s">
-        <v>63</v>
-      </c>
-      <c r="B119">
-        <v>68</v>
-      </c>
-      <c r="C119">
-        <v>1251</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E119" s="1" t="s">
+      <c r="A119" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B119" s="3">
+        <v>156</v>
+      </c>
+      <c r="C119" s="3">
+        <v>1197</v>
+      </c>
+      <c r="D119" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E119" s="4" t="s">
         <v>225</v>
       </c>
       <c r="F119" s="2" t="s">
@@ -4674,33 +4845,37 @@
       <c r="G119" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="K119" s="1"/>
+      <c r="H119" s="3"/>
+      <c r="I119" s="3"/>
+      <c r="K119" s="4"/>
       <c r="L119" s="2"/>
       <c r="M119" s="2"/>
-      <c r="N119" s="1"/>
+      <c r="N119" s="4"/>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A120" t="s">
-        <v>8</v>
-      </c>
-      <c r="B120">
-        <v>69</v>
-      </c>
-      <c r="C120">
-        <v>1353</v>
-      </c>
-      <c r="D120" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E120" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F120" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="A120" s="24" t="s">
+        <v>143</v>
+      </c>
+      <c r="B120" s="24">
+        <v>154</v>
+      </c>
+      <c r="C120" s="24">
+        <v>1215</v>
+      </c>
+      <c r="D120" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E120" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="F120" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="G120" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="H120" s="24"/>
+      <c r="I120" s="24"/>
       <c r="K120" s="1"/>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
@@ -4708,13 +4883,13 @@
     </row>
     <row r="121" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A121" t="s">
-        <v>174</v>
+        <v>138</v>
       </c>
       <c r="B121">
-        <v>70</v>
+        <v>153</v>
       </c>
       <c r="C121">
-        <v>1296</v>
+        <v>1288</v>
       </c>
       <c r="D121" s="1" t="s">
         <v>222</v>
@@ -4735,16 +4910,16 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A122" t="s">
-        <v>166</v>
+        <v>3</v>
       </c>
       <c r="B122">
-        <v>71</v>
+        <v>152</v>
       </c>
       <c r="C122">
-        <v>1308</v>
-      </c>
-      <c r="D122" s="1" t="s">
-        <v>222</v>
+        <v>1373</v>
+      </c>
+      <c r="D122" s="23" t="s">
+        <v>223</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>225</v>
@@ -4754,6 +4929,9 @@
       </c>
       <c r="G122" s="2" t="s">
         <v>230</v>
+      </c>
+      <c r="H122" t="s">
+        <v>247</v>
       </c>
       <c r="K122" s="1"/>
       <c r="L122" s="2"/>
@@ -4762,13 +4940,13 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A123" t="s">
-        <v>211</v>
+        <v>124</v>
       </c>
       <c r="B123">
-        <v>72</v>
+        <v>150</v>
       </c>
       <c r="C123">
-        <v>1127</v>
+        <v>1109</v>
       </c>
       <c r="D123" s="1" t="s">
         <v>222</v>
@@ -4789,13 +4967,13 @@
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A124" t="s">
-        <v>215</v>
+        <v>78</v>
       </c>
       <c r="B124">
-        <v>73</v>
+        <v>149</v>
       </c>
       <c r="C124">
-        <v>1272</v>
+        <v>1135</v>
       </c>
       <c r="D124" s="1" t="s">
         <v>222</v>
@@ -4804,7 +4982,7 @@
         <v>225</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G124" s="2" t="s">
         <v>230</v>
@@ -4816,13 +4994,13 @@
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A125" t="s">
-        <v>168</v>
+        <v>71</v>
       </c>
       <c r="B125">
-        <v>74</v>
+        <v>148</v>
       </c>
       <c r="C125">
-        <v>1031</v>
+        <v>1169</v>
       </c>
       <c r="D125" s="1" t="s">
         <v>222</v>
@@ -4843,13 +5021,13 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A126" t="s">
-        <v>45</v>
+        <v>104</v>
       </c>
       <c r="B126">
-        <v>75</v>
+        <v>145</v>
       </c>
       <c r="C126">
-        <v>1188</v>
+        <v>1291</v>
       </c>
       <c r="D126" s="1" t="s">
         <v>222</v>
@@ -4870,13 +5048,13 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A127" t="s">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="B127">
-        <v>76</v>
+        <v>144</v>
       </c>
       <c r="C127">
-        <v>1146</v>
+        <v>1245</v>
       </c>
       <c r="D127" s="1" t="s">
         <v>222</v>
@@ -4897,13 +5075,13 @@
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A128" t="s">
-        <v>102</v>
+        <v>26</v>
       </c>
       <c r="B128">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="C128">
-        <v>1325</v>
+        <v>1252</v>
       </c>
       <c r="D128" s="1" t="s">
         <v>222</v>
@@ -4924,13 +5102,13 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A129" t="s">
-        <v>79</v>
+        <v>134</v>
       </c>
       <c r="B129">
-        <v>78</v>
+        <v>137</v>
       </c>
       <c r="C129">
-        <v>1115</v>
+        <v>1170</v>
       </c>
       <c r="D129" s="1" t="s">
         <v>222</v>
@@ -4951,13 +5129,13 @@
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A130" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B130">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="C130">
-        <v>1128</v>
+        <v>1233</v>
       </c>
       <c r="D130" s="1" t="s">
         <v>222</v>
@@ -4978,13 +5156,13 @@
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A131" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="B131">
-        <v>81</v>
+        <v>135</v>
       </c>
       <c r="C131">
-        <v>1237</v>
+        <v>1089</v>
       </c>
       <c r="D131" s="1" t="s">
         <v>222</v>
@@ -4993,7 +5171,7 @@
         <v>225</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G131" s="2" t="s">
         <v>230</v>
@@ -5005,13 +5183,13 @@
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A132" t="s">
-        <v>133</v>
+        <v>209</v>
       </c>
       <c r="B132">
-        <v>82</v>
+        <v>134</v>
       </c>
       <c r="C132">
-        <v>1268</v>
+        <v>1111</v>
       </c>
       <c r="D132" s="1" t="s">
         <v>222</v>
@@ -5032,13 +5210,13 @@
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A133" t="s">
-        <v>159</v>
+        <v>33</v>
       </c>
       <c r="B133">
-        <v>83</v>
+        <v>132</v>
       </c>
       <c r="C133">
-        <v>1192</v>
+        <v>1214</v>
       </c>
       <c r="D133" s="1" t="s">
         <v>222</v>
@@ -5059,13 +5237,13 @@
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A134" t="s">
-        <v>84</v>
+        <v>195</v>
       </c>
       <c r="B134">
-        <v>84</v>
+        <v>131</v>
       </c>
       <c r="C134">
-        <v>1129</v>
+        <v>1269</v>
       </c>
       <c r="D134" s="1" t="s">
         <v>222</v>
@@ -5086,13 +5264,13 @@
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A135" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B135">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C135">
-        <v>1073</v>
+        <v>1306</v>
       </c>
       <c r="D135" s="1" t="s">
         <v>222</v>
@@ -5113,13 +5291,13 @@
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A136" t="s">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="B136">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="C136">
-        <v>1247</v>
+        <v>1092</v>
       </c>
       <c r="D136" s="1" t="s">
         <v>222</v>
@@ -5128,7 +5306,7 @@
         <v>225</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G136" s="2" t="s">
         <v>230</v>
@@ -5140,13 +5318,13 @@
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A137" t="s">
-        <v>132</v>
+        <v>207</v>
       </c>
       <c r="B137">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="C137">
-        <v>1131</v>
+        <v>1232</v>
       </c>
       <c r="D137" s="1" t="s">
         <v>222</v>
@@ -5155,7 +5333,7 @@
         <v>225</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G137" s="2" t="s">
         <v>230</v>
@@ -5167,13 +5345,13 @@
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A138" t="s">
-        <v>15</v>
+        <v>123</v>
       </c>
       <c r="B138">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="C138">
-        <v>1091</v>
+        <v>1055</v>
       </c>
       <c r="D138" s="1" t="s">
         <v>222</v>
@@ -5194,13 +5372,13 @@
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A139" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="B139">
-        <v>91</v>
+        <v>124</v>
       </c>
       <c r="C139">
-        <v>1345</v>
+        <v>1256</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>222</v>
@@ -5221,13 +5399,13 @@
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A140" t="s">
-        <v>69</v>
+        <v>202</v>
       </c>
       <c r="B140">
-        <v>92</v>
+        <v>122</v>
       </c>
       <c r="C140">
-        <v>1244</v>
+        <v>1307</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>222</v>
@@ -5248,13 +5426,13 @@
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A141" t="s">
-        <v>57</v>
+        <v>137</v>
       </c>
       <c r="B141">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="C141">
-        <v>1289</v>
+        <v>1234</v>
       </c>
       <c r="D141" s="1" t="s">
         <v>222</v>
@@ -5275,13 +5453,13 @@
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A142" t="s">
-        <v>171</v>
+        <v>131</v>
       </c>
       <c r="B142">
-        <v>97</v>
+        <v>120</v>
       </c>
       <c r="C142">
-        <v>1011</v>
+        <v>1070</v>
       </c>
       <c r="D142" s="1" t="s">
         <v>222</v>
@@ -5302,13 +5480,13 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A143" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B143">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="C143">
-        <v>1166</v>
+        <v>1277</v>
       </c>
       <c r="D143" s="1" t="s">
         <v>222</v>
@@ -5329,13 +5507,13 @@
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A144" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B144">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C144">
-        <v>1346</v>
+        <v>1257</v>
       </c>
       <c r="D144" s="1" t="s">
         <v>222</v>
@@ -5356,13 +5534,13 @@
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A145" t="s">
-        <v>130</v>
+        <v>65</v>
       </c>
       <c r="B145">
-        <v>102</v>
+        <v>116</v>
       </c>
       <c r="C145">
-        <v>1050</v>
+        <v>1151</v>
       </c>
       <c r="D145" s="1" t="s">
         <v>222</v>
@@ -5383,13 +5561,13 @@
     </row>
     <row r="146" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A146" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="B146">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C146">
-        <v>1224</v>
+        <v>1108</v>
       </c>
       <c r="D146" s="1" t="s">
         <v>222</v>
@@ -5410,13 +5588,13 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A147" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="B147">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C147">
-        <v>1167</v>
+        <v>1033</v>
       </c>
       <c r="D147" s="1" t="s">
         <v>222</v>
@@ -5437,13 +5615,13 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A148" t="s">
-        <v>199</v>
+        <v>112</v>
       </c>
       <c r="B148">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="C148">
-        <v>1134</v>
+        <v>1287</v>
       </c>
       <c r="D148" s="1" t="s">
         <v>222</v>
@@ -5464,13 +5642,13 @@
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A149" t="s">
-        <v>98</v>
+        <v>83</v>
       </c>
       <c r="B149">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C149">
-        <v>1347</v>
+        <v>1126</v>
       </c>
       <c r="D149" s="1" t="s">
         <v>222</v>
@@ -5518,13 +5696,13 @@
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A151" t="s">
-        <v>83</v>
+        <v>98</v>
       </c>
       <c r="B151">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C151">
-        <v>1126</v>
+        <v>1347</v>
       </c>
       <c r="D151" s="1" t="s">
         <v>222</v>
@@ -5545,13 +5723,13 @@
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A152" t="s">
-        <v>112</v>
+        <v>199</v>
       </c>
       <c r="B152">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C152">
-        <v>1287</v>
+        <v>1134</v>
       </c>
       <c r="D152" s="1" t="s">
         <v>222</v>
@@ -5572,13 +5750,13 @@
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A153" t="s">
-        <v>73</v>
+        <v>31</v>
       </c>
       <c r="B153">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="C153">
-        <v>1033</v>
+        <v>1167</v>
       </c>
       <c r="D153" s="1" t="s">
         <v>222</v>
@@ -5599,13 +5777,13 @@
     </row>
     <row r="154" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A154" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="B154">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="C154">
-        <v>1108</v>
+        <v>1224</v>
       </c>
       <c r="D154" s="1" t="s">
         <v>222</v>
@@ -5626,13 +5804,13 @@
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A155" t="s">
-        <v>65</v>
+        <v>130</v>
       </c>
       <c r="B155">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="C155">
-        <v>1151</v>
+        <v>1050</v>
       </c>
       <c r="D155" s="1" t="s">
         <v>222</v>
@@ -5653,13 +5831,13 @@
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A156" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B156">
-        <v>118</v>
+        <v>101</v>
       </c>
       <c r="C156">
-        <v>1257</v>
+        <v>1346</v>
       </c>
       <c r="D156" s="1" t="s">
         <v>222</v>
@@ -5680,13 +5858,13 @@
     </row>
     <row r="157" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A157" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B157">
-        <v>119</v>
+        <v>100</v>
       </c>
       <c r="C157">
-        <v>1277</v>
+        <v>1166</v>
       </c>
       <c r="D157" s="1" t="s">
         <v>222</v>
@@ -5707,13 +5885,13 @@
     </row>
     <row r="158" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A158" t="s">
-        <v>131</v>
+        <v>171</v>
       </c>
       <c r="B158">
-        <v>120</v>
+        <v>97</v>
       </c>
       <c r="C158">
-        <v>1070</v>
+        <v>1011</v>
       </c>
       <c r="D158" s="1" t="s">
         <v>222</v>
@@ -5734,13 +5912,13 @@
     </row>
     <row r="159" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A159" t="s">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="B159">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="C159">
-        <v>1234</v>
+        <v>1289</v>
       </c>
       <c r="D159" s="1" t="s">
         <v>222</v>
@@ -5761,13 +5939,13 @@
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A160" t="s">
-        <v>202</v>
+        <v>69</v>
       </c>
       <c r="B160">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="C160">
-        <v>1307</v>
+        <v>1244</v>
       </c>
       <c r="D160" s="1" t="s">
         <v>222</v>
@@ -5788,13 +5966,13 @@
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A161" t="s">
-        <v>87</v>
+        <v>119</v>
       </c>
       <c r="B161">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="C161">
-        <v>1256</v>
+        <v>1345</v>
       </c>
       <c r="D161" s="1" t="s">
         <v>222</v>
@@ -5815,13 +5993,13 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A162" t="s">
-        <v>123</v>
+        <v>15</v>
       </c>
       <c r="B162">
-        <v>125</v>
+        <v>90</v>
       </c>
       <c r="C162">
-        <v>1055</v>
+        <v>1091</v>
       </c>
       <c r="D162" s="1" t="s">
         <v>222</v>
@@ -5842,13 +6020,13 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A163" t="s">
-        <v>207</v>
+        <v>132</v>
       </c>
       <c r="B163">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="C163">
-        <v>1232</v>
+        <v>1131</v>
       </c>
       <c r="D163" s="1" t="s">
         <v>222</v>
@@ -5857,7 +6035,7 @@
         <v>225</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G163" s="2" t="s">
         <v>230</v>
@@ -5869,13 +6047,13 @@
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A164" t="s">
-        <v>21</v>
+        <v>103</v>
       </c>
       <c r="B164">
-        <v>128</v>
+        <v>87</v>
       </c>
       <c r="C164">
-        <v>1092</v>
+        <v>1247</v>
       </c>
       <c r="D164" s="1" t="s">
         <v>222</v>
@@ -5884,7 +6062,7 @@
         <v>225</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G164" s="2" t="s">
         <v>230</v>
@@ -5896,13 +6074,13 @@
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A165" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B165">
-        <v>130</v>
+        <v>86</v>
       </c>
       <c r="C165">
-        <v>1306</v>
+        <v>1073</v>
       </c>
       <c r="D165" s="1" t="s">
         <v>222</v>
@@ -5923,13 +6101,13 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A166" t="s">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="B166">
-        <v>131</v>
+        <v>84</v>
       </c>
       <c r="C166">
-        <v>1269</v>
+        <v>1129</v>
       </c>
       <c r="D166" s="1" t="s">
         <v>222</v>
@@ -5950,13 +6128,13 @@
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A167" t="s">
-        <v>33</v>
+        <v>159</v>
       </c>
       <c r="B167">
-        <v>132</v>
+        <v>83</v>
       </c>
       <c r="C167">
-        <v>1214</v>
+        <v>1192</v>
       </c>
       <c r="D167" s="1" t="s">
         <v>222</v>
@@ -5977,13 +6155,13 @@
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A168" t="s">
-        <v>209</v>
+        <v>133</v>
       </c>
       <c r="B168">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="C168">
-        <v>1111</v>
+        <v>1268</v>
       </c>
       <c r="D168" s="1" t="s">
         <v>222</v>
@@ -6004,13 +6182,13 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A169" t="s">
-        <v>126</v>
+        <v>163</v>
       </c>
       <c r="B169">
-        <v>135</v>
+        <v>81</v>
       </c>
       <c r="C169">
-        <v>1089</v>
+        <v>1237</v>
       </c>
       <c r="D169" s="1" t="s">
         <v>222</v>
@@ -6019,7 +6197,7 @@
         <v>225</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G169" s="2" t="s">
         <v>230</v>
@@ -6031,13 +6209,13 @@
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A170" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B170">
-        <v>136</v>
+        <v>79</v>
       </c>
       <c r="C170">
-        <v>1233</v>
+        <v>1128</v>
       </c>
       <c r="D170" s="1" t="s">
         <v>222</v>
@@ -6058,13 +6236,13 @@
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A171" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="B171">
-        <v>137</v>
+        <v>78</v>
       </c>
       <c r="C171">
-        <v>1170</v>
+        <v>1115</v>
       </c>
       <c r="D171" s="1" t="s">
         <v>222</v>
@@ -6085,13 +6263,13 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A172" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="B172">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="C172">
-        <v>1252</v>
+        <v>1325</v>
       </c>
       <c r="D172" s="1" t="s">
         <v>222</v>
@@ -6112,13 +6290,13 @@
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A173" t="s">
-        <v>95</v>
+        <v>55</v>
       </c>
       <c r="B173">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="C173">
-        <v>1245</v>
+        <v>1146</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>222</v>
@@ -6139,13 +6317,13 @@
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A174" t="s">
-        <v>104</v>
+        <v>45</v>
       </c>
       <c r="B174">
-        <v>145</v>
+        <v>75</v>
       </c>
       <c r="C174">
-        <v>1291</v>
+        <v>1188</v>
       </c>
       <c r="D174" s="1" t="s">
         <v>222</v>
@@ -6166,13 +6344,13 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A175" t="s">
-        <v>71</v>
+        <v>168</v>
       </c>
       <c r="B175">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="C175">
-        <v>1169</v>
+        <v>1031</v>
       </c>
       <c r="D175" s="1" t="s">
         <v>222</v>
@@ -6193,13 +6371,13 @@
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A176" t="s">
-        <v>78</v>
+        <v>215</v>
       </c>
       <c r="B176">
-        <v>149</v>
+        <v>73</v>
       </c>
       <c r="C176">
-        <v>1135</v>
+        <v>1272</v>
       </c>
       <c r="D176" s="1" t="s">
         <v>222</v>
@@ -6208,7 +6386,7 @@
         <v>225</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G176" s="2" t="s">
         <v>230</v>
@@ -6220,13 +6398,13 @@
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A177" t="s">
-        <v>124</v>
+        <v>211</v>
       </c>
       <c r="B177">
-        <v>150</v>
+        <v>72</v>
       </c>
       <c r="C177">
-        <v>1109</v>
+        <v>1127</v>
       </c>
       <c r="D177" s="1" t="s">
         <v>222</v>
@@ -6247,13 +6425,13 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A178" t="s">
-        <v>3</v>
+        <v>166</v>
       </c>
       <c r="B178">
-        <v>152</v>
+        <v>71</v>
       </c>
       <c r="C178">
-        <v>1373</v>
+        <v>1308</v>
       </c>
       <c r="D178" s="1" t="s">
         <v>222</v>
@@ -6274,13 +6452,13 @@
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A179" t="s">
-        <v>138</v>
+        <v>174</v>
       </c>
       <c r="B179">
-        <v>153</v>
+        <v>70</v>
       </c>
       <c r="C179">
-        <v>1288</v>
+        <v>1296</v>
       </c>
       <c r="D179" s="1" t="s">
         <v>222</v>
@@ -6300,48 +6478,46 @@
       <c r="N179" s="1"/>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B180" s="3">
-        <v>156</v>
-      </c>
-      <c r="C180" s="3">
-        <v>1197</v>
-      </c>
-      <c r="D180" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E180" s="4" t="s">
+      <c r="A180" t="s">
+        <v>8</v>
+      </c>
+      <c r="B180">
+        <v>69</v>
+      </c>
+      <c r="C180">
+        <v>1353</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E180" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="G180" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H180" s="3"/>
-      <c r="I180" s="3"/>
-      <c r="K180" s="4"/>
+      <c r="K180" s="1"/>
       <c r="L180" s="2"/>
       <c r="M180" s="2"/>
-      <c r="N180" s="4"/>
+      <c r="N180" s="1"/>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A181" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B181" s="3">
-        <v>157</v>
-      </c>
-      <c r="C181" s="3">
-        <v>1155</v>
-      </c>
-      <c r="D181" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E181" s="4" t="s">
+      <c r="A181" t="s">
+        <v>63</v>
+      </c>
+      <c r="B181">
+        <v>68</v>
+      </c>
+      <c r="C181">
+        <v>1251</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E181" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F181" s="2" t="s">
@@ -6350,27 +6526,25 @@
       <c r="G181" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H181" s="3"/>
-      <c r="I181" s="3"/>
-      <c r="K181" s="4"/>
+      <c r="K181" s="1"/>
       <c r="L181" s="2"/>
       <c r="M181" s="2"/>
-      <c r="N181" s="4"/>
+      <c r="N181" s="1"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A182" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B182" s="3">
-        <v>159</v>
-      </c>
-      <c r="C182" s="3">
-        <v>1312</v>
-      </c>
-      <c r="D182" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E182" s="4" t="s">
+      <c r="A182" t="s">
+        <v>49</v>
+      </c>
+      <c r="B182">
+        <v>66</v>
+      </c>
+      <c r="C182">
+        <v>1313</v>
+      </c>
+      <c r="D182" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E182" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F182" s="2" t="s">
@@ -6379,27 +6553,25 @@
       <c r="G182" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H182" s="3"/>
-      <c r="I182" s="3"/>
-      <c r="K182" s="4"/>
+      <c r="K182" s="1"/>
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
-      <c r="N182" s="4"/>
+      <c r="N182" s="1"/>
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A183" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B183" s="3">
-        <v>163</v>
-      </c>
-      <c r="C183" s="3">
-        <v>1148</v>
-      </c>
-      <c r="D183" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E183" s="4" t="s">
+      <c r="A183" t="s">
+        <v>48</v>
+      </c>
+      <c r="B183">
+        <v>65</v>
+      </c>
+      <c r="C183">
+        <v>1074</v>
+      </c>
+      <c r="D183" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E183" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F183" s="2" t="s">
@@ -6408,27 +6580,25 @@
       <c r="G183" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H183" s="3"/>
-      <c r="I183" s="3"/>
-      <c r="K183" s="4"/>
+      <c r="K183" s="1"/>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
-      <c r="N183" s="4"/>
+      <c r="N183" s="1"/>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A184" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B184" s="3">
-        <v>164</v>
-      </c>
-      <c r="C184" s="3">
-        <v>1149</v>
-      </c>
-      <c r="D184" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E184" s="4" t="s">
+      <c r="A184" t="s">
+        <v>114</v>
+      </c>
+      <c r="B184">
+        <v>64</v>
+      </c>
+      <c r="C184">
+        <v>1265</v>
+      </c>
+      <c r="D184" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E184" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F184" s="2" t="s">
@@ -6437,27 +6607,25 @@
       <c r="G184" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H184" s="3"/>
-      <c r="I184" s="3"/>
-      <c r="K184" s="4"/>
+      <c r="K184" s="1"/>
       <c r="L184" s="2"/>
       <c r="M184" s="2"/>
-      <c r="N184" s="4"/>
+      <c r="N184" s="1"/>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A185" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B185" s="3">
-        <v>165</v>
-      </c>
-      <c r="C185" s="3">
-        <v>1168</v>
-      </c>
-      <c r="D185" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E185" s="4" t="s">
+      <c r="A185" t="s">
+        <v>27</v>
+      </c>
+      <c r="B185">
+        <v>61</v>
+      </c>
+      <c r="C185">
+        <v>1309</v>
+      </c>
+      <c r="D185" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E185" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F185" s="2" t="s">
@@ -6466,27 +6634,25 @@
       <c r="G185" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H185" s="3"/>
-      <c r="I185" s="3"/>
-      <c r="K185" s="4"/>
+      <c r="K185" s="1"/>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
-      <c r="N185" s="4"/>
+      <c r="N185" s="1"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A186" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B186" s="3">
-        <v>166</v>
-      </c>
-      <c r="C186" s="3">
-        <v>1173</v>
-      </c>
-      <c r="D186" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E186" s="4" t="s">
+      <c r="A186" t="s">
+        <v>181</v>
+      </c>
+      <c r="B186">
+        <v>57</v>
+      </c>
+      <c r="C186">
+        <v>1093</v>
+      </c>
+      <c r="D186" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E186" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F186" s="2" t="s">
@@ -6495,27 +6661,25 @@
       <c r="G186" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H186" s="3"/>
-      <c r="I186" s="3"/>
-      <c r="K186" s="4"/>
+      <c r="K186" s="1"/>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
-      <c r="N186" s="4"/>
+      <c r="N186" s="1"/>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A187" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B187" s="3">
-        <v>167</v>
-      </c>
-      <c r="C187" s="3">
-        <v>1210</v>
-      </c>
-      <c r="D187" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E187" s="4" t="s">
+      <c r="A187" t="s">
+        <v>219</v>
+      </c>
+      <c r="B187">
+        <v>56</v>
+      </c>
+      <c r="C187">
+        <v>1235</v>
+      </c>
+      <c r="D187" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E187" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F187" s="2" t="s">
@@ -6524,27 +6688,25 @@
       <c r="G187" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H187" s="3"/>
-      <c r="I187" s="3"/>
-      <c r="K187" s="4"/>
+      <c r="K187" s="1"/>
       <c r="L187" s="2"/>
       <c r="M187" s="2"/>
-      <c r="N187" s="4"/>
+      <c r="N187" s="1"/>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A188" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B188" s="3">
-        <v>168</v>
-      </c>
-      <c r="C188" s="3">
-        <v>1110</v>
-      </c>
-      <c r="D188" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E188" s="4" t="s">
+      <c r="A188" t="s">
+        <v>94</v>
+      </c>
+      <c r="B188">
+        <v>54</v>
+      </c>
+      <c r="C188">
+        <v>1054</v>
+      </c>
+      <c r="D188" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E188" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F188" s="2" t="s">
@@ -6553,27 +6715,25 @@
       <c r="G188" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H188" s="3"/>
-      <c r="I188" s="3"/>
-      <c r="K188" s="4"/>
+      <c r="K188" s="1"/>
       <c r="L188" s="2"/>
       <c r="M188" s="2"/>
-      <c r="N188" s="4"/>
+      <c r="N188" s="1"/>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A189" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B189" s="3">
-        <v>170</v>
-      </c>
-      <c r="C189" s="3">
-        <v>1209</v>
-      </c>
-      <c r="D189" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E189" s="4" t="s">
+      <c r="A189" t="s">
+        <v>167</v>
+      </c>
+      <c r="B189">
+        <v>53</v>
+      </c>
+      <c r="C189">
+        <v>1133</v>
+      </c>
+      <c r="D189" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E189" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F189" s="2" t="s">
@@ -6582,27 +6742,25 @@
       <c r="G189" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H189" s="3"/>
-      <c r="I189" s="3"/>
-      <c r="K189" s="4"/>
+      <c r="K189" s="1"/>
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
-      <c r="N189" s="4"/>
+      <c r="N189" s="1"/>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A190" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B190" s="3">
-        <v>171</v>
-      </c>
-      <c r="C190" s="3">
-        <v>1208</v>
-      </c>
-      <c r="D190" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="E190" s="4" t="s">
+      <c r="A190" t="s">
+        <v>76</v>
+      </c>
+      <c r="B190">
+        <v>52</v>
+      </c>
+      <c r="C190">
+        <v>1052</v>
+      </c>
+      <c r="D190" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E190" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F190" s="2" t="s">
@@ -6611,22 +6769,20 @@
       <c r="G190" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="H190" s="3"/>
-      <c r="I190" s="3"/>
-      <c r="K190" s="4"/>
+      <c r="K190" s="1"/>
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
-      <c r="N190" s="4"/>
+      <c r="N190" s="1"/>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A191" t="s">
-        <v>220</v>
+        <v>18</v>
       </c>
       <c r="B191">
-        <v>174</v>
+        <v>50</v>
       </c>
       <c r="C191">
-        <v>1230</v>
+        <v>1090</v>
       </c>
       <c r="D191" s="1" t="s">
         <v>222</v>
@@ -6647,13 +6803,13 @@
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A192" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="B192">
-        <v>175</v>
+        <v>47</v>
       </c>
       <c r="C192">
-        <v>1152</v>
+        <v>1264</v>
       </c>
       <c r="D192" s="1" t="s">
         <v>222</v>
@@ -6674,13 +6830,13 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A193" t="s">
-        <v>90</v>
+        <v>187</v>
       </c>
       <c r="B193">
-        <v>177</v>
+        <v>45</v>
       </c>
       <c r="C193">
-        <v>1207</v>
+        <v>1075</v>
       </c>
       <c r="D193" s="1" t="s">
         <v>222</v>
@@ -6701,13 +6857,13 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A194" t="s">
-        <v>72</v>
+        <v>169</v>
       </c>
       <c r="B194">
-        <v>1153</v>
+        <v>44</v>
       </c>
       <c r="C194">
-        <v>1153</v>
+        <v>1199</v>
       </c>
       <c r="D194" s="1" t="s">
         <v>222</v>
@@ -6716,7 +6872,7 @@
         <v>225</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G194" s="2" t="s">
         <v>230</v>
@@ -6728,13 +6884,13 @@
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A195" t="s">
-        <v>173</v>
+        <v>40</v>
       </c>
       <c r="B195">
-        <v>1154</v>
+        <v>43</v>
       </c>
       <c r="C195">
-        <v>1154</v>
+        <v>1328</v>
       </c>
       <c r="D195" s="1" t="s">
         <v>222</v>
@@ -6743,7 +6899,7 @@
         <v>225</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G195" s="2" t="s">
         <v>230</v>
@@ -6755,13 +6911,13 @@
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A196" t="s">
-        <v>146</v>
+        <v>189</v>
       </c>
       <c r="B196">
-        <v>1156</v>
+        <v>41</v>
       </c>
       <c r="C196">
-        <v>1156</v>
+        <v>1266</v>
       </c>
       <c r="D196" s="1" t="s">
         <v>222</v>
@@ -6770,7 +6926,7 @@
         <v>225</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G196" s="2" t="s">
         <v>230</v>
@@ -6782,13 +6938,13 @@
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A197" t="s">
+        <v>214</v>
+      </c>
+      <c r="B197">
         <v>39</v>
       </c>
-      <c r="B197">
-        <v>1177</v>
-      </c>
       <c r="C197">
-        <v>1177</v>
+        <v>1333</v>
       </c>
       <c r="D197" s="1" t="s">
         <v>222</v>
@@ -6797,7 +6953,7 @@
         <v>225</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G197" s="2" t="s">
         <v>230</v>
@@ -6809,13 +6965,13 @@
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A198" t="s">
-        <v>206</v>
+        <v>34</v>
       </c>
       <c r="B198">
-        <v>1179</v>
+        <v>38</v>
       </c>
       <c r="C198">
-        <v>1179</v>
+        <v>1032</v>
       </c>
       <c r="D198" s="1" t="s">
         <v>222</v>
@@ -6824,7 +6980,7 @@
         <v>225</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>230</v>
@@ -6836,13 +6992,13 @@
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A199" t="s">
-        <v>212</v>
+        <v>117</v>
       </c>
       <c r="B199">
-        <v>1193</v>
+        <v>37</v>
       </c>
       <c r="C199">
-        <v>1193</v>
+        <v>1284</v>
       </c>
       <c r="D199" s="1" t="s">
         <v>222</v>
@@ -6851,7 +7007,7 @@
         <v>225</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G199" s="2" t="s">
         <v>230</v>
@@ -6863,13 +7019,13 @@
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A200" t="s">
-        <v>178</v>
+        <v>113</v>
       </c>
       <c r="B200">
-        <v>1194</v>
+        <v>35</v>
       </c>
       <c r="C200">
-        <v>1194</v>
+        <v>1286</v>
       </c>
       <c r="D200" s="1" t="s">
         <v>222</v>
@@ -6878,7 +7034,7 @@
         <v>225</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G200" s="2" t="s">
         <v>230</v>
@@ -6890,13 +7046,13 @@
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A201" t="s">
-        <v>108</v>
+        <v>191</v>
       </c>
       <c r="B201">
-        <v>1196</v>
+        <v>34</v>
       </c>
       <c r="C201">
-        <v>1196</v>
+        <v>1271</v>
       </c>
       <c r="D201" s="1" t="s">
         <v>222</v>
@@ -6905,7 +7061,7 @@
         <v>225</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G201" s="2" t="s">
         <v>230</v>
@@ -6917,13 +7073,13 @@
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A202" t="s">
-        <v>16</v>
+        <v>58</v>
       </c>
       <c r="B202">
-        <v>1213</v>
+        <v>33</v>
       </c>
       <c r="C202">
-        <v>1213</v>
+        <v>1365</v>
       </c>
       <c r="D202" s="1" t="s">
         <v>222</v>
@@ -6932,7 +7088,7 @@
         <v>225</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G202" s="2" t="s">
         <v>230</v>
@@ -6944,13 +7100,13 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A203" t="s">
-        <v>180</v>
+        <v>122</v>
       </c>
       <c r="B203">
-        <v>1216</v>
+        <v>32</v>
       </c>
       <c r="C203">
-        <v>1216</v>
+        <v>1267</v>
       </c>
       <c r="D203" s="1" t="s">
         <v>222</v>
@@ -6959,7 +7115,7 @@
         <v>225</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G203" s="2" t="s">
         <v>230</v>
@@ -6971,13 +7127,13 @@
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A204" t="s">
-        <v>205</v>
+        <v>37</v>
       </c>
       <c r="B204">
-        <v>1219</v>
+        <v>30</v>
       </c>
       <c r="C204">
-        <v>1219</v>
+        <v>1349</v>
       </c>
       <c r="D204" s="1" t="s">
         <v>222</v>
@@ -6986,7 +7142,7 @@
         <v>225</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G204" s="2" t="s">
         <v>230</v>
@@ -6998,13 +7154,13 @@
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A205" t="s">
-        <v>177</v>
+        <v>46</v>
       </c>
       <c r="B205">
-        <v>1227</v>
+        <v>29</v>
       </c>
       <c r="C205">
-        <v>1227</v>
+        <v>1348</v>
       </c>
       <c r="D205" s="1" t="s">
         <v>222</v>
@@ -7013,7 +7169,7 @@
         <v>225</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>230</v>
@@ -7025,13 +7181,13 @@
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A206" t="s">
-        <v>161</v>
+        <v>29</v>
       </c>
       <c r="B206">
-        <v>1236</v>
+        <v>28</v>
       </c>
       <c r="C206">
-        <v>1236</v>
+        <v>1150</v>
       </c>
       <c r="D206" s="1" t="s">
         <v>222</v>
@@ -7040,7 +7196,7 @@
         <v>225</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G206" s="2" t="s">
         <v>230</v>
@@ -7052,13 +7208,13 @@
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A207" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="B207">
-        <v>1238</v>
+        <v>24</v>
       </c>
       <c r="C207">
-        <v>1238</v>
+        <v>1324</v>
       </c>
       <c r="D207" s="1" t="s">
         <v>222</v>
@@ -7067,7 +7223,7 @@
         <v>225</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G207" s="2" t="s">
         <v>230</v>
@@ -7079,13 +7235,13 @@
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A208" t="s">
-        <v>182</v>
+        <v>221</v>
       </c>
       <c r="B208">
-        <v>1239</v>
+        <v>23</v>
       </c>
       <c r="C208">
-        <v>1239</v>
+        <v>1095</v>
       </c>
       <c r="D208" s="1" t="s">
         <v>222</v>
@@ -7094,7 +7250,7 @@
         <v>225</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G208" s="2" t="s">
         <v>230</v>
@@ -7106,13 +7262,13 @@
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A209" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="B209">
-        <v>1248</v>
+        <v>22</v>
       </c>
       <c r="C209">
-        <v>1248</v>
+        <v>1147</v>
       </c>
       <c r="D209" s="1" t="s">
         <v>222</v>
@@ -7121,7 +7277,7 @@
         <v>225</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G209" s="2" t="s">
         <v>230</v>
@@ -7133,13 +7289,13 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A210" t="s">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="B210">
-        <v>1253</v>
+        <v>21</v>
       </c>
       <c r="C210">
-        <v>1253</v>
+        <v>1187</v>
       </c>
       <c r="D210" s="1" t="s">
         <v>222</v>
@@ -7148,7 +7304,7 @@
         <v>225</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G210" s="2" t="s">
         <v>230</v>
@@ -7160,13 +7316,13 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A211" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="B211">
-        <v>1255</v>
+        <v>20</v>
       </c>
       <c r="C211">
-        <v>1255</v>
+        <v>1218</v>
       </c>
       <c r="D211" s="1" t="s">
         <v>222</v>
@@ -7175,7 +7331,7 @@
         <v>225</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G211" s="2" t="s">
         <v>230</v>
@@ -7187,13 +7343,13 @@
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A212" t="s">
-        <v>106</v>
+        <v>183</v>
       </c>
       <c r="B212">
-        <v>1258</v>
+        <v>18</v>
       </c>
       <c r="C212">
-        <v>1258</v>
+        <v>1130</v>
       </c>
       <c r="D212" s="1" t="s">
         <v>222</v>
@@ -7202,7 +7358,7 @@
         <v>225</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G212" s="2" t="s">
         <v>230</v>
@@ -7214,13 +7370,13 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A213" t="s">
-        <v>128</v>
+        <v>62</v>
       </c>
       <c r="B213">
-        <v>1274</v>
+        <v>16</v>
       </c>
       <c r="C213">
-        <v>1274</v>
+        <v>1053</v>
       </c>
       <c r="D213" s="1" t="s">
         <v>222</v>
@@ -7229,7 +7385,7 @@
         <v>225</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G213" s="2" t="s">
         <v>230</v>
@@ -7240,25 +7396,25 @@
       <c r="N213" s="1"/>
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A214" t="s">
-        <v>28</v>
-      </c>
-      <c r="B214">
-        <v>1278</v>
-      </c>
-      <c r="C214">
-        <v>1278</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="E214" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="F214" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="G214" s="2" t="s">
+      <c r="A214" s="24" t="s">
+        <v>127</v>
+      </c>
+      <c r="B214" s="24">
+        <v>14</v>
+      </c>
+      <c r="C214" s="24">
+        <v>1198</v>
+      </c>
+      <c r="D214" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E214" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="F214" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="G214" s="26" t="s">
         <v>230</v>
       </c>
       <c r="K214" s="1"/>
@@ -7268,13 +7424,13 @@
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A215" t="s">
-        <v>70</v>
+        <v>32</v>
       </c>
       <c r="B215">
-        <v>1290</v>
+        <v>13</v>
       </c>
       <c r="C215">
-        <v>1290</v>
+        <v>1229</v>
       </c>
       <c r="D215" s="1" t="s">
         <v>222</v>
@@ -7283,7 +7439,7 @@
         <v>225</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G215" s="2" t="s">
         <v>230</v>
@@ -7295,13 +7451,13 @@
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A216" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="B216">
-        <v>1292</v>
+        <v>11</v>
       </c>
       <c r="C216">
-        <v>1292</v>
+        <v>1314</v>
       </c>
       <c r="D216" s="1" t="s">
         <v>222</v>
@@ -7310,7 +7466,7 @@
         <v>225</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G216" s="2" t="s">
         <v>230</v>
@@ -7322,13 +7478,13 @@
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A217" t="s">
-        <v>196</v>
+        <v>51</v>
       </c>
       <c r="B217">
-        <v>1298</v>
+        <v>9</v>
       </c>
       <c r="C217">
-        <v>1298</v>
+        <v>1217</v>
       </c>
       <c r="D217" s="1" t="s">
         <v>222</v>
@@ -7337,7 +7493,7 @@
         <v>225</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G217" s="2" t="s">
         <v>230</v>
@@ -7349,13 +7505,13 @@
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A218" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="B218">
-        <v>1311</v>
+        <v>8</v>
       </c>
       <c r="C218">
-        <v>1311</v>
+        <v>1304</v>
       </c>
       <c r="D218" s="1" t="s">
         <v>222</v>
@@ -7364,7 +7520,7 @@
         <v>225</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G218" s="2" t="s">
         <v>230</v>
@@ -7376,13 +7532,13 @@
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A219" t="s">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="B219">
-        <v>1326</v>
+        <v>7</v>
       </c>
       <c r="C219">
-        <v>1326</v>
+        <v>1112</v>
       </c>
       <c r="D219" s="1" t="s">
         <v>222</v>
@@ -7391,7 +7547,7 @@
         <v>225</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G219" s="2" t="s">
         <v>230</v>
@@ -7403,13 +7559,13 @@
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A220" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B220">
-        <v>1332</v>
+        <v>6</v>
       </c>
       <c r="C220">
-        <v>1332</v>
+        <v>1228</v>
       </c>
       <c r="D220" s="1" t="s">
         <v>222</v>
@@ -7418,7 +7574,7 @@
         <v>225</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G220" s="2" t="s">
         <v>230</v>
@@ -7430,28 +7586,25 @@
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A221" t="s">
-        <v>218</v>
+        <v>85</v>
       </c>
       <c r="B221">
-        <v>1246</v>
+        <v>4</v>
       </c>
       <c r="C221">
-        <v>1246</v>
+        <v>1094</v>
       </c>
       <c r="D221" s="1" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="E221" s="1" t="s">
         <v>225</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G221" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="H221" t="s">
-        <v>239</v>
       </c>
       <c r="K221" s="1"/>
       <c r="L221" s="2"/>
@@ -7460,8 +7613,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N221">
-    <sortCondition descending="1" ref="E2:E221"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N225">
+    <sortCondition descending="1" ref="E2:E225"/>
+    <sortCondition ref="I2:I225"/>
+    <sortCondition descending="1" ref="B2:B225"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/gcover/data/GC_Sources_PA.xlsx
+++ b/src/gcover/data/GC_Sources_PA.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\v0t0020a.adr.admin.ch\lg\01_PRODUKTION\GIS\TOPGIS\Produktableitung\R17_2026\Excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{549AA853-4802-4A2E-86CF-6419B054669F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44F0F06C-3DB4-4E9C-BE3D-33A16D28B112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -82,7 +82,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="251">
   <si>
     <t>MSH_MAP_TITLE</t>
   </si>
@@ -804,9 +804,6 @@
     <t>RC1 = RC2, incomplètes (travaux Luc débutés dans TopGIS..)</t>
   </si>
   <si>
-    <t>Selon planning</t>
-  </si>
-  <si>
     <t>Mapsheet Val Bregaglia + Campodolcino fusionnés (feuille Campodolcino supprimée). Selon planning</t>
   </si>
   <si>
@@ -832,6 +829,12 @@
   </si>
   <si>
     <t>sans points</t>
+  </si>
+  <si>
+    <t>sans points + contrôle auteurs nécessaire</t>
+  </si>
+  <si>
+    <t>pas prêt</t>
   </si>
 </sst>
 </file>
@@ -869,7 +872,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -891,24 +894,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -937,7 +922,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -976,47 +961,20 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1302,17 +1260,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:N221"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.5703125" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.42578125" style="1" customWidth="1"/>
-    <col min="6" max="7" width="11.42578125" style="2"/>
-    <col min="8" max="8" width="28.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.54296875" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.453125" style="1" customWidth="1"/>
+    <col min="6" max="7" width="11.453125" style="2"/>
+    <col min="8" max="8" width="28.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:14" ht="13" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -1335,10 +1293,10 @@
         <v>233</v>
       </c>
       <c r="H1" s="14" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="I1" s="14" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J1" s="1"/>
       <c r="K1" s="2"/>
@@ -1346,7 +1304,7 @@
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>36</v>
       </c>
@@ -1372,14 +1330,14 @@
         <v>238</v>
       </c>
       <c r="I2" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>194</v>
       </c>
@@ -1402,14 +1360,14 @@
         <v>230</v>
       </c>
       <c r="I3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K3" s="1"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
       <c r="N3" s="1"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>129</v>
       </c>
@@ -1433,14 +1391,14 @@
       </c>
       <c r="H4" s="3"/>
       <c r="I4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K4" s="1"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>20</v>
       </c>
@@ -1464,14 +1422,14 @@
       </c>
       <c r="H5" s="3"/>
       <c r="I5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K5" s="1"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
       <c r="N5" s="4"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>154</v>
       </c>
@@ -1495,14 +1453,14 @@
       </c>
       <c r="H6" s="3"/>
       <c r="I6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K6" s="4"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="4"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>188</v>
       </c>
@@ -1525,14 +1483,14 @@
         <v>229</v>
       </c>
       <c r="I7" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="1"/>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>96</v>
       </c>
@@ -1555,14 +1513,14 @@
         <v>229</v>
       </c>
       <c r="I8" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K8" s="1"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="1"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>139</v>
       </c>
@@ -1585,14 +1543,14 @@
         <v>229</v>
       </c>
       <c r="I9" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K9" s="1"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="1"/>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>201</v>
       </c>
@@ -1615,14 +1573,14 @@
         <v>229</v>
       </c>
       <c r="I10" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K10" s="1"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="1"/>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>111</v>
       </c>
@@ -1645,14 +1603,14 @@
         <v>229</v>
       </c>
       <c r="I11" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K11" s="1"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="1"/>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>110</v>
       </c>
@@ -1675,14 +1633,14 @@
         <v>229</v>
       </c>
       <c r="I12" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K12" s="1"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="1"/>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>149</v>
       </c>
@@ -1705,14 +1663,14 @@
         <v>229</v>
       </c>
       <c r="I13" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K13" s="1"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="1"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>185</v>
       </c>
@@ -1735,14 +1693,14 @@
         <v>229</v>
       </c>
       <c r="I14" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K14" s="1"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="1"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>115</v>
       </c>
@@ -1765,14 +1723,14 @@
         <v>229</v>
       </c>
       <c r="I15" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K15" s="1"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="1"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>99</v>
       </c>
@@ -1795,14 +1753,14 @@
         <v>229</v>
       </c>
       <c r="I16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K16" s="1"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="1"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>155</v>
       </c>
@@ -1825,14 +1783,14 @@
         <v>229</v>
       </c>
       <c r="I17" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K17" s="1"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="1"/>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>148</v>
       </c>
@@ -1855,14 +1813,14 @@
         <v>229</v>
       </c>
       <c r="I18" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K18" s="1"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="1"/>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>176</v>
       </c>
@@ -1885,14 +1843,14 @@
         <v>229</v>
       </c>
       <c r="I19" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K19" s="1"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="1"/>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>107</v>
       </c>
@@ -1915,14 +1873,14 @@
         <v>229</v>
       </c>
       <c r="I20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K20" s="1"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="1"/>
     </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>157</v>
       </c>
@@ -1945,14 +1903,14 @@
         <v>229</v>
       </c>
       <c r="I21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K21" s="1"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="1"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>25</v>
       </c>
@@ -1975,14 +1933,14 @@
         <v>229</v>
       </c>
       <c r="I22" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K22" s="1"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>64</v>
       </c>
@@ -2005,14 +1963,14 @@
         <v>229</v>
       </c>
       <c r="I23" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K23" s="1"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="1"/>
     </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>86</v>
       </c>
@@ -2035,14 +1993,14 @@
         <v>229</v>
       </c>
       <c r="I24" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K24" s="1"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>140</v>
       </c>
@@ -2065,14 +2023,14 @@
         <v>229</v>
       </c>
       <c r="I25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K25" s="1"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
       <c r="N25" s="1"/>
     </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>192</v>
       </c>
@@ -2095,14 +2053,14 @@
         <v>229</v>
       </c>
       <c r="I26" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K26" s="1"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>144</v>
       </c>
@@ -2125,14 +2083,14 @@
         <v>229</v>
       </c>
       <c r="I27" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K27" s="1"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
       <c r="N27" s="1"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>91</v>
       </c>
@@ -2155,14 +2113,14 @@
         <v>229</v>
       </c>
       <c r="I28" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K28" s="1"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
       <c r="N28" s="1"/>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>24</v>
       </c>
@@ -2185,14 +2143,14 @@
         <v>229</v>
       </c>
       <c r="I29" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K29" s="1"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
       <c r="N29" s="1"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>158</v>
       </c>
@@ -2215,14 +2173,14 @@
         <v>229</v>
       </c>
       <c r="I30" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K30" s="1"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
       <c r="N30" s="1"/>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>145</v>
       </c>
@@ -2245,14 +2203,14 @@
         <v>229</v>
       </c>
       <c r="I31" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K31" s="1"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
       <c r="N31" s="1"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>198</v>
       </c>
@@ -2275,14 +2233,14 @@
         <v>229</v>
       </c>
       <c r="I32" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K32" s="1"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>105</v>
       </c>
@@ -2305,14 +2263,14 @@
         <v>229</v>
       </c>
       <c r="I33" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K33" s="1"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
       <c r="N33" s="1"/>
     </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>38</v>
       </c>
@@ -2335,14 +2293,14 @@
         <v>229</v>
       </c>
       <c r="I34" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K34" s="1"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
       <c r="N34" s="1"/>
     </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>4</v>
       </c>
@@ -2365,14 +2323,14 @@
         <v>229</v>
       </c>
       <c r="I35" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K35" s="1"/>
       <c r="L35" s="2"/>
       <c r="M35" s="2"/>
       <c r="N35" s="1"/>
     </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>7</v>
       </c>
@@ -2395,14 +2353,14 @@
         <v>229</v>
       </c>
       <c r="I36" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K36" s="1"/>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
       <c r="N36" s="1"/>
     </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>160</v>
       </c>
@@ -2425,14 +2383,14 @@
         <v>229</v>
       </c>
       <c r="I37" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K37" s="1"/>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
       <c r="N37" s="1"/>
     </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>100</v>
       </c>
@@ -2455,14 +2413,14 @@
         <v>229</v>
       </c>
       <c r="I38" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K38" s="1"/>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
       <c r="N38" s="1"/>
     </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>200</v>
       </c>
@@ -2485,14 +2443,14 @@
         <v>229</v>
       </c>
       <c r="I39" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K39" s="1"/>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
       <c r="N39" s="1"/>
     </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>152</v>
       </c>
@@ -2515,14 +2473,14 @@
         <v>229</v>
       </c>
       <c r="I40" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K40" s="1"/>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="1"/>
     </row>
-    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>54</v>
       </c>
@@ -2545,14 +2503,14 @@
         <v>229</v>
       </c>
       <c r="I41" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K41" s="1"/>
       <c r="L41" s="2"/>
       <c r="M41" s="2"/>
       <c r="N41" s="1"/>
     </row>
-    <row r="42" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>35</v>
       </c>
@@ -2575,14 +2533,14 @@
         <v>229</v>
       </c>
       <c r="I42" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K42" s="1"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
       <c r="N42" s="1"/>
     </row>
-    <row r="43" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>164</v>
       </c>
@@ -2605,14 +2563,14 @@
         <v>229</v>
       </c>
       <c r="I43" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K43" s="1"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="1"/>
     </row>
-    <row r="44" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>150</v>
       </c>
@@ -2635,14 +2593,14 @@
         <v>229</v>
       </c>
       <c r="I44" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K44" s="1"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="1"/>
     </row>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>120</v>
       </c>
@@ -2665,14 +2623,14 @@
         <v>229</v>
       </c>
       <c r="I45" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="1"/>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="8" t="s">
         <v>22</v>
       </c>
@@ -2696,14 +2654,14 @@
       </c>
       <c r="H46" s="3"/>
       <c r="I46" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K46" s="4"/>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="1"/>
     </row>
-    <row r="47" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="s">
         <v>125</v>
       </c>
@@ -2726,14 +2684,14 @@
         <v>229</v>
       </c>
       <c r="I47" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K47" s="4"/>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
       <c r="N47" s="1"/>
     </row>
-    <row r="48" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
         <v>208</v>
       </c>
@@ -2756,14 +2714,14 @@
         <v>229</v>
       </c>
       <c r="I48" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
       <c r="N48" s="1"/>
     </row>
-    <row r="49" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
         <v>23</v>
       </c>
@@ -2786,14 +2744,14 @@
         <v>229</v>
       </c>
       <c r="I49" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="1"/>
     </row>
-    <row r="50" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
         <v>5</v>
       </c>
@@ -2816,14 +2774,14 @@
         <v>229</v>
       </c>
       <c r="I50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K50" s="4"/>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
       <c r="N50" s="1"/>
     </row>
-    <row r="51" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
         <v>141</v>
       </c>
@@ -2846,14 +2804,14 @@
         <v>229</v>
       </c>
       <c r="I51" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K51" s="4"/>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
       <c r="N51" s="1"/>
     </row>
-    <row r="52" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
         <v>19</v>
       </c>
@@ -2876,14 +2834,14 @@
         <v>229</v>
       </c>
       <c r="I52" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
       <c r="N52" s="1"/>
     </row>
-    <row r="53" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
         <v>179</v>
       </c>
@@ -2906,587 +2864,527 @@
         <v>229</v>
       </c>
       <c r="I53" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="K53" s="4"/>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
       <c r="N53" s="1"/>
     </row>
-    <row r="54" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A54" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="B54" s="20">
-        <v>1294</v>
-      </c>
-      <c r="C54" s="20">
-        <v>1294</v>
-      </c>
-      <c r="D54" s="16" t="s">
-        <v>223</v>
-      </c>
-      <c r="E54" s="16" t="s">
+    <row r="54" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A54" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="B54" s="16">
+        <v>1276</v>
+      </c>
+      <c r="C54" s="16">
+        <v>1276</v>
+      </c>
+      <c r="D54" s="20" t="s">
+        <v>222</v>
+      </c>
+      <c r="E54" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F54" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="G54" s="22" t="s">
+      <c r="F54" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G54" s="19" t="s">
         <v>230</v>
       </c>
       <c r="H54" t="s">
         <v>240</v>
       </c>
       <c r="I54" t="s">
-        <v>246</v>
-      </c>
-      <c r="J54" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
       <c r="N54" s="1"/>
     </row>
-    <row r="55" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A55" s="27" t="s">
-        <v>59</v>
-      </c>
-      <c r="B55" s="27">
-        <v>1276</v>
-      </c>
-      <c r="C55" s="27">
-        <v>1276</v>
-      </c>
-      <c r="D55" s="31" t="s">
-        <v>222</v>
-      </c>
-      <c r="E55" s="28" t="s">
+    <row r="55" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A55" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="B55" s="16">
+        <v>1273</v>
+      </c>
+      <c r="C55" s="16">
+        <v>1273</v>
+      </c>
+      <c r="D55" s="18" t="s">
+        <v>223</v>
+      </c>
+      <c r="E55" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F55" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="G55" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H55" t="s">
-        <v>241</v>
+      <c r="F55" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G55" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I55" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A56" s="27" t="s">
-        <v>210</v>
-      </c>
-      <c r="B56" s="27">
-        <v>1273</v>
-      </c>
-      <c r="C56" s="27">
-        <v>1273</v>
-      </c>
-      <c r="D56" s="29" t="s">
+      <c r="N55" s="4"/>
+    </row>
+    <row r="56" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A56" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B56" s="16">
+        <v>1189</v>
+      </c>
+      <c r="C56" s="16">
+        <v>1189</v>
+      </c>
+      <c r="D56" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="E56" s="28" t="s">
+      <c r="E56" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F56" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="G56" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H56" t="s">
-        <v>240</v>
+      <c r="F56" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G56" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I56" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
       <c r="N56" s="4"/>
     </row>
-    <row r="57" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A57" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="B57" s="20">
-        <v>1254</v>
-      </c>
-      <c r="C57" s="20">
-        <v>1254</v>
-      </c>
-      <c r="D57" s="16" t="s">
+    <row r="57" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A57" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1176</v>
+      </c>
+      <c r="C57" s="16">
+        <v>1176</v>
+      </c>
+      <c r="D57" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E57" s="16" t="s">
+      <c r="E57" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F57" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="G57" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="H57" t="s">
-        <v>240</v>
+      <c r="F57" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G57" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I57" t="s">
-        <v>246</v>
-      </c>
-      <c r="J57" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
       <c r="N57" s="1"/>
     </row>
-    <row r="58" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A58" s="20" t="s">
-        <v>10</v>
-      </c>
-      <c r="B58" s="20">
-        <v>1191</v>
-      </c>
-      <c r="C58" s="20">
-        <v>1191</v>
-      </c>
-      <c r="D58" s="15" t="s">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A58" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1171</v>
+      </c>
+      <c r="C58" s="16">
+        <v>1171</v>
+      </c>
+      <c r="D58" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E58" s="16" t="s">
+      <c r="E58" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F58" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="G58" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="H58" t="s">
-        <v>240</v>
+      <c r="F58" s="19" t="s">
+        <v>230</v>
+      </c>
+      <c r="G58" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I58" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J58" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="1"/>
     </row>
-    <row r="59" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A59" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="B59" s="20">
-        <v>1189</v>
-      </c>
-      <c r="C59" s="20">
-        <v>1189</v>
-      </c>
-      <c r="D59" s="18" t="s">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A59" s="16" t="s">
+        <v>217</v>
+      </c>
+      <c r="B59" s="16">
+        <v>178</v>
+      </c>
+      <c r="C59" s="16">
+        <v>1175</v>
+      </c>
+      <c r="D59" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E59" s="16" t="s">
+      <c r="E59" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F59" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="G59" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="H59" t="s">
-        <v>240</v>
+      <c r="F59" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G59" s="19" t="s">
+        <v>229</v>
       </c>
       <c r="I59" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
-      <c r="N59" s="4"/>
-    </row>
-    <row r="60" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A60" s="20" t="s">
-        <v>89</v>
-      </c>
-      <c r="B60" s="20">
-        <v>1176</v>
-      </c>
-      <c r="C60" s="20">
-        <v>1176</v>
-      </c>
-      <c r="D60" s="19" t="s">
+      <c r="N59" s="1"/>
+    </row>
+    <row r="60" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A60" s="21" t="s">
+        <v>9</v>
+      </c>
+      <c r="B60" s="21">
+        <v>173</v>
+      </c>
+      <c r="C60" s="21">
+        <v>1174</v>
+      </c>
+      <c r="D60" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E60" s="16" t="s">
+      <c r="E60" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F60" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="G60" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="H60" t="s">
-        <v>240</v>
+      <c r="F60" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G60" s="19" t="s">
+        <v>229</v>
       </c>
       <c r="I60" t="s">
-        <v>246</v>
-      </c>
-      <c r="K60" s="1"/>
+        <v>245</v>
+      </c>
+      <c r="K60" s="4"/>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
-      <c r="N60" s="1"/>
-    </row>
-    <row r="61" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A61" s="20" t="s">
-        <v>162</v>
-      </c>
-      <c r="B61" s="20">
-        <v>1171</v>
-      </c>
-      <c r="C61" s="20">
-        <v>1171</v>
-      </c>
-      <c r="D61" s="19" t="s">
+      <c r="N60" s="4"/>
+    </row>
+    <row r="61" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A61" s="21" t="s">
+        <v>241</v>
+      </c>
+      <c r="B61" s="21">
+        <v>161</v>
+      </c>
+      <c r="C61" s="21">
+        <v>1068</v>
+      </c>
+      <c r="D61" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E61" s="16" t="s">
+      <c r="E61" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F61" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="G61" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="H61" t="s">
-        <v>240</v>
+      <c r="F61" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G61" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I61" t="s">
-        <v>246</v>
-      </c>
-      <c r="J61" t="s">
-        <v>249</v>
-      </c>
-      <c r="K61" s="1"/>
+        <v>245</v>
+      </c>
+      <c r="K61" s="4"/>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
-      <c r="N61" s="1"/>
-    </row>
-    <row r="62" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A62" s="27" t="s">
-        <v>217</v>
-      </c>
-      <c r="B62" s="27">
-        <v>178</v>
-      </c>
-      <c r="C62" s="27">
-        <v>1175</v>
-      </c>
-      <c r="D62" s="28" t="s">
+      <c r="N61" s="4"/>
+    </row>
+    <row r="62" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A62" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="B62" s="21">
+        <v>160</v>
+      </c>
+      <c r="C62" s="21">
+        <v>1212</v>
+      </c>
+      <c r="D62" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F62" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G62" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H62" t="s">
-        <v>240</v>
+      <c r="F62" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G62" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I62" t="s">
-        <v>246</v>
-      </c>
-      <c r="K62" s="1"/>
+        <v>245</v>
+      </c>
+      <c r="K62" s="4"/>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
-      <c r="N62" s="1"/>
-    </row>
-    <row r="63" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A63" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="B63" s="32">
-        <v>173</v>
-      </c>
-      <c r="C63" s="32">
-        <v>1174</v>
-      </c>
-      <c r="D63" s="28" t="s">
+      <c r="N62" s="4"/>
+    </row>
+    <row r="63" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A63" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="B63" s="16">
+        <v>146</v>
+      </c>
+      <c r="C63" s="16">
+        <v>1211</v>
+      </c>
+      <c r="D63" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E63" s="29" t="s">
+      <c r="E63" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F63" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G63" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H63" t="s">
-        <v>240</v>
+      <c r="F63" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G63" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I63" t="s">
-        <v>246</v>
-      </c>
-      <c r="K63" s="4"/>
+        <v>245</v>
+      </c>
+      <c r="K63" s="1"/>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
-      <c r="N63" s="4"/>
-    </row>
-    <row r="64" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A64" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="B64" s="32">
-        <v>161</v>
-      </c>
-      <c r="C64" s="32">
-        <v>1068</v>
-      </c>
-      <c r="D64" s="28" t="s">
+      <c r="N63" s="1"/>
+    </row>
+    <row r="64" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A64" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="B64" s="16">
+        <v>133</v>
+      </c>
+      <c r="C64" s="16">
+        <v>1231</v>
+      </c>
+      <c r="D64" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="17" t="s">
         <v>226</v>
       </c>
-      <c r="F64" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G64" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H64" t="s">
-        <v>240</v>
+      <c r="F64" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>230</v>
       </c>
       <c r="I64" t="s">
-        <v>246</v>
-      </c>
-      <c r="K64" s="4"/>
+        <v>245</v>
+      </c>
+      <c r="K64" s="1"/>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
-      <c r="N64" s="4"/>
-    </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A65" s="32" t="s">
-        <v>17</v>
-      </c>
-      <c r="B65" s="32">
-        <v>160</v>
-      </c>
-      <c r="C65" s="32">
-        <v>1212</v>
-      </c>
-      <c r="D65" s="28" t="s">
+      <c r="N64" s="1"/>
+    </row>
+    <row r="65" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A65" s="16" t="s">
+        <v>175</v>
+      </c>
+      <c r="B65" s="16">
+        <v>129</v>
+      </c>
+      <c r="C65" s="16">
+        <v>1132</v>
+      </c>
+      <c r="D65" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F65" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G65" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H65" t="s">
-        <v>240</v>
+      <c r="F65" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>229</v>
       </c>
       <c r="I65" t="s">
-        <v>246</v>
-      </c>
-      <c r="K65" s="4"/>
+        <v>245</v>
+      </c>
+      <c r="K65" s="1"/>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
-      <c r="N65" s="4"/>
-    </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A66" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="B66" s="21">
-        <v>158</v>
-      </c>
-      <c r="C66" s="21">
-        <v>1088</v>
-      </c>
-      <c r="D66" s="19" t="s">
+      <c r="N65" s="1"/>
+    </row>
+    <row r="66" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A66" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="B66" s="16">
+        <v>127</v>
+      </c>
+      <c r="C66" s="16">
+        <v>1172</v>
+      </c>
+      <c r="D66" s="17" t="s">
         <v>223</v>
       </c>
-      <c r="E66" s="17" t="s">
+      <c r="E66" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="F66" s="22" t="s">
-        <v>229</v>
-      </c>
-      <c r="G66" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="H66" t="s">
-        <v>240</v>
+      <c r="F66" s="19" t="s">
+        <v>229</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>229</v>
       </c>
       <c r="I66" t="s">
-        <v>246</v>
-      </c>
-      <c r="K66" s="4"/>
+        <v>245</v>
+      </c>
+      <c r="K66" s="1"/>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
-      <c r="N66" s="4"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A67" s="27" t="s">
-        <v>116</v>
-      </c>
-      <c r="B67" s="27">
-        <v>146</v>
-      </c>
-      <c r="C67" s="27">
-        <v>1211</v>
-      </c>
-      <c r="D67" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="E67" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="F67" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G67" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H67" t="s">
-        <v>240</v>
-      </c>
-      <c r="I67" t="s">
-        <v>246</v>
+      <c r="N66" s="1"/>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>77</v>
+      </c>
+      <c r="B67">
+        <v>1294</v>
+      </c>
+      <c r="C67">
+        <v>1294</v>
+      </c>
+      <c r="D67" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J67" t="s">
+        <v>249</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
       <c r="N67" s="1"/>
     </row>
-    <row r="68" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A68" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="B68" s="27">
-        <v>133</v>
-      </c>
-      <c r="C68" s="27">
-        <v>1231</v>
-      </c>
-      <c r="D68" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="E68" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="F68" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G68" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H68" t="s">
-        <v>240</v>
-      </c>
-      <c r="I68" t="s">
-        <v>246</v>
+    <row r="68" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>213</v>
+      </c>
+      <c r="B68">
+        <v>1254</v>
+      </c>
+      <c r="C68">
+        <v>1254</v>
+      </c>
+      <c r="D68" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E68" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J68" t="s">
+        <v>249</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
       <c r="N68" s="1"/>
     </row>
-    <row r="69" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A69" s="27" t="s">
-        <v>175</v>
-      </c>
-      <c r="B69" s="27">
-        <v>129</v>
-      </c>
-      <c r="C69" s="27">
-        <v>1132</v>
-      </c>
-      <c r="D69" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="E69" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="F69" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G69" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H69" t="s">
-        <v>240</v>
-      </c>
-      <c r="I69" t="s">
-        <v>246</v>
+    <row r="69" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>10</v>
+      </c>
+      <c r="B69">
+        <v>1191</v>
+      </c>
+      <c r="C69">
+        <v>1191</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="J69" t="s">
+        <v>250</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
       <c r="N69" s="1"/>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A70" s="27" t="s">
-        <v>66</v>
-      </c>
-      <c r="B70" s="27">
-        <v>127</v>
-      </c>
-      <c r="C70" s="27">
-        <v>1172</v>
-      </c>
-      <c r="D70" s="28" t="s">
-        <v>223</v>
-      </c>
-      <c r="E70" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="F70" s="30" t="s">
-        <v>229</v>
-      </c>
-      <c r="G70" s="30" t="s">
-        <v>230</v>
-      </c>
-      <c r="H70" t="s">
-        <v>240</v>
-      </c>
-      <c r="I70" t="s">
-        <v>246</v>
-      </c>
-      <c r="K70" s="1"/>
+    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A70" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B70" s="3">
+        <v>158</v>
+      </c>
+      <c r="C70" s="3">
+        <v>1088</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="K70" s="4"/>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
-      <c r="N70" s="1"/>
-    </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="N70" s="4"/>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>50</v>
       </c>
@@ -3513,7 +3411,7 @@
       <c r="M71" s="2"/>
       <c r="N71" s="1"/>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>53</v>
       </c>
@@ -3540,7 +3438,7 @@
       <c r="M72" s="2"/>
       <c r="N72" s="1"/>
     </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>101</v>
       </c>
@@ -3567,7 +3465,7 @@
       <c r="M73" s="2"/>
       <c r="N73" s="1"/>
     </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>196</v>
       </c>
@@ -3594,7 +3492,7 @@
       <c r="M74" s="2"/>
       <c r="N74" s="1"/>
     </row>
-    <row r="75" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>68</v>
       </c>
@@ -3624,7 +3522,7 @@
       <c r="M75" s="2"/>
       <c r="N75" s="1"/>
     </row>
-    <row r="76" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>136</v>
       </c>
@@ -3651,7 +3549,7 @@
       <c r="M76" s="2"/>
       <c r="N76" s="1"/>
     </row>
-    <row r="77" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>70</v>
       </c>
@@ -3678,7 +3576,7 @@
       <c r="M77" s="2"/>
       <c r="N77" s="1"/>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>28</v>
       </c>
@@ -3705,7 +3603,7 @@
       <c r="M78" s="2"/>
       <c r="N78" s="1"/>
     </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>128</v>
       </c>
@@ -3732,7 +3630,7 @@
       <c r="M79" s="2"/>
       <c r="N79" s="1"/>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>142</v>
       </c>
@@ -3762,7 +3660,7 @@
       <c r="M80" s="2"/>
       <c r="N80" s="4"/>
     </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>106</v>
       </c>
@@ -3789,7 +3687,7 @@
       <c r="M81" s="2"/>
       <c r="N81" s="1"/>
     </row>
-    <row r="82" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>30</v>
       </c>
@@ -3816,7 +3714,7 @@
       <c r="M82" s="2"/>
       <c r="N82" s="1"/>
     </row>
-    <row r="83" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>172</v>
       </c>
@@ -3843,7 +3741,7 @@
       <c r="M83" s="2"/>
       <c r="N83" s="1"/>
     </row>
-    <row r="84" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>60</v>
       </c>
@@ -3873,7 +3771,7 @@
       <c r="M84" s="2"/>
       <c r="N84" s="1"/>
     </row>
-    <row r="85" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>193</v>
       </c>
@@ -3903,7 +3801,7 @@
       <c r="M85" s="2"/>
       <c r="N85" s="1"/>
     </row>
-    <row r="86" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>56</v>
       </c>
@@ -3930,7 +3828,7 @@
       <c r="M86" s="2"/>
       <c r="N86" s="1"/>
     </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>218</v>
       </c>
@@ -3960,7 +3858,7 @@
       <c r="M87" s="2"/>
       <c r="N87" s="1"/>
     </row>
-    <row r="88" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>182</v>
       </c>
@@ -3987,7 +3885,7 @@
       <c r="M88" s="2"/>
       <c r="N88" s="1"/>
     </row>
-    <row r="89" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>153</v>
       </c>
@@ -4014,7 +3912,7 @@
       <c r="M89" s="2"/>
       <c r="N89" s="1"/>
     </row>
-    <row r="90" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>161</v>
       </c>
@@ -4041,7 +3939,7 @@
       <c r="M90" s="2"/>
       <c r="N90" s="1"/>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>177</v>
       </c>
@@ -4068,7 +3966,7 @@
       <c r="M91" s="2"/>
       <c r="N91" s="1"/>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>205</v>
       </c>
@@ -4095,7 +3993,7 @@
       <c r="M92" s="2"/>
       <c r="N92" s="1"/>
     </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>180</v>
       </c>
@@ -4122,7 +4020,7 @@
       <c r="M93" s="2"/>
       <c r="N93" s="1"/>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>16</v>
       </c>
@@ -4149,7 +4047,7 @@
       <c r="M94" s="2"/>
       <c r="N94" s="1"/>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>108</v>
       </c>
@@ -4176,7 +4074,7 @@
       <c r="M95" s="2"/>
       <c r="N95" s="1"/>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>178</v>
       </c>
@@ -4203,7 +4101,7 @@
       <c r="M96" s="2"/>
       <c r="N96" s="1"/>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>212</v>
       </c>
@@ -4230,26 +4128,26 @@
       <c r="M97" s="2"/>
       <c r="N97" s="1"/>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A98" s="24" t="s">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
         <v>170</v>
       </c>
-      <c r="B98" s="24">
+      <c r="B98">
         <v>1190</v>
       </c>
-      <c r="C98" s="24">
+      <c r="C98">
         <v>1190</v>
       </c>
-      <c r="D98" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="E98" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="F98" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="G98" s="26" t="s">
+      <c r="D98" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G98" s="2" t="s">
         <v>230</v>
       </c>
       <c r="K98" s="1"/>
@@ -4257,7 +4155,7 @@
       <c r="M98" s="2"/>
       <c r="N98" s="1"/>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>206</v>
       </c>
@@ -4284,7 +4182,7 @@
       <c r="M99" s="2"/>
       <c r="N99" s="1"/>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>39</v>
       </c>
@@ -4311,7 +4209,7 @@
       <c r="M100" s="2"/>
       <c r="N100" s="1"/>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>146</v>
       </c>
@@ -4338,7 +4236,7 @@
       <c r="M101" s="2"/>
       <c r="N101" s="1"/>
     </row>
-    <row r="102" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>173</v>
       </c>
@@ -4365,7 +4263,7 @@
       <c r="M102" s="2"/>
       <c r="N102" s="1"/>
     </row>
-    <row r="103" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>72</v>
       </c>
@@ -4392,7 +4290,7 @@
       <c r="M103" s="2"/>
       <c r="N103" s="1"/>
     </row>
-    <row r="104" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
         <v>147</v>
       </c>
@@ -4423,7 +4321,7 @@
       <c r="M104" s="2"/>
       <c r="N104" s="4"/>
     </row>
-    <row r="105" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>90</v>
       </c>
@@ -4450,7 +4348,7 @@
       <c r="M105" s="2"/>
       <c r="N105" s="1"/>
     </row>
-    <row r="106" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>156</v>
       </c>
@@ -4477,7 +4375,7 @@
       <c r="M106" s="2"/>
       <c r="N106" s="1"/>
     </row>
-    <row r="107" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>220</v>
       </c>
@@ -4504,7 +4402,7 @@
       <c r="M107" s="2"/>
       <c r="N107" s="1"/>
     </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
         <v>118</v>
       </c>
@@ -4533,7 +4431,7 @@
       <c r="M108" s="2"/>
       <c r="N108" s="4"/>
     </row>
-    <row r="109" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
         <v>67</v>
       </c>
@@ -4562,7 +4460,7 @@
       <c r="M109" s="2"/>
       <c r="N109" s="4"/>
     </row>
-    <row r="110" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
         <v>13</v>
       </c>
@@ -4591,7 +4489,7 @@
       <c r="M110" s="2"/>
       <c r="N110" s="4"/>
     </row>
-    <row r="111" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
         <v>14</v>
       </c>
@@ -4620,7 +4518,7 @@
       <c r="M111" s="2"/>
       <c r="N111" s="4"/>
     </row>
-    <row r="112" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
         <v>6</v>
       </c>
@@ -4649,7 +4547,7 @@
       <c r="M112" s="2"/>
       <c r="N112" s="4"/>
     </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
         <v>44</v>
       </c>
@@ -4678,7 +4576,7 @@
       <c r="M113" s="2"/>
       <c r="N113" s="4"/>
     </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
         <v>11</v>
       </c>
@@ -4707,7 +4605,7 @@
       <c r="M114" s="2"/>
       <c r="N114" s="4"/>
     </row>
-    <row r="115" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
         <v>12</v>
       </c>
@@ -4736,7 +4634,7 @@
       <c r="M115" s="2"/>
       <c r="N115" s="4"/>
     </row>
-    <row r="116" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
         <v>41</v>
       </c>
@@ -4765,7 +4663,7 @@
       <c r="M116" s="2"/>
       <c r="N116" s="4"/>
     </row>
-    <row r="117" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
         <v>42</v>
       </c>
@@ -4794,7 +4692,7 @@
       <c r="M117" s="2"/>
       <c r="N117" s="4"/>
     </row>
-    <row r="118" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
         <v>80</v>
       </c>
@@ -4823,7 +4721,7 @@
       <c r="M118" s="2"/>
       <c r="N118" s="4"/>
     </row>
-    <row r="119" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
         <v>74</v>
       </c>
@@ -4852,36 +4750,34 @@
       <c r="M119" s="2"/>
       <c r="N119" s="4"/>
     </row>
-    <row r="120" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A120" s="24" t="s">
+    <row r="120" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
         <v>143</v>
       </c>
-      <c r="B120" s="24">
+      <c r="B120">
         <v>154</v>
       </c>
-      <c r="C120" s="24">
+      <c r="C120">
         <v>1215</v>
       </c>
-      <c r="D120" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="E120" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="G120" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="H120" s="24"/>
-      <c r="I120" s="24"/>
+      <c r="D120" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="K120" s="1"/>
       <c r="L120" s="2"/>
       <c r="M120" s="2"/>
       <c r="N120" s="1"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>138</v>
       </c>
@@ -4908,7 +4804,7 @@
       <c r="M121" s="2"/>
       <c r="N121" s="1"/>
     </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>3</v>
       </c>
@@ -4918,7 +4814,7 @@
       <c r="C122">
         <v>1373</v>
       </c>
-      <c r="D122" s="23" t="s">
+      <c r="D122" s="15" t="s">
         <v>223</v>
       </c>
       <c r="E122" s="1" t="s">
@@ -4931,14 +4827,14 @@
         <v>230</v>
       </c>
       <c r="H122" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="K122" s="1"/>
       <c r="L122" s="2"/>
       <c r="M122" s="2"/>
       <c r="N122" s="1"/>
     </row>
-    <row r="123" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>124</v>
       </c>
@@ -4965,7 +4861,7 @@
       <c r="M123" s="2"/>
       <c r="N123" s="1"/>
     </row>
-    <row r="124" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>78</v>
       </c>
@@ -4992,7 +4888,7 @@
       <c r="M124" s="2"/>
       <c r="N124" s="1"/>
     </row>
-    <row r="125" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>71</v>
       </c>
@@ -5019,7 +4915,7 @@
       <c r="M125" s="2"/>
       <c r="N125" s="1"/>
     </row>
-    <row r="126" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>104</v>
       </c>
@@ -5046,7 +4942,7 @@
       <c r="M126" s="2"/>
       <c r="N126" s="1"/>
     </row>
-    <row r="127" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>95</v>
       </c>
@@ -5073,7 +4969,7 @@
       <c r="M127" s="2"/>
       <c r="N127" s="1"/>
     </row>
-    <row r="128" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>26</v>
       </c>
@@ -5100,7 +4996,7 @@
       <c r="M128" s="2"/>
       <c r="N128" s="1"/>
     </row>
-    <row r="129" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>134</v>
       </c>
@@ -5127,7 +5023,7 @@
       <c r="M129" s="2"/>
       <c r="N129" s="1"/>
     </row>
-    <row r="130" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>109</v>
       </c>
@@ -5154,7 +5050,7 @@
       <c r="M130" s="2"/>
       <c r="N130" s="1"/>
     </row>
-    <row r="131" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>126</v>
       </c>
@@ -5181,7 +5077,7 @@
       <c r="M131" s="2"/>
       <c r="N131" s="1"/>
     </row>
-    <row r="132" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>209</v>
       </c>
@@ -5208,7 +5104,7 @@
       <c r="M132" s="2"/>
       <c r="N132" s="1"/>
     </row>
-    <row r="133" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>33</v>
       </c>
@@ -5235,7 +5131,7 @@
       <c r="M133" s="2"/>
       <c r="N133" s="1"/>
     </row>
-    <row r="134" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>195</v>
       </c>
@@ -5262,7 +5158,7 @@
       <c r="M134" s="2"/>
       <c r="N134" s="1"/>
     </row>
-    <row r="135" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>190</v>
       </c>
@@ -5289,7 +5185,7 @@
       <c r="M135" s="2"/>
       <c r="N135" s="1"/>
     </row>
-    <row r="136" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>21</v>
       </c>
@@ -5316,7 +5212,7 @@
       <c r="M136" s="2"/>
       <c r="N136" s="1"/>
     </row>
-    <row r="137" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>207</v>
       </c>
@@ -5343,7 +5239,7 @@
       <c r="M137" s="2"/>
       <c r="N137" s="1"/>
     </row>
-    <row r="138" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>123</v>
       </c>
@@ -5370,7 +5266,7 @@
       <c r="M138" s="2"/>
       <c r="N138" s="1"/>
     </row>
-    <row r="139" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>87</v>
       </c>
@@ -5397,7 +5293,7 @@
       <c r="M139" s="2"/>
       <c r="N139" s="1"/>
     </row>
-    <row r="140" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>202</v>
       </c>
@@ -5424,7 +5320,7 @@
       <c r="M140" s="2"/>
       <c r="N140" s="1"/>
     </row>
-    <row r="141" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>137</v>
       </c>
@@ -5451,7 +5347,7 @@
       <c r="M141" s="2"/>
       <c r="N141" s="1"/>
     </row>
-    <row r="142" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>131</v>
       </c>
@@ -5478,7 +5374,7 @@
       <c r="M142" s="2"/>
       <c r="N142" s="1"/>
     </row>
-    <row r="143" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>216</v>
       </c>
@@ -5505,7 +5401,7 @@
       <c r="M143" s="2"/>
       <c r="N143" s="1"/>
     </row>
-    <row r="144" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>61</v>
       </c>
@@ -5532,7 +5428,7 @@
       <c r="M144" s="2"/>
       <c r="N144" s="1"/>
     </row>
-    <row r="145" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>65</v>
       </c>
@@ -5559,7 +5455,7 @@
       <c r="M145" s="2"/>
       <c r="N145" s="1"/>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>197</v>
       </c>
@@ -5586,7 +5482,7 @@
       <c r="M146" s="2"/>
       <c r="N146" s="1"/>
     </row>
-    <row r="147" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>73</v>
       </c>
@@ -5613,7 +5509,7 @@
       <c r="M147" s="2"/>
       <c r="N147" s="1"/>
     </row>
-    <row r="148" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>112</v>
       </c>
@@ -5640,7 +5536,7 @@
       <c r="M148" s="2"/>
       <c r="N148" s="1"/>
     </row>
-    <row r="149" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>83</v>
       </c>
@@ -5667,7 +5563,7 @@
       <c r="M149" s="2"/>
       <c r="N149" s="1"/>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>186</v>
       </c>
@@ -5694,7 +5590,7 @@
       <c r="M150" s="2"/>
       <c r="N150" s="1"/>
     </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>98</v>
       </c>
@@ -5721,7 +5617,7 @@
       <c r="M151" s="2"/>
       <c r="N151" s="1"/>
     </row>
-    <row r="152" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>199</v>
       </c>
@@ -5748,7 +5644,7 @@
       <c r="M152" s="2"/>
       <c r="N152" s="1"/>
     </row>
-    <row r="153" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>31</v>
       </c>
@@ -5775,7 +5671,7 @@
       <c r="M153" s="2"/>
       <c r="N153" s="1"/>
     </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>204</v>
       </c>
@@ -5802,7 +5698,7 @@
       <c r="M154" s="2"/>
       <c r="N154" s="1"/>
     </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>130</v>
       </c>
@@ -5829,7 +5725,7 @@
       <c r="M155" s="2"/>
       <c r="N155" s="1"/>
     </row>
-    <row r="156" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>52</v>
       </c>
@@ -5856,7 +5752,7 @@
       <c r="M156" s="2"/>
       <c r="N156" s="1"/>
     </row>
-    <row r="157" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>203</v>
       </c>
@@ -5883,7 +5779,7 @@
       <c r="M157" s="2"/>
       <c r="N157" s="1"/>
     </row>
-    <row r="158" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>171</v>
       </c>
@@ -5910,7 +5806,7 @@
       <c r="M158" s="2"/>
       <c r="N158" s="1"/>
     </row>
-    <row r="159" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>57</v>
       </c>
@@ -5937,7 +5833,7 @@
       <c r="M159" s="2"/>
       <c r="N159" s="1"/>
     </row>
-    <row r="160" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>69</v>
       </c>
@@ -5964,7 +5860,7 @@
       <c r="M160" s="2"/>
       <c r="N160" s="1"/>
     </row>
-    <row r="161" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>119</v>
       </c>
@@ -5991,7 +5887,7 @@
       <c r="M161" s="2"/>
       <c r="N161" s="1"/>
     </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>15</v>
       </c>
@@ -6018,7 +5914,7 @@
       <c r="M162" s="2"/>
       <c r="N162" s="1"/>
     </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>132</v>
       </c>
@@ -6045,7 +5941,7 @@
       <c r="M163" s="2"/>
       <c r="N163" s="1"/>
     </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>103</v>
       </c>
@@ -6072,7 +5968,7 @@
       <c r="M164" s="2"/>
       <c r="N164" s="1"/>
     </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>184</v>
       </c>
@@ -6099,7 +5995,7 @@
       <c r="M165" s="2"/>
       <c r="N165" s="1"/>
     </row>
-    <row r="166" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>84</v>
       </c>
@@ -6126,7 +6022,7 @@
       <c r="M166" s="2"/>
       <c r="N166" s="1"/>
     </row>
-    <row r="167" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>159</v>
       </c>
@@ -6153,7 +6049,7 @@
       <c r="M167" s="2"/>
       <c r="N167" s="1"/>
     </row>
-    <row r="168" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>133</v>
       </c>
@@ -6180,7 +6076,7 @@
       <c r="M168" s="2"/>
       <c r="N168" s="1"/>
     </row>
-    <row r="169" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>163</v>
       </c>
@@ -6207,7 +6103,7 @@
       <c r="M169" s="2"/>
       <c r="N169" s="1"/>
     </row>
-    <row r="170" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>97</v>
       </c>
@@ -6234,7 +6130,7 @@
       <c r="M170" s="2"/>
       <c r="N170" s="1"/>
     </row>
-    <row r="171" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>79</v>
       </c>
@@ -6261,7 +6157,7 @@
       <c r="M171" s="2"/>
       <c r="N171" s="1"/>
     </row>
-    <row r="172" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>102</v>
       </c>
@@ -6288,7 +6184,7 @@
       <c r="M172" s="2"/>
       <c r="N172" s="1"/>
     </row>
-    <row r="173" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>55</v>
       </c>
@@ -6315,7 +6211,7 @@
       <c r="M173" s="2"/>
       <c r="N173" s="1"/>
     </row>
-    <row r="174" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>45</v>
       </c>
@@ -6342,7 +6238,7 @@
       <c r="M174" s="2"/>
       <c r="N174" s="1"/>
     </row>
-    <row r="175" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>168</v>
       </c>
@@ -6369,7 +6265,7 @@
       <c r="M175" s="2"/>
       <c r="N175" s="1"/>
     </row>
-    <row r="176" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>215</v>
       </c>
@@ -6396,7 +6292,7 @@
       <c r="M176" s="2"/>
       <c r="N176" s="1"/>
     </row>
-    <row r="177" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>211</v>
       </c>
@@ -6423,7 +6319,7 @@
       <c r="M177" s="2"/>
       <c r="N177" s="1"/>
     </row>
-    <row r="178" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>166</v>
       </c>
@@ -6450,7 +6346,7 @@
       <c r="M178" s="2"/>
       <c r="N178" s="1"/>
     </row>
-    <row r="179" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>174</v>
       </c>
@@ -6477,7 +6373,7 @@
       <c r="M179" s="2"/>
       <c r="N179" s="1"/>
     </row>
-    <row r="180" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>8</v>
       </c>
@@ -6504,7 +6400,7 @@
       <c r="M180" s="2"/>
       <c r="N180" s="1"/>
     </row>
-    <row r="181" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>63</v>
       </c>
@@ -6531,7 +6427,7 @@
       <c r="M181" s="2"/>
       <c r="N181" s="1"/>
     </row>
-    <row r="182" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>49</v>
       </c>
@@ -6558,7 +6454,7 @@
       <c r="M182" s="2"/>
       <c r="N182" s="1"/>
     </row>
-    <row r="183" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>48</v>
       </c>
@@ -6585,7 +6481,7 @@
       <c r="M183" s="2"/>
       <c r="N183" s="1"/>
     </row>
-    <row r="184" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>114</v>
       </c>
@@ -6612,7 +6508,7 @@
       <c r="M184" s="2"/>
       <c r="N184" s="1"/>
     </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>27</v>
       </c>
@@ -6639,7 +6535,7 @@
       <c r="M185" s="2"/>
       <c r="N185" s="1"/>
     </row>
-    <row r="186" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>181</v>
       </c>
@@ -6666,7 +6562,7 @@
       <c r="M186" s="2"/>
       <c r="N186" s="1"/>
     </row>
-    <row r="187" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>219</v>
       </c>
@@ -6693,7 +6589,7 @@
       <c r="M187" s="2"/>
       <c r="N187" s="1"/>
     </row>
-    <row r="188" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>94</v>
       </c>
@@ -6720,7 +6616,7 @@
       <c r="M188" s="2"/>
       <c r="N188" s="1"/>
     </row>
-    <row r="189" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>167</v>
       </c>
@@ -6747,7 +6643,7 @@
       <c r="M189" s="2"/>
       <c r="N189" s="1"/>
     </row>
-    <row r="190" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>76</v>
       </c>
@@ -6774,7 +6670,7 @@
       <c r="M190" s="2"/>
       <c r="N190" s="1"/>
     </row>
-    <row r="191" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -6801,7 +6697,7 @@
       <c r="M191" s="2"/>
       <c r="N191" s="1"/>
     </row>
-    <row r="192" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>121</v>
       </c>
@@ -6828,7 +6724,7 @@
       <c r="M192" s="2"/>
       <c r="N192" s="1"/>
     </row>
-    <row r="193" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>187</v>
       </c>
@@ -6855,7 +6751,7 @@
       <c r="M193" s="2"/>
       <c r="N193" s="1"/>
     </row>
-    <row r="194" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>169</v>
       </c>
@@ -6882,7 +6778,7 @@
       <c r="M194" s="2"/>
       <c r="N194" s="1"/>
     </row>
-    <row r="195" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>40</v>
       </c>
@@ -6909,7 +6805,7 @@
       <c r="M195" s="2"/>
       <c r="N195" s="1"/>
     </row>
-    <row r="196" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>189</v>
       </c>
@@ -6936,7 +6832,7 @@
       <c r="M196" s="2"/>
       <c r="N196" s="1"/>
     </row>
-    <row r="197" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>214</v>
       </c>
@@ -6963,7 +6859,7 @@
       <c r="M197" s="2"/>
       <c r="N197" s="1"/>
     </row>
-    <row r="198" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>34</v>
       </c>
@@ -6990,7 +6886,7 @@
       <c r="M198" s="2"/>
       <c r="N198" s="1"/>
     </row>
-    <row r="199" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>117</v>
       </c>
@@ -7017,7 +6913,7 @@
       <c r="M199" s="2"/>
       <c r="N199" s="1"/>
     </row>
-    <row r="200" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>113</v>
       </c>
@@ -7044,7 +6940,7 @@
       <c r="M200" s="2"/>
       <c r="N200" s="1"/>
     </row>
-    <row r="201" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>191</v>
       </c>
@@ -7071,7 +6967,7 @@
       <c r="M201" s="2"/>
       <c r="N201" s="1"/>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>58</v>
       </c>
@@ -7098,7 +6994,7 @@
       <c r="M202" s="2"/>
       <c r="N202" s="1"/>
     </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>122</v>
       </c>
@@ -7125,7 +7021,7 @@
       <c r="M203" s="2"/>
       <c r="N203" s="1"/>
     </row>
-    <row r="204" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>37</v>
       </c>
@@ -7152,7 +7048,7 @@
       <c r="M204" s="2"/>
       <c r="N204" s="1"/>
     </row>
-    <row r="205" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>46</v>
       </c>
@@ -7179,7 +7075,7 @@
       <c r="M205" s="2"/>
       <c r="N205" s="1"/>
     </row>
-    <row r="206" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>29</v>
       </c>
@@ -7206,7 +7102,7 @@
       <c r="M206" s="2"/>
       <c r="N206" s="1"/>
     </row>
-    <row r="207" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>151</v>
       </c>
@@ -7233,7 +7129,7 @@
       <c r="M207" s="2"/>
       <c r="N207" s="1"/>
     </row>
-    <row r="208" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>221</v>
       </c>
@@ -7260,7 +7156,7 @@
       <c r="M208" s="2"/>
       <c r="N208" s="1"/>
     </row>
-    <row r="209" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>165</v>
       </c>
@@ -7287,7 +7183,7 @@
       <c r="M209" s="2"/>
       <c r="N209" s="1"/>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>75</v>
       </c>
@@ -7314,7 +7210,7 @@
       <c r="M210" s="2"/>
       <c r="N210" s="1"/>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>92</v>
       </c>
@@ -7341,7 +7237,7 @@
       <c r="M211" s="2"/>
       <c r="N211" s="1"/>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>183</v>
       </c>
@@ -7368,7 +7264,7 @@
       <c r="M212" s="2"/>
       <c r="N212" s="1"/>
     </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>62</v>
       </c>
@@ -7395,26 +7291,26 @@
       <c r="M213" s="2"/>
       <c r="N213" s="1"/>
     </row>
-    <row r="214" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A214" s="24" t="s">
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
         <v>127</v>
       </c>
-      <c r="B214" s="24">
+      <c r="B214">
         <v>14</v>
       </c>
-      <c r="C214" s="24">
+      <c r="C214">
         <v>1198</v>
       </c>
-      <c r="D214" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="E214" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="F214" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="G214" s="26" t="s">
+      <c r="D214" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="E214" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F214" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="G214" s="2" t="s">
         <v>230</v>
       </c>
       <c r="K214" s="1"/>
@@ -7422,7 +7318,7 @@
       <c r="M214" s="2"/>
       <c r="N214" s="1"/>
     </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>32</v>
       </c>
@@ -7449,7 +7345,7 @@
       <c r="M215" s="2"/>
       <c r="N215" s="1"/>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>82</v>
       </c>
@@ -7476,7 +7372,7 @@
       <c r="M216" s="2"/>
       <c r="N216" s="1"/>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>51</v>
       </c>
@@ -7503,7 +7399,7 @@
       <c r="M217" s="2"/>
       <c r="N217" s="1"/>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>93</v>
       </c>
@@ -7530,7 +7426,7 @@
       <c r="M218" s="2"/>
       <c r="N218" s="1"/>
     </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>81</v>
       </c>
@@ -7557,7 +7453,7 @@
       <c r="M219" s="2"/>
       <c r="N219" s="1"/>
     </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>47</v>
       </c>
@@ -7584,7 +7480,7 @@
       <c r="M220" s="2"/>
       <c r="N220" s="1"/>
     </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>85</v>
       </c>
@@ -7613,10 +7509,10 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:P1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:N225">
-    <sortCondition descending="1" ref="E2:E225"/>
-    <sortCondition ref="I2:I225"/>
-    <sortCondition descending="1" ref="B2:B225"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:N221">
+    <sortCondition descending="1" ref="E1:E221"/>
+    <sortCondition ref="I1:I221"/>
+    <sortCondition descending="1" ref="B1:B221"/>
   </sortState>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
